--- a/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FF5D5E2-9EA3-4A68-B295-DFB116ABAA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68616C16-9A92-45DC-9084-72F774CA4112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -1383,18 +1383,318 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_069</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 69</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_024</t>
   </si>
   <si>
@@ -1407,112 +1707,28 @@
     <t>connecting solar to buses in cluster 38</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
+    <t>distr_solelc_spv_IND_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
   </si>
   <si>
     <t>distr_solelc_spv_IND_004</t>
@@ -1539,6 +1755,30 @@
     <t>connecting solar to buses in cluster 75</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_001</t>
   </si>
   <si>
@@ -1575,204 +1815,6 @@
     <t>connecting solar to buses in cluster 58</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_007</t>
   </si>
   <si>
@@ -1815,190 +1857,412 @@
     <t>connecting solar to buses in cluster 45</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
-    <t>e_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>e_w420797421-765_IND,e_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>e_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>e_w1143180503-765_IND,e_w369866141-765_IND,e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>e_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>e_w315823978-765_IND,e_w201845280-765_IND,e_w353914865-765_IND,e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311118424-765_IND,e_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND,e_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>e_w420797421-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w315823978-765_IND,e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w201845280-765_IND,e_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN684-765_IND,e_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND,e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>e_w209826798-765_IND,e_w420797421-765_IND,e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>e_w209826798-765_IND,e_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>e_w201845280-765_IND,e_w688672711-765_IND,e_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND,e_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>e_w201845280-765_IND,e_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w688672711-765_IND,e_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND,e_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>e_w353914865-765_IND,e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>e_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w688672711-765_IND,e_w331275940-765_IND,e_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>e_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>e_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>e_w331275940-765_IND,e_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w1143180503-765_IND,e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND,e_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND,e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND,e_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>e_w201845280-765_IND,e_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND,e_w386153973-765_IND,e_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>e_w201845280-765_IND,e_w420797421-765_IND,e_w353914865-765_IND,e_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>e_w353914865-765_IND,e_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>e_w353914865-765_IND,e_w311118424-765_IND,e_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>e_w209826798-765_IND,e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>e_w331275940-765_IND,e_w1143180503-765_IND,e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>e_w353914865-765_IND,e_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>e_w201845280-765_IND,e_w331275940-765_IND,e_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w315823978-765_IND,e_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>e_w331275940-765_IND,e_w209826798-765_IND,e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>e_w315823978-765_IND</t>
+    <t>e_Solapur_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND,e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND,e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_Rajahmundry_IND,e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND,e_Vadodara_IND,e_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND,e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND,e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND,e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND,e_Dharmapuri_IND,e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Sikandarabad_IND,e_Korba_IND,e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND,e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND,e_Fatehpur_IND,e_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND,e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND,e_Jaipur_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND,e_Indore_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND,e_Wardha_IND,e_Korba_IND,e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND,e_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>e_Moga_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Sikandarabad_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND,e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Medinipur_IND,e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND,e_Phalodi_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND,e_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Bhuj_IND,e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND,e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND,e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND,e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Vadodara_IND,e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_067</t>
@@ -2031,148 +2295,64 @@
     <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
+    <t>distr_wonelc_won_IND_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_061</t>
@@ -2223,192 +2403,174 @@
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>elc_won_IND_053</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND,e_Vadodara_IND,e_Bhuj_IND,e_Indore_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_036</t>
+  </si>
+  <si>
+    <t>elc_won_IND_012</t>
+  </si>
+  <si>
+    <t>elc_won_IND_066</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND,e_Phalodi_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_040</t>
+  </si>
+  <si>
+    <t>elc_won_IND_038</t>
+  </si>
+  <si>
+    <t>elc_won_IND_052</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_037</t>
+  </si>
+  <si>
+    <t>elc_won_IND_032</t>
+  </si>
+  <si>
+    <t>elc_won_IND_018</t>
+  </si>
+  <si>
+    <t>elc_won_IND_008</t>
+  </si>
+  <si>
+    <t>elc_won_IND_007</t>
+  </si>
+  <si>
+    <t>elc_won_IND_006</t>
+  </si>
+  <si>
+    <t>elc_won_IND_051</t>
+  </si>
+  <si>
+    <t>elc_won_IND_004</t>
+  </si>
+  <si>
+    <t>elc_won_IND_029</t>
+  </si>
+  <si>
+    <t>elc_won_IND_003</t>
+  </si>
+  <si>
+    <t>elc_won_IND_055</t>
+  </si>
+  <si>
+    <t>elc_won_IND_016</t>
+  </si>
+  <si>
+    <t>elc_won_IND_028</t>
+  </si>
+  <si>
+    <t>elc_won_IND_049</t>
+  </si>
+  <si>
+    <t>elc_won_IND_047</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND,e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_035</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Vadodara_IND,e_Indore_IND,e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_062</t>
+  </si>
+  <si>
+    <t>elc_won_IND_033</t>
+  </si>
+  <si>
+    <t>elc_won_IND_060</t>
+  </si>
+  <si>
+    <t>elc_won_IND_010</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND,e_Korba_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_019</t>
+  </si>
+  <si>
+    <t>elc_won_IND_017</t>
+  </si>
+  <si>
+    <t>elc_won_IND_057</t>
+  </si>
+  <si>
+    <t>elc_won_IND_041</t>
+  </si>
+  <si>
+    <t>elc_won_IND_030</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND,e_Kurnool_IND,e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_043</t>
+  </si>
+  <si>
+    <t>elc_won_IND_045</t>
+  </si>
+  <si>
+    <t>elc_won_IND_031</t>
+  </si>
+  <si>
+    <t>elc_won_IND_059</t>
+  </si>
+  <si>
+    <t>elc_won_IND_027</t>
+  </si>
+  <si>
+    <t>elc_won_IND_056</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Jaipur_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_054</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_014</t>
+  </si>
+  <si>
+    <t>elc_won_IND_050</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND,e_Wardha_IND,e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_064</t>
+  </si>
+  <si>
+    <t>elc_won_IND_011</t>
+  </si>
+  <si>
+    <t>elc_won_IND_025</t>
+  </si>
+  <si>
+    <t>e_Medinipur_IND</t>
   </si>
   <si>
     <t>elc_won_IND_067</t>
   </si>
   <si>
-    <t>e_w1143180503-765_IND,e_w369866141-765_IND</t>
-  </si>
-  <si>
     <t>elc_won_IND_063</t>
   </si>
   <si>
@@ -2421,88 +2583,34 @@
     <t>elc_won_IND_026</t>
   </si>
   <si>
-    <t>elc_won_IND_051</t>
-  </si>
-  <si>
-    <t>elc_won_IND_004</t>
-  </si>
-  <si>
-    <t>elc_won_IND_029</t>
-  </si>
-  <si>
-    <t>elc_won_IND_003</t>
-  </si>
-  <si>
-    <t>elc_won_IND_066</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND,e_w1143180503-765_IND,e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_040</t>
-  </si>
-  <si>
-    <t>elc_won_IND_038</t>
-  </si>
-  <si>
-    <t>elc_won_IND_055</t>
-  </si>
-  <si>
-    <t>elc_won_IND_016</t>
-  </si>
-  <si>
-    <t>elc_won_IND_028</t>
-  </si>
-  <si>
-    <t>elc_won_IND_043</t>
-  </si>
-  <si>
-    <t>elc_won_IND_045</t>
-  </si>
-  <si>
-    <t>elc_won_IND_031</t>
-  </si>
-  <si>
-    <t>elc_won_IND_059</t>
-  </si>
-  <si>
-    <t>elc_won_IND_027</t>
-  </si>
-  <si>
-    <t>elc_won_IND_049</t>
-  </si>
-  <si>
-    <t>elc_won_IND_047</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND,e_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_035</t>
-  </si>
-  <si>
-    <t>e_w201845280-765_IND,e_w331275940-765_IND,e_w209826798-765_IND,e_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_062</t>
-  </si>
-  <si>
-    <t>elc_won_IND_033</t>
-  </si>
-  <si>
-    <t>elc_won_IND_060</t>
-  </si>
-  <si>
-    <t>elc_won_IND_010</t>
-  </si>
-  <si>
-    <t>e_w311118424-765_IND,e_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_019</t>
-  </si>
-  <si>
-    <t>elc_won_IND_017</t>
+    <t>elc_won_IND_048</t>
+  </si>
+  <si>
+    <t>elc_won_IND_034</t>
+  </si>
+  <si>
+    <t>elc_won_IND_046</t>
+  </si>
+  <si>
+    <t>elc_won_IND_022</t>
+  </si>
+  <si>
+    <t>elc_won_IND_065</t>
+  </si>
+  <si>
+    <t>elc_won_IND_044</t>
+  </si>
+  <si>
+    <t>elc_won_IND_042</t>
+  </si>
+  <si>
+    <t>elc_won_IND_005</t>
+  </si>
+  <si>
+    <t>elc_won_IND_039</t>
+  </si>
+  <si>
+    <t>elc_won_IND_002</t>
   </si>
   <si>
     <t>elc_won_IND_061</t>
@@ -2523,126 +2631,78 @@
     <t>elc_won_IND_023</t>
   </si>
   <si>
-    <t>e_w759521252-765_IND</t>
-  </si>
-  <si>
     <t>elc_won_IND_009</t>
   </si>
   <si>
     <t>elc_won_IND_013</t>
   </si>
   <si>
-    <t>elc_won_IND_057</t>
-  </si>
-  <si>
-    <t>elc_won_IND_041</t>
-  </si>
-  <si>
-    <t>elc_won_IND_030</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND,e_w315823978-765_IND,e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_052</t>
-  </si>
-  <si>
-    <t>elc_won_IND_037</t>
-  </si>
-  <si>
-    <t>elc_won_IND_032</t>
-  </si>
-  <si>
-    <t>elc_won_IND_018</t>
-  </si>
-  <si>
-    <t>elc_won_IND_048</t>
-  </si>
-  <si>
-    <t>elc_won_IND_034</t>
-  </si>
-  <si>
-    <t>elc_won_IND_046</t>
-  </si>
-  <si>
-    <t>elc_won_IND_022</t>
-  </si>
-  <si>
-    <t>elc_won_IND_065</t>
-  </si>
-  <si>
-    <t>elc_won_IND_044</t>
-  </si>
-  <si>
-    <t>elc_won_IND_042</t>
-  </si>
-  <si>
-    <t>elc_won_IND_005</t>
-  </si>
-  <si>
-    <t>elc_won_IND_039</t>
-  </si>
-  <si>
-    <t>elc_won_IND_002</t>
-  </si>
-  <si>
-    <t>elc_won_IND_050</t>
-  </si>
-  <si>
-    <t>e_w688672711-765_IND,e_w201845280-765_IND,e_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_064</t>
-  </si>
-  <si>
-    <t>elc_won_IND_011</t>
-  </si>
-  <si>
-    <t>elc_won_IND_025</t>
-  </si>
-  <si>
-    <t>elc_won_IND_008</t>
-  </si>
-  <si>
-    <t>elc_won_IND_007</t>
-  </si>
-  <si>
-    <t>elc_won_IND_006</t>
-  </si>
-  <si>
-    <t>elc_won_IND_056</t>
-  </si>
-  <si>
-    <t>e_w209826798-765_IND,e_w369866141-765_IND,e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_054</t>
-  </si>
-  <si>
-    <t>e_w420797421-765_IND,e_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_014</t>
-  </si>
-  <si>
-    <t>elc_won_IND_053</t>
-  </si>
-  <si>
-    <t>e_w1143180503-765_IND,e_w331275940-765_IND,e_w688672711-765_IND,e_w209826798-765_IND,e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_036</t>
-  </si>
-  <si>
-    <t>elc_won_IND_012</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_002</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_IND_011</t>
   </si>
   <si>
@@ -2661,46 +2721,40 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_010</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
+    <t>distr_wofelc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_009</t>
@@ -2727,67 +2781,43 @@
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
     <t>elc_wof_IND_002</t>
   </si>
   <si>
+    <t>elc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_013</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_023</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_018</t>
+  </si>
+  <si>
     <t>elc_wof_IND_011</t>
   </si>
   <si>
-    <t>e_w201845280-765_IND,e_w688672711-765_IND</t>
+    <t>e_Wardha_IND,e_Bhuj_IND</t>
   </si>
   <si>
     <t>elc_wof_IND_003</t>
@@ -2796,31 +2826,28 @@
     <t>elc_wof_IND_016</t>
   </si>
   <si>
-    <t>elc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_018</t>
-  </si>
-  <si>
     <t>elc_wof_IND_010</t>
   </si>
   <si>
-    <t>elc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_012</t>
+    <t>elc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_022</t>
   </si>
   <si>
     <t>elc_wof_IND_009</t>
   </si>
   <si>
-    <t>e_w688672711-765_IND,e_w201845280-765_IND</t>
+    <t>e_Bhuj_IND,e_Wardha_IND</t>
   </si>
   <si>
     <t>elc_wof_IND_017</t>
@@ -2832,34 +2859,7 @@
     <t>elc_wof_IND_021</t>
   </si>
   <si>
-    <t>e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_015</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_013</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_023</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_024</t>
+    <t>e_Rajahmundry_IND</t>
   </si>
   <si>
     <t>e_won_IND_001</t>
@@ -8280,7 +8280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02DA0041-FDD9-49B3-BBEC-39D5D75E2FDA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A24A560-DA28-4BDD-AE41-EB216959A8BF}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -8518,16 +8518,16 @@
         <v>418</v>
       </c>
       <c r="Y11" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="Z11" t="s">
         <v>578</v>
       </c>
       <c r="AA11">
-        <v>0.99670408962762203</v>
+        <v>0.99540885392130762</v>
       </c>
       <c r="AB11">
-        <v>60.425023493595695</v>
+        <v>84.171011442693441</v>
       </c>
       <c r="AD11" t="s">
         <v>417</v>
@@ -8560,10 +8560,10 @@
         <v>759</v>
       </c>
       <c r="AO11">
-        <v>0.99584476105827657</v>
+        <v>0.99439150850611324</v>
       </c>
       <c r="AP11">
-        <v>76.179380598263194</v>
+        <v>102.82234405458999</v>
       </c>
       <c r="AR11" t="s">
         <v>417</v>
@@ -8593,7 +8593,7 @@
         <v>884</v>
       </c>
       <c r="BB11" t="s">
-        <v>621</v>
+        <v>603</v>
       </c>
       <c r="BC11">
         <v>0.97123008268954114</v>
@@ -8664,16 +8664,16 @@
         <v>422</v>
       </c>
       <c r="Y12" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="Z12" t="s">
         <v>579</v>
       </c>
       <c r="AA12">
-        <v>0.9960389195261472</v>
+        <v>0.99360802526828129</v>
       </c>
       <c r="AB12">
-        <v>72.619808687301173</v>
+        <v>117.18620341484296</v>
       </c>
       <c r="AD12" t="s">
         <v>417</v>
@@ -8703,13 +8703,13 @@
         <v>760</v>
       </c>
       <c r="AN12" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="AO12">
-        <v>0.9961146125371938</v>
+        <v>0.99595416313893737</v>
       </c>
       <c r="AP12">
-        <v>71.232103484781334</v>
+        <v>74.173675786148877</v>
       </c>
       <c r="AR12" t="s">
         <v>417</v>
@@ -8739,13 +8739,13 @@
         <v>885</v>
       </c>
       <c r="BB12" t="s">
-        <v>886</v>
+        <v>588</v>
       </c>
       <c r="BC12">
-        <v>0.98158890816872557</v>
+        <v>0.99603877136023145</v>
       </c>
       <c r="BD12">
-        <v>337.53668357336363</v>
+        <v>72.622525062424401</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8810,16 +8810,16 @@
         <v>424</v>
       </c>
       <c r="Y13" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="Z13" t="s">
         <v>580</v>
       </c>
       <c r="AA13">
-        <v>0.99707957985864093</v>
+        <v>0.99515679011930902</v>
       </c>
       <c r="AB13">
-        <v>53.541035924916123</v>
+        <v>88.792181146001369</v>
       </c>
       <c r="AD13" t="s">
         <v>417</v>
@@ -8849,13 +8849,13 @@
         <v>761</v>
       </c>
       <c r="AN13" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AO13">
-        <v>0.99607298561021362</v>
+        <v>0.99687821505939955</v>
       </c>
       <c r="AP13">
-        <v>71.995263812749926</v>
+        <v>57.232723911007447</v>
       </c>
       <c r="AR13" t="s">
         <v>417</v>
@@ -8882,16 +8882,16 @@
         <v>840</v>
       </c>
       <c r="BA13" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="BB13" t="s">
-        <v>621</v>
+        <v>588</v>
       </c>
       <c r="BC13">
-        <v>0.98402494782096717</v>
+        <v>0.99526782804010661</v>
       </c>
       <c r="BD13">
-        <v>292.87595661560192</v>
+        <v>86.756485931379871</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8956,16 +8956,16 @@
         <v>426</v>
       </c>
       <c r="Y14" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="Z14" t="s">
         <v>581</v>
       </c>
       <c r="AA14">
-        <v>0.99569491323214321</v>
+        <v>0.99409145347725225</v>
       </c>
       <c r="AB14">
-        <v>78.926590744041093</v>
+        <v>108.32335291704148</v>
       </c>
       <c r="AD14" t="s">
         <v>417</v>
@@ -8995,13 +8995,13 @@
         <v>762</v>
       </c>
       <c r="AN14" t="s">
-        <v>618</v>
+        <v>763</v>
       </c>
       <c r="AO14">
-        <v>0.9929182563937401</v>
+        <v>0.99618121233373258</v>
       </c>
       <c r="AP14">
-        <v>129.83196611476453</v>
+        <v>70.011107214903078</v>
       </c>
       <c r="AR14" t="s">
         <v>417</v>
@@ -9028,16 +9028,16 @@
         <v>842</v>
       </c>
       <c r="BA14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="BB14" t="s">
-        <v>578</v>
+        <v>615</v>
       </c>
       <c r="BC14">
-        <v>0.99223982078870177</v>
+        <v>0.98605138538291048</v>
       </c>
       <c r="BD14">
-        <v>142.26995220713331</v>
+        <v>255.7246013133088</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9102,16 +9102,16 @@
         <v>428</v>
       </c>
       <c r="Y15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Z15" t="s">
         <v>582</v>
       </c>
       <c r="AA15">
-        <v>0.99484118006716937</v>
+        <v>0.99464051280908794</v>
       </c>
       <c r="AB15">
-        <v>94.578365435227795</v>
+        <v>98.257265166721183</v>
       </c>
       <c r="AD15" t="s">
         <v>417</v>
@@ -9138,16 +9138,16 @@
         <v>632</v>
       </c>
       <c r="AM15" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AN15" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="AO15">
-        <v>0.99628542339510884</v>
+        <v>0.99592364356186902</v>
       </c>
       <c r="AP15">
-        <v>68.100571089671959</v>
+        <v>74.733201365734146</v>
       </c>
       <c r="AR15" t="s">
         <v>417</v>
@@ -9174,16 +9174,16 @@
         <v>844</v>
       </c>
       <c r="BA15" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="BB15" t="s">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="BC15">
-        <v>0.96206044130113966</v>
+        <v>0.99307601382667698</v>
       </c>
       <c r="BD15">
-        <v>695.55857614577315</v>
+        <v>126.93974651092147</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9248,16 +9248,16 @@
         <v>430</v>
       </c>
       <c r="Y16" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="Z16" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AA16">
-        <v>0.99539558382203508</v>
+        <v>0.99579357955795456</v>
       </c>
       <c r="AB16">
-        <v>84.414296596023817</v>
+        <v>77.117708104165573</v>
       </c>
       <c r="AD16" t="s">
         <v>417</v>
@@ -9284,16 +9284,16 @@
         <v>634</v>
       </c>
       <c r="AM16" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AN16" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="AO16">
-        <v>0.99533901157332205</v>
+        <v>0.99641167752379312</v>
       </c>
       <c r="AP16">
-        <v>85.451454489096079</v>
+        <v>65.785912063792665</v>
       </c>
       <c r="AR16" t="s">
         <v>417</v>
@@ -9320,16 +9320,16 @@
         <v>846</v>
       </c>
       <c r="BA16" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="BB16" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="BC16">
-        <v>0.98742179529179352</v>
+        <v>0.99275904397179515</v>
       </c>
       <c r="BD16">
-        <v>230.6004196504513</v>
+        <v>132.75086051708826</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9394,16 +9394,16 @@
         <v>432</v>
       </c>
       <c r="Y17" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Z17" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA17">
-        <v>0.99125780375299366</v>
+        <v>0.99066346416517681</v>
       </c>
       <c r="AB17">
-        <v>160.27359786178269</v>
+        <v>171.16982363842584</v>
       </c>
       <c r="AD17" t="s">
         <v>417</v>
@@ -9430,16 +9430,16 @@
         <v>636</v>
       </c>
       <c r="AM17" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AN17" t="s">
-        <v>594</v>
+        <v>767</v>
       </c>
       <c r="AO17">
-        <v>0.99754339130519476</v>
+        <v>0.99540934349034305</v>
       </c>
       <c r="AP17">
-        <v>45.037826071429087</v>
+        <v>84.162036010377406</v>
       </c>
       <c r="AR17" t="s">
         <v>417</v>
@@ -9466,16 +9466,16 @@
         <v>848</v>
       </c>
       <c r="BA17" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="BB17" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="BC17">
-        <v>0.98154438143849254</v>
+        <v>0.98787195157138663</v>
       </c>
       <c r="BD17">
-        <v>338.35300696097039</v>
+        <v>222.34755452457901</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9540,16 +9540,16 @@
         <v>434</v>
       </c>
       <c r="Y18" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="Z18" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AA18">
-        <v>0.99619006668481902</v>
+        <v>0.99560939477262078</v>
       </c>
       <c r="AB18">
-        <v>69.848777444984194</v>
+        <v>80.494429168619106</v>
       </c>
       <c r="AD18" t="s">
         <v>417</v>
@@ -9576,16 +9576,16 @@
         <v>638</v>
       </c>
       <c r="AM18" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AN18" t="s">
         <v>588</v>
       </c>
       <c r="AO18">
-        <v>0.99542398891280204</v>
+        <v>0.99657664224037934</v>
       </c>
       <c r="AP18">
-        <v>83.893536598629126</v>
+        <v>62.761558926379031</v>
       </c>
       <c r="AR18" t="s">
         <v>417</v>
@@ -9612,16 +9612,16 @@
         <v>850</v>
       </c>
       <c r="BA18" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="BB18" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="BC18">
-        <v>0.99307601382667698</v>
+        <v>0.98853599644984702</v>
       </c>
       <c r="BD18">
-        <v>126.93974651092147</v>
+        <v>210.17339841947171</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9686,16 +9686,16 @@
         <v>436</v>
       </c>
       <c r="Y19" t="s">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="Z19" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AA19">
-        <v>0.99021813732178554</v>
+        <v>0.99544039231362502</v>
       </c>
       <c r="AB19">
-        <v>179.3341491005981</v>
+        <v>83.592807583541571</v>
       </c>
       <c r="AD19" t="s">
         <v>417</v>
@@ -9722,16 +9722,16 @@
         <v>640</v>
       </c>
       <c r="AM19" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="AN19" t="s">
-        <v>601</v>
+        <v>621</v>
       </c>
       <c r="AO19">
-        <v>0.99617615910816915</v>
+        <v>0.99091245964276031</v>
       </c>
       <c r="AP19">
-        <v>70.103749683564772</v>
+        <v>166.60490654939525</v>
       </c>
       <c r="AR19" t="s">
         <v>417</v>
@@ -9758,16 +9758,16 @@
         <v>852</v>
       </c>
       <c r="BA19" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="BB19" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="BC19">
-        <v>0.99275904397179515</v>
+        <v>0.98734896749216872</v>
       </c>
       <c r="BD19">
-        <v>132.75086051708826</v>
+        <v>231.9355959769062</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9832,16 +9832,16 @@
         <v>438</v>
       </c>
       <c r="Y20" t="s">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="Z20" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="AA20">
-        <v>0.99686736582623381</v>
+        <v>0.99190124970484694</v>
       </c>
       <c r="AB20">
-        <v>57.431626519047455</v>
+        <v>148.47708874447352</v>
       </c>
       <c r="AD20" t="s">
         <v>417</v>
@@ -9868,16 +9868,16 @@
         <v>642</v>
       </c>
       <c r="AM20" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AN20" t="s">
-        <v>769</v>
+        <v>591</v>
       </c>
       <c r="AO20">
-        <v>0.99618121233373258</v>
+        <v>0.99846230399777702</v>
       </c>
       <c r="AP20">
-        <v>70.011107214903078</v>
+        <v>28.191093374087806</v>
       </c>
       <c r="AR20" t="s">
         <v>417</v>
@@ -9904,16 +9904,16 @@
         <v>854</v>
       </c>
       <c r="BA20" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="BB20" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="BC20">
-        <v>0.98787195157138663</v>
+        <v>0.96206044130113966</v>
       </c>
       <c r="BD20">
-        <v>222.34755452457901</v>
+        <v>695.55857614577315</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9978,16 +9978,16 @@
         <v>440</v>
       </c>
       <c r="Y21" t="s">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="Z21" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="AA21">
-        <v>0.99725672762159434</v>
+        <v>0.9940089461809174</v>
       </c>
       <c r="AB21">
-        <v>50.29332693743671</v>
+        <v>109.83598668318054</v>
       </c>
       <c r="AD21" t="s">
         <v>417</v>
@@ -10014,16 +10014,16 @@
         <v>644</v>
       </c>
       <c r="AM21" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN21" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="AO21">
-        <v>0.99592364356186902</v>
+        <v>0.99784941409648109</v>
       </c>
       <c r="AP21">
-        <v>74.733201365734146</v>
+        <v>39.427408231180806</v>
       </c>
       <c r="AR21" t="s">
         <v>417</v>
@@ -10050,16 +10050,16 @@
         <v>856</v>
       </c>
       <c r="BA21" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="BB21" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="BC21">
-        <v>0.98853599644984702</v>
+        <v>0.98742179529179352</v>
       </c>
       <c r="BD21">
-        <v>210.17339841947171</v>
+        <v>230.6004196504513</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10124,16 +10124,16 @@
         <v>442</v>
       </c>
       <c r="Y22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="Z22" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="AA22">
-        <v>0.99540885392130762</v>
+        <v>0.99600761890991041</v>
       </c>
       <c r="AB22">
-        <v>84.171011442693441</v>
+        <v>73.193653318309615</v>
       </c>
       <c r="AD22" t="s">
         <v>417</v>
@@ -10160,16 +10160,16 @@
         <v>646</v>
       </c>
       <c r="AM22" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AN22" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AO22">
-        <v>0.99641167752379312</v>
+        <v>0.99831921281104818</v>
       </c>
       <c r="AP22">
-        <v>65.785912063792665</v>
+        <v>30.814431797450247</v>
       </c>
       <c r="AR22" t="s">
         <v>417</v>
@@ -10196,16 +10196,16 @@
         <v>858</v>
       </c>
       <c r="BA22" t="s">
+        <v>895</v>
+      </c>
+      <c r="BB22" t="s">
         <v>896</v>
       </c>
-      <c r="BB22" t="s">
-        <v>897</v>
-      </c>
       <c r="BC22">
-        <v>0.98137594918937099</v>
+        <v>0.98158890816872557</v>
       </c>
       <c r="BD22">
-        <v>341.44093152819772</v>
+        <v>337.53668357336363</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10270,16 +10270,16 @@
         <v>444</v>
       </c>
       <c r="Y23" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z23" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AA23">
-        <v>0.99360802526828129</v>
+        <v>0.99700029739711071</v>
       </c>
       <c r="AB23">
-        <v>117.18620341484296</v>
+        <v>54.994547719637801</v>
       </c>
       <c r="AD23" t="s">
         <v>417</v>
@@ -10306,16 +10306,16 @@
         <v>648</v>
       </c>
       <c r="AM23" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AN23" t="s">
-        <v>622</v>
+        <v>599</v>
       </c>
       <c r="AO23">
-        <v>0.99611612132862803</v>
+        <v>0.99845356202909108</v>
       </c>
       <c r="AP23">
-        <v>71.204442308486065</v>
+        <v>28.351362799997673</v>
       </c>
       <c r="AR23" t="s">
         <v>417</v>
@@ -10342,16 +10342,16 @@
         <v>860</v>
       </c>
       <c r="BA23" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="BB23" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="BC23">
-        <v>0.9889956676941275</v>
+        <v>0.98402494782096717</v>
       </c>
       <c r="BD23">
-        <v>201.74609227432916</v>
+        <v>292.87595661560192</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10416,16 +10416,16 @@
         <v>446</v>
       </c>
       <c r="Y24" t="s">
-        <v>403</v>
+        <v>363</v>
       </c>
       <c r="Z24" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AA24">
-        <v>0.99515679011930902</v>
+        <v>0.99408511741207395</v>
       </c>
       <c r="AB24">
-        <v>88.792181146001369</v>
+        <v>108.43951411197776</v>
       </c>
       <c r="AD24" t="s">
         <v>417</v>
@@ -10452,16 +10452,16 @@
         <v>650</v>
       </c>
       <c r="AM24" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AN24" t="s">
-        <v>601</v>
+        <v>586</v>
       </c>
       <c r="AO24">
-        <v>0.99761105057437038</v>
+        <v>0.99533901157332205</v>
       </c>
       <c r="AP24">
-        <v>43.797406136543607</v>
+        <v>85.451454489096079</v>
       </c>
       <c r="AR24" t="s">
         <v>417</v>
@@ -10488,16 +10488,16 @@
         <v>862</v>
       </c>
       <c r="BA24" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="BB24" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="BC24">
-        <v>0.99193721244794397</v>
+        <v>0.99223982078870177</v>
       </c>
       <c r="BD24">
-        <v>147.81777178769397</v>
+        <v>142.26995220713331</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10562,16 +10562,16 @@
         <v>448</v>
       </c>
       <c r="Y25" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="Z25" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AA25">
-        <v>0.99409145347725225</v>
+        <v>0.99529948277209723</v>
       </c>
       <c r="AB25">
-        <v>108.32335291704148</v>
+        <v>86.176149178218239</v>
       </c>
       <c r="AD25" t="s">
         <v>417</v>
@@ -10598,16 +10598,16 @@
         <v>652</v>
       </c>
       <c r="AM25" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AN25" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="AO25">
-        <v>0.99615289372526561</v>
+        <v>0.99754339130519476</v>
       </c>
       <c r="AP25">
-        <v>70.530281703464368</v>
+        <v>45.037826071429087</v>
       </c>
       <c r="AR25" t="s">
         <v>417</v>
@@ -10634,16 +10634,16 @@
         <v>864</v>
       </c>
       <c r="BA25" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="BB25" t="s">
-        <v>901</v>
+        <v>585</v>
       </c>
       <c r="BC25">
-        <v>0.99308209783432144</v>
+        <v>0.98154438143849254</v>
       </c>
       <c r="BD25">
-        <v>126.82820637077275</v>
+        <v>338.35300696097039</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10708,16 +10708,16 @@
         <v>450</v>
       </c>
       <c r="Y26" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="Z26" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AA26">
-        <v>0.99464051280908794</v>
+        <v>0.99557960200072415</v>
       </c>
       <c r="AB26">
-        <v>98.257265166721183</v>
+        <v>81.040629986723459</v>
       </c>
       <c r="AD26" t="s">
         <v>417</v>
@@ -10744,16 +10744,16 @@
         <v>654</v>
       </c>
       <c r="AM26" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AN26" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="AO26">
-        <v>0.99368259233234391</v>
+        <v>0.99542398891280204</v>
       </c>
       <c r="AP26">
-        <v>115.81914057369519</v>
+        <v>83.893536598629126</v>
       </c>
       <c r="AR26" t="s">
         <v>417</v>
@@ -10780,16 +10780,16 @@
         <v>866</v>
       </c>
       <c r="BA26" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="BB26" t="s">
-        <v>798</v>
+        <v>584</v>
       </c>
       <c r="BC26">
-        <v>0.98389167860462323</v>
+        <v>0.98838558997012138</v>
       </c>
       <c r="BD26">
-        <v>295.31922558190735</v>
+        <v>212.93085054777492</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10854,16 +10854,16 @@
         <v>452</v>
       </c>
       <c r="Y27" t="s">
-        <v>350</v>
+        <v>401</v>
       </c>
       <c r="Z27" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AA27">
-        <v>0.99478609753984348</v>
+        <v>0.99295357769237991</v>
       </c>
       <c r="AB27">
-        <v>95.588211769535249</v>
+        <v>129.18440897303603</v>
       </c>
       <c r="AD27" t="s">
         <v>417</v>
@@ -10890,16 +10890,16 @@
         <v>656</v>
       </c>
       <c r="AM27" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AN27" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="AO27">
-        <v>0.9954443722844073</v>
+        <v>0.99617615910816915</v>
       </c>
       <c r="AP27">
-        <v>83.519841452532361</v>
+        <v>70.103749683564772</v>
       </c>
       <c r="AR27" t="s">
         <v>417</v>
@@ -10926,16 +10926,16 @@
         <v>868</v>
       </c>
       <c r="BA27" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="BB27" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="BC27">
-        <v>0.98734896749216872</v>
+        <v>0.98730637899749651</v>
       </c>
       <c r="BD27">
-        <v>231.9355959769062</v>
+        <v>232.71638504589731</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -11000,16 +11000,16 @@
         <v>454</v>
       </c>
       <c r="Y28" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="Z28" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="AA28">
-        <v>0.99568525132868968</v>
+        <v>0.99696751363483405</v>
       </c>
       <c r="AB28">
-        <v>79.10372564068922</v>
+        <v>55.595583361375894</v>
       </c>
       <c r="AD28" t="s">
         <v>417</v>
@@ -11036,16 +11036,16 @@
         <v>658</v>
       </c>
       <c r="AM28" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AN28" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="AO28">
-        <v>0.99363040616365128</v>
+        <v>0.99611612132862803</v>
       </c>
       <c r="AP28">
-        <v>116.77588699972566</v>
+        <v>71.204442308486065</v>
       </c>
       <c r="AR28" t="s">
         <v>417</v>
@@ -11072,16 +11072,16 @@
         <v>870</v>
       </c>
       <c r="BA28" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="BB28" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="BC28">
-        <v>0.99603877136023145</v>
+        <v>0.98809190602642238</v>
       </c>
       <c r="BD28">
-        <v>72.622525062424401</v>
+        <v>218.31505618225569</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11146,16 +11146,16 @@
         <v>456</v>
       </c>
       <c r="Y29" t="s">
-        <v>345</v>
+        <v>411</v>
       </c>
       <c r="Z29" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="AA29">
-        <v>0.99590266392783655</v>
+        <v>0.98964014500078279</v>
       </c>
       <c r="AB29">
-        <v>75.117827989662302</v>
+        <v>189.93067498564957</v>
       </c>
       <c r="AD29" t="s">
         <v>417</v>
@@ -11182,16 +11182,16 @@
         <v>660</v>
       </c>
       <c r="AM29" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AN29" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="AO29">
-        <v>0.99782402570187057</v>
+        <v>0.99761105057437038</v>
       </c>
       <c r="AP29">
-        <v>39.892862132373601</v>
+        <v>43.797406136543607</v>
       </c>
       <c r="AR29" t="s">
         <v>417</v>
@@ -11218,16 +11218,16 @@
         <v>872</v>
       </c>
       <c r="BA29" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="BB29" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="BC29">
-        <v>0.99526782804010661</v>
+        <v>0.994208528887633</v>
       </c>
       <c r="BD29">
-        <v>86.756485931379871</v>
+        <v>106.17697039339514</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11292,16 +11292,16 @@
         <v>458</v>
       </c>
       <c r="Y30" t="s">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="Z30" t="s">
         <v>594</v>
       </c>
       <c r="AA30">
-        <v>0.99449671322390631</v>
+        <v>0.9966137462997855</v>
       </c>
       <c r="AB30">
-        <v>100.89359089505045</v>
+        <v>62.081317837266766</v>
       </c>
       <c r="AD30" t="s">
         <v>417</v>
@@ -11328,16 +11328,16 @@
         <v>662</v>
       </c>
       <c r="AM30" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AN30" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="AO30">
-        <v>0.99756462867082185</v>
+        <v>0.99615289372526561</v>
       </c>
       <c r="AP30">
-        <v>44.648474368267038</v>
+        <v>70.530281703464368</v>
       </c>
       <c r="AR30" t="s">
         <v>417</v>
@@ -11364,16 +11364,16 @@
         <v>874</v>
       </c>
       <c r="BA30" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="BB30" t="s">
-        <v>618</v>
+        <v>812</v>
       </c>
       <c r="BC30">
-        <v>0.98605138538291048</v>
+        <v>0.98389167860462323</v>
       </c>
       <c r="BD30">
-        <v>255.7246013133088</v>
+        <v>295.31922558190735</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11438,16 +11438,16 @@
         <v>460</v>
       </c>
       <c r="Y31" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="Z31" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AA31">
-        <v>0.99701127670202949</v>
+        <v>0.99011796851295664</v>
       </c>
       <c r="AB31">
-        <v>54.793260462791778</v>
+        <v>181.17057726246117</v>
       </c>
       <c r="AD31" t="s">
         <v>417</v>
@@ -11474,10 +11474,10 @@
         <v>664</v>
       </c>
       <c r="AM31" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AN31" t="s">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="AO31">
         <v>0.99418244113372889</v>
@@ -11510,16 +11510,16 @@
         <v>876</v>
       </c>
       <c r="BA31" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="BB31" t="s">
-        <v>604</v>
+        <v>906</v>
       </c>
       <c r="BC31">
-        <v>0.98838558997012138</v>
+        <v>0.98137594918937099</v>
       </c>
       <c r="BD31">
-        <v>212.93085054777492</v>
+        <v>341.44093152819772</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11584,16 +11584,16 @@
         <v>462</v>
       </c>
       <c r="Y32" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="Z32" t="s">
         <v>595</v>
       </c>
       <c r="AA32">
-        <v>0.99080344458411729</v>
+        <v>0.99635118654529808</v>
       </c>
       <c r="AB32">
-        <v>168.60351595784994</v>
+        <v>66.894913336202478</v>
       </c>
       <c r="AD32" t="s">
         <v>417</v>
@@ -11620,10 +11620,10 @@
         <v>666</v>
       </c>
       <c r="AM32" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AN32" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AO32">
         <v>0.99206751173516827</v>
@@ -11656,16 +11656,16 @@
         <v>878</v>
       </c>
       <c r="BA32" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="BB32" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="BC32">
-        <v>0.98730637899749651</v>
+        <v>0.9889956676941275</v>
       </c>
       <c r="BD32">
-        <v>232.71638504589731</v>
+        <v>201.74609227432916</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11730,16 +11730,16 @@
         <v>464</v>
       </c>
       <c r="Y33" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="Z33" t="s">
         <v>596</v>
       </c>
       <c r="AA33">
-        <v>0.98636012609964985</v>
+        <v>0.99440507690252466</v>
       </c>
       <c r="AB33">
-        <v>250.06435483975247</v>
+        <v>102.57359012038077</v>
       </c>
       <c r="AD33" t="s">
         <v>417</v>
@@ -11766,10 +11766,10 @@
         <v>668</v>
       </c>
       <c r="AM33" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AN33" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AO33">
         <v>0.99566554346996428</v>
@@ -11802,16 +11802,16 @@
         <v>880</v>
       </c>
       <c r="BA33" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="BB33" t="s">
-        <v>621</v>
+        <v>588</v>
       </c>
       <c r="BC33">
-        <v>0.98809190602642238</v>
+        <v>0.99193721244794397</v>
       </c>
       <c r="BD33">
-        <v>218.31505618225569</v>
+        <v>147.81777178769397</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11876,16 +11876,16 @@
         <v>466</v>
       </c>
       <c r="Y34" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="Z34" t="s">
         <v>597</v>
       </c>
       <c r="AA34">
-        <v>0.99598850450039844</v>
+        <v>0.99551989204648861</v>
       </c>
       <c r="AB34">
-        <v>73.544084159361034</v>
+        <v>82.135312481041623</v>
       </c>
       <c r="AD34" t="s">
         <v>417</v>
@@ -11912,10 +11912,10 @@
         <v>670</v>
       </c>
       <c r="AM34" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AN34" t="s">
-        <v>609</v>
+        <v>590</v>
       </c>
       <c r="AO34">
         <v>0.99667664296701652</v>
@@ -11948,16 +11948,16 @@
         <v>882</v>
       </c>
       <c r="BA34" t="s">
+        <v>909</v>
+      </c>
+      <c r="BB34" t="s">
         <v>910</v>
       </c>
-      <c r="BB34" t="s">
-        <v>582</v>
-      </c>
       <c r="BC34">
-        <v>0.994208528887633</v>
+        <v>0.99308209783432144</v>
       </c>
       <c r="BD34">
-        <v>106.17697039339514</v>
+        <v>126.82820637077275</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -12022,16 +12022,16 @@
         <v>468</v>
       </c>
       <c r="Y35" t="s">
-        <v>412</v>
+        <v>359</v>
       </c>
       <c r="Z35" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="AA35">
-        <v>0.99310312827752323</v>
+        <v>0.9979392050107273</v>
       </c>
       <c r="AB35">
-        <v>126.44264824540761</v>
+        <v>37.781241469999252</v>
       </c>
       <c r="AD35" t="s">
         <v>417</v>
@@ -12058,10 +12058,10 @@
         <v>672</v>
       </c>
       <c r="AM35" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AN35" t="s">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="AO35">
         <v>0.99608442334318104</v>
@@ -12132,16 +12132,16 @@
         <v>470</v>
       </c>
       <c r="Y36" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="Z36" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AA36">
-        <v>0.99578350963230966</v>
+        <v>0.9982033297630386</v>
       </c>
       <c r="AB36">
-        <v>77.302323407656075</v>
+        <v>32.938954344292306</v>
       </c>
       <c r="AD36" t="s">
         <v>417</v>
@@ -12168,10 +12168,10 @@
         <v>674</v>
       </c>
       <c r="AM36" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AN36" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="AO36">
         <v>0.9967907157363165</v>
@@ -12242,16 +12242,16 @@
         <v>472</v>
       </c>
       <c r="Y37" t="s">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="Z37" t="s">
-        <v>578</v>
+        <v>600</v>
       </c>
       <c r="AA37">
-        <v>0.99720191150310689</v>
+        <v>0.99769372286934066</v>
       </c>
       <c r="AB37">
-        <v>51.298289109706943</v>
+        <v>42.281747395421668</v>
       </c>
       <c r="AD37" t="s">
         <v>417</v>
@@ -12278,10 +12278,10 @@
         <v>676</v>
       </c>
       <c r="AM37" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AN37" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AO37">
         <v>0.99443964677468366</v>
@@ -12352,16 +12352,16 @@
         <v>474</v>
       </c>
       <c r="Y38" t="s">
-        <v>404</v>
+        <v>352</v>
       </c>
       <c r="Z38" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AA38">
-        <v>0.9954551465796494</v>
+        <v>0.99569491323214321</v>
       </c>
       <c r="AB38">
-        <v>83.32231270642734</v>
+        <v>78.926590744041093</v>
       </c>
       <c r="AD38" t="s">
         <v>417</v>
@@ -12388,10 +12388,10 @@
         <v>678</v>
       </c>
       <c r="AM38" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AN38" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="AO38">
         <v>0.99761003390352465</v>
@@ -12462,16 +12462,16 @@
         <v>476</v>
       </c>
       <c r="Y39" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="Z39" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="AA39">
-        <v>0.99552053983611355</v>
+        <v>0.99484118006716937</v>
       </c>
       <c r="AB39">
-        <v>82.123436337918946</v>
+        <v>94.578365435227795</v>
       </c>
       <c r="AD39" t="s">
         <v>417</v>
@@ -12498,10 +12498,10 @@
         <v>680</v>
       </c>
       <c r="AM39" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AN39" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="AO39">
         <v>0.99777413567568085</v>
@@ -12572,16 +12572,16 @@
         <v>478</v>
       </c>
       <c r="Y40" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="Z40" t="s">
         <v>600</v>
       </c>
       <c r="AA40">
-        <v>0.98935435476104872</v>
+        <v>0.99539558382203508</v>
       </c>
       <c r="AB40">
-        <v>195.1701627141077</v>
+        <v>84.414296596023817</v>
       </c>
       <c r="AD40" t="s">
         <v>417</v>
@@ -12608,16 +12608,16 @@
         <v>682</v>
       </c>
       <c r="AM40" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AN40" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="AO40">
-        <v>0.99425851119451991</v>
+        <v>0.99568571110966864</v>
       </c>
       <c r="AP40">
-        <v>105.26062810046888</v>
+        <v>79.095296322741547</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12682,16 +12682,16 @@
         <v>480</v>
       </c>
       <c r="Y41" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Z41" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AA41">
-        <v>0.99775872574768198</v>
+        <v>0.99282834435956602</v>
       </c>
       <c r="AB41">
-        <v>41.090027959164246</v>
+        <v>131.48035340795542</v>
       </c>
       <c r="AD41" t="s">
         <v>417</v>
@@ -12718,16 +12718,16 @@
         <v>684</v>
       </c>
       <c r="AM41" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AN41" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="AO41">
-        <v>0.99712282780353001</v>
+        <v>0.99609062270337045</v>
       </c>
       <c r="AP41">
-        <v>52.74815693528295</v>
+        <v>71.671917104874566</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12792,16 +12792,16 @@
         <v>482</v>
       </c>
       <c r="Y42" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="Z42" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AA42">
-        <v>0.99462937148232844</v>
+        <v>0.99569310304523451</v>
       </c>
       <c r="AB42">
-        <v>98.461522823979266</v>
+        <v>78.959777504033639</v>
       </c>
       <c r="AD42" t="s">
         <v>417</v>
@@ -12828,16 +12828,16 @@
         <v>686</v>
       </c>
       <c r="AM42" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AN42" t="s">
-        <v>600</v>
+        <v>796</v>
       </c>
       <c r="AO42">
-        <v>0.99005506097810436</v>
+        <v>0.99598588086244633</v>
       </c>
       <c r="AP42">
-        <v>182.32388206808599</v>
+        <v>73.592184188484865</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12902,16 +12902,16 @@
         <v>484</v>
       </c>
       <c r="Y43" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="Z43" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="AA43">
-        <v>0.99462643269733408</v>
+        <v>0.99502431999137919</v>
       </c>
       <c r="AB43">
-        <v>98.51540054887441</v>
+        <v>91.220800158047325</v>
       </c>
       <c r="AD43" t="s">
         <v>417</v>
@@ -12938,16 +12938,16 @@
         <v>688</v>
       </c>
       <c r="AM43" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AN43" t="s">
-        <v>614</v>
+        <v>578</v>
       </c>
       <c r="AO43">
-        <v>0.99631269816920021</v>
+        <v>0.99368259233234391</v>
       </c>
       <c r="AP43">
-        <v>67.600533564663479</v>
+        <v>115.81914057369519</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -13012,16 +13012,16 @@
         <v>486</v>
       </c>
       <c r="Y44" t="s">
-        <v>365</v>
+        <v>405</v>
       </c>
       <c r="Z44" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="AA44">
-        <v>0.99755789282691543</v>
+        <v>0.99584577617815018</v>
       </c>
       <c r="AB44">
-        <v>44.77196483988353</v>
+        <v>76.16077006724673</v>
       </c>
       <c r="AD44" t="s">
         <v>417</v>
@@ -13048,16 +13048,16 @@
         <v>690</v>
       </c>
       <c r="AM44" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="AN44" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="AO44">
-        <v>0.99772400077475298</v>
+        <v>0.9954443722844073</v>
       </c>
       <c r="AP44">
-        <v>41.726652462862774</v>
+        <v>83.519841452532361</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13122,16 +13122,16 @@
         <v>488</v>
       </c>
       <c r="Y45" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="Z45" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="AA45">
-        <v>0.99246356041150996</v>
+        <v>0.99699505644961572</v>
       </c>
       <c r="AB45">
-        <v>138.16805912231732</v>
+        <v>55.090631757044932</v>
       </c>
       <c r="AD45" t="s">
         <v>417</v>
@@ -13158,16 +13158,16 @@
         <v>692</v>
       </c>
       <c r="AM45" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="AN45" t="s">
-        <v>798</v>
+        <v>623</v>
       </c>
       <c r="AO45">
-        <v>0.99604673274056554</v>
+        <v>0.99363040616365128</v>
       </c>
       <c r="AP45">
-        <v>72.476566422965192</v>
+        <v>116.77588699972566</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13232,16 +13232,16 @@
         <v>490</v>
       </c>
       <c r="Y46" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="Z46" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="AA46">
-        <v>0.99579357955795456</v>
+        <v>0.99170691261633115</v>
       </c>
       <c r="AB46">
-        <v>77.117708104165573</v>
+        <v>152.03993536726261</v>
       </c>
       <c r="AD46" t="s">
         <v>417</v>
@@ -13268,16 +13268,16 @@
         <v>694</v>
       </c>
       <c r="AM46" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AN46" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="AO46">
-        <v>0.99720397512579328</v>
+        <v>0.99782402570187057</v>
       </c>
       <c r="AP46">
-        <v>51.260456027123361</v>
+        <v>39.892862132373601</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13342,16 +13342,16 @@
         <v>492</v>
       </c>
       <c r="Y47" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="Z47" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="AA47">
-        <v>0.99066346416517681</v>
+        <v>0.9904035062850528</v>
       </c>
       <c r="AB47">
-        <v>171.16982363842584</v>
+        <v>175.93571810736526</v>
       </c>
       <c r="AD47" t="s">
         <v>417</v>
@@ -13378,16 +13378,16 @@
         <v>696</v>
       </c>
       <c r="AM47" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AN47" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="AO47">
-        <v>0.99565348329230585</v>
+        <v>0.99756462867082185</v>
       </c>
       <c r="AP47">
-        <v>79.686139641060379</v>
+        <v>44.648474368267038</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13452,16 +13452,16 @@
         <v>494</v>
       </c>
       <c r="Y48" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="Z48" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AA48">
-        <v>0.99560939477262078</v>
+        <v>0.99125780375299366</v>
       </c>
       <c r="AB48">
-        <v>80.494429168619106</v>
+        <v>160.27359786178269</v>
       </c>
       <c r="AD48" t="s">
         <v>417</v>
@@ -13488,16 +13488,16 @@
         <v>698</v>
       </c>
       <c r="AM48" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AN48" t="s">
-        <v>616</v>
+        <v>803</v>
       </c>
       <c r="AO48">
-        <v>0.99568571110966864</v>
+        <v>0.99474825047892679</v>
       </c>
       <c r="AP48">
-        <v>79.095296322741547</v>
+        <v>96.282074553009053</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13562,16 +13562,16 @@
         <v>496</v>
       </c>
       <c r="Y49" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="Z49" t="s">
         <v>606</v>
       </c>
       <c r="AA49">
-        <v>0.99544039231362502</v>
+        <v>0.99619006668481902</v>
       </c>
       <c r="AB49">
-        <v>83.592807583541571</v>
+        <v>69.848777444984194</v>
       </c>
       <c r="AD49" t="s">
         <v>417</v>
@@ -13598,16 +13598,16 @@
         <v>700</v>
       </c>
       <c r="AM49" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AN49" t="s">
-        <v>608</v>
+        <v>805</v>
       </c>
       <c r="AO49">
-        <v>0.99609062270337045</v>
+        <v>0.99684527597966854</v>
       </c>
       <c r="AP49">
-        <v>71.671917104874566</v>
+        <v>57.836607039410005</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13672,16 +13672,16 @@
         <v>498</v>
       </c>
       <c r="Y50" t="s">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="Z50" t="s">
         <v>607</v>
       </c>
       <c r="AA50">
-        <v>0.99190124970484694</v>
+        <v>0.99021813732178554</v>
       </c>
       <c r="AB50">
-        <v>148.47708874447352</v>
+        <v>179.3341491005981</v>
       </c>
       <c r="AD50" t="s">
         <v>417</v>
@@ -13708,16 +13708,16 @@
         <v>702</v>
       </c>
       <c r="AM50" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="AN50" t="s">
-        <v>804</v>
+        <v>581</v>
       </c>
       <c r="AO50">
-        <v>0.99598588086244633</v>
+        <v>0.9943927545810437</v>
       </c>
       <c r="AP50">
-        <v>73.592184188484865</v>
+        <v>102.79949934753229</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13782,16 +13782,16 @@
         <v>500</v>
       </c>
       <c r="Y51" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
       <c r="Z51" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="AA51">
-        <v>0.9940089461809174</v>
+        <v>0.99686736582623381</v>
       </c>
       <c r="AB51">
-        <v>109.83598668318054</v>
+        <v>57.431626519047455</v>
       </c>
       <c r="AD51" t="s">
         <v>417</v>
@@ -13818,16 +13818,16 @@
         <v>704</v>
       </c>
       <c r="AM51" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="AN51" t="s">
-        <v>759</v>
+        <v>808</v>
       </c>
       <c r="AO51">
-        <v>0.99540934349034305</v>
+        <v>0.99074948308423383</v>
       </c>
       <c r="AP51">
-        <v>84.162036010377406</v>
+        <v>169.59281012238051</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13892,16 +13892,16 @@
         <v>502</v>
       </c>
       <c r="Y52" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="Z52" t="s">
         <v>608</v>
       </c>
       <c r="AA52">
-        <v>0.99600761890991041</v>
+        <v>0.99725672762159434</v>
       </c>
       <c r="AB52">
-        <v>73.193653318309615</v>
+        <v>50.29332693743671</v>
       </c>
       <c r="AD52" t="s">
         <v>417</v>
@@ -13928,16 +13928,16 @@
         <v>706</v>
       </c>
       <c r="AM52" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="AN52" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="AO52">
-        <v>0.99657664224037934</v>
+        <v>0.99270401267208797</v>
       </c>
       <c r="AP52">
-        <v>62.761558926379031</v>
+        <v>133.75976767838793</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -14002,16 +14002,16 @@
         <v>504</v>
       </c>
       <c r="Y53" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="Z53" t="s">
         <v>609</v>
       </c>
       <c r="AA53">
-        <v>0.99700029739711071</v>
+        <v>0.99478609753984348</v>
       </c>
       <c r="AB53">
-        <v>54.994547719637801</v>
+        <v>95.588211769535249</v>
       </c>
       <c r="AD53" t="s">
         <v>417</v>
@@ -14038,16 +14038,16 @@
         <v>708</v>
       </c>
       <c r="AM53" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="AN53" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="AO53">
-        <v>0.99091245964276031</v>
+        <v>0.99764772442226368</v>
       </c>
       <c r="AP53">
-        <v>166.60490654939525</v>
+        <v>43.125052258499352</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -14112,16 +14112,16 @@
         <v>506</v>
       </c>
       <c r="Y54" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="Z54" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="AA54">
-        <v>0.99408511741207395</v>
+        <v>0.99568525132868968</v>
       </c>
       <c r="AB54">
-        <v>108.43951411197776</v>
+        <v>79.10372564068922</v>
       </c>
       <c r="AD54" t="s">
         <v>417</v>
@@ -14148,16 +14148,16 @@
         <v>710</v>
       </c>
       <c r="AM54" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="AN54" t="s">
-        <v>601</v>
+        <v>812</v>
       </c>
       <c r="AO54">
-        <v>0.99846230399777702</v>
+        <v>0.99703044337128366</v>
       </c>
       <c r="AP54">
-        <v>28.191093374087806</v>
+        <v>54.441871526466279</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -14222,16 +14222,16 @@
         <v>508</v>
       </c>
       <c r="Y55" t="s">
-        <v>381</v>
+        <v>345</v>
       </c>
       <c r="Z55" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="AA55">
-        <v>0.99529948277209723</v>
+        <v>0.99590266392783655</v>
       </c>
       <c r="AB55">
-        <v>86.176149178218239</v>
+        <v>75.117827989662302</v>
       </c>
       <c r="AD55" t="s">
         <v>417</v>
@@ -14258,16 +14258,16 @@
         <v>712</v>
       </c>
       <c r="AM55" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="AN55" t="s">
-        <v>604</v>
+        <v>767</v>
       </c>
       <c r="AO55">
-        <v>0.99660391553167893</v>
+        <v>0.99584476105827657</v>
       </c>
       <c r="AP55">
-        <v>62.261548585886977</v>
+        <v>76.179380598263194</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14332,16 +14332,16 @@
         <v>510</v>
       </c>
       <c r="Y56" t="s">
-        <v>407</v>
+        <v>360</v>
       </c>
       <c r="Z56" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AA56">
-        <v>0.99675394464629852</v>
+        <v>0.99449671322390631</v>
       </c>
       <c r="AB56">
-        <v>59.511014817860868</v>
+        <v>100.89359089505045</v>
       </c>
       <c r="AD56" t="s">
         <v>417</v>
@@ -14368,16 +14368,16 @@
         <v>714</v>
       </c>
       <c r="AM56" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="AN56" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="AO56">
-        <v>0.9959136876641268</v>
+        <v>0.9961146125371938</v>
       </c>
       <c r="AP56">
-        <v>74.915726157675209</v>
+        <v>71.232103484781334</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14442,16 +14442,16 @@
         <v>512</v>
       </c>
       <c r="Y57" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Z57" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="AA57">
-        <v>0.9962437778559039</v>
+        <v>0.99701127670202949</v>
       </c>
       <c r="AB57">
-        <v>68.86407264176249</v>
+        <v>54.793260462791778</v>
       </c>
       <c r="AD57" t="s">
         <v>417</v>
@@ -14478,16 +14478,16 @@
         <v>716</v>
       </c>
       <c r="AM57" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="AN57" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="AO57">
-        <v>0.9935275292913992</v>
+        <v>0.99607298561021362</v>
       </c>
       <c r="AP57">
-        <v>118.66196299101547</v>
+        <v>71.995263812749926</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14552,16 +14552,16 @@
         <v>514</v>
       </c>
       <c r="Y58" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="Z58" t="s">
-        <v>580</v>
+        <v>612</v>
       </c>
       <c r="AA58">
-        <v>0.99617006411660358</v>
+        <v>0.99675394464629852</v>
       </c>
       <c r="AB58">
-        <v>70.215491195600634</v>
+        <v>59.511014817860868</v>
       </c>
       <c r="AD58" t="s">
         <v>417</v>
@@ -14588,16 +14588,16 @@
         <v>718</v>
       </c>
       <c r="AM58" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="AN58" t="s">
-        <v>580</v>
+        <v>615</v>
       </c>
       <c r="AO58">
-        <v>0.99687120387267125</v>
+        <v>0.9929182563937401</v>
       </c>
       <c r="AP58">
-        <v>57.361262334360205</v>
+        <v>129.83196611476453</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14662,16 +14662,16 @@
         <v>516</v>
       </c>
       <c r="Y59" t="s">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="Z59" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AA59">
-        <v>0.99557960200072415</v>
+        <v>0.9962437778559039</v>
       </c>
       <c r="AB59">
-        <v>81.040629986723459</v>
+        <v>68.86407264176249</v>
       </c>
       <c r="AD59" t="s">
         <v>417</v>
@@ -14698,16 +14698,16 @@
         <v>720</v>
       </c>
       <c r="AM59" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="AN59" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="AO59">
-        <v>0.99245794727704639</v>
+        <v>0.99628542339510884</v>
       </c>
       <c r="AP59">
-        <v>138.27096658748206</v>
+        <v>68.100571089671959</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14772,16 +14772,16 @@
         <v>518</v>
       </c>
       <c r="Y60" t="s">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="Z60" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="AA60">
-        <v>0.99295357769237991</v>
+        <v>0.99617006411660358</v>
       </c>
       <c r="AB60">
-        <v>129.18440897303603</v>
+        <v>70.215491195600634</v>
       </c>
       <c r="AD60" t="s">
         <v>417</v>
@@ -14808,16 +14808,16 @@
         <v>722</v>
       </c>
       <c r="AM60" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="AN60" t="s">
-        <v>782</v>
+        <v>584</v>
       </c>
       <c r="AO60">
-        <v>0.99381230463557813</v>
+        <v>0.99660391553167893</v>
       </c>
       <c r="AP60">
-        <v>113.44108168106689</v>
+        <v>62.261548585886977</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14882,16 +14882,16 @@
         <v>520</v>
       </c>
       <c r="Y61" t="s">
-        <v>358</v>
+        <v>406</v>
       </c>
       <c r="Z61" t="s">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="AA61">
-        <v>0.99696751363483405</v>
+        <v>0.99670408962762203</v>
       </c>
       <c r="AB61">
-        <v>55.595583361375894</v>
+        <v>60.425023493595695</v>
       </c>
       <c r="AD61" t="s">
         <v>417</v>
@@ -14918,16 +14918,16 @@
         <v>724</v>
       </c>
       <c r="AM61" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="AN61" t="s">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="AO61">
-        <v>0.99534539864304916</v>
+        <v>0.9959136876641268</v>
       </c>
       <c r="AP61">
-        <v>85.3343582107656</v>
+        <v>74.915726157675209</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14992,16 +14992,16 @@
         <v>522</v>
       </c>
       <c r="Y62" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="Z62" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="AA62">
-        <v>0.98964014500078279</v>
+        <v>0.9960389195261472</v>
       </c>
       <c r="AB62">
-        <v>189.93067498564957</v>
+        <v>72.619808687301173</v>
       </c>
       <c r="AD62" t="s">
         <v>417</v>
@@ -15028,16 +15028,16 @@
         <v>726</v>
       </c>
       <c r="AM62" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="AN62" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="AO62">
-        <v>0.99310873310996184</v>
+        <v>0.9935275292913992</v>
       </c>
       <c r="AP62">
-        <v>126.33989298403215</v>
+        <v>118.66196299101547</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -15102,16 +15102,16 @@
         <v>524</v>
       </c>
       <c r="Y63" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="Z63" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="AA63">
-        <v>0.9966137462997855</v>
+        <v>0.99707957985864093</v>
       </c>
       <c r="AB63">
-        <v>62.081317837266766</v>
+        <v>53.541035924916123</v>
       </c>
       <c r="AD63" t="s">
         <v>417</v>
@@ -15138,16 +15138,16 @@
         <v>728</v>
       </c>
       <c r="AM63" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="AN63" t="s">
-        <v>578</v>
+        <v>600</v>
       </c>
       <c r="AO63">
-        <v>0.99715437961127318</v>
+        <v>0.99687120387267125</v>
       </c>
       <c r="AP63">
-        <v>52.169707126657627</v>
+        <v>57.361262334360205</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -15212,16 +15212,16 @@
         <v>526</v>
       </c>
       <c r="Y64" t="s">
-        <v>387</v>
+        <v>339</v>
       </c>
       <c r="Z64" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="AA64">
-        <v>0.99011796851295664</v>
+        <v>0.99359748433922845</v>
       </c>
       <c r="AB64">
-        <v>181.17057726246117</v>
+        <v>117.37945378081078</v>
       </c>
       <c r="AD64" t="s">
         <v>417</v>
@@ -15248,16 +15248,16 @@
         <v>730</v>
       </c>
       <c r="AM64" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="AN64" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="AO64">
-        <v>0.9950502580620818</v>
+        <v>0.99245794727704639</v>
       </c>
       <c r="AP64">
-        <v>90.745268861833736</v>
+        <v>138.27096658748206</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -15322,16 +15322,16 @@
         <v>528</v>
       </c>
       <c r="Y65" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="Z65" t="s">
-        <v>614</v>
+        <v>588</v>
       </c>
       <c r="AA65">
-        <v>0.99635118654529808</v>
+        <v>0.99592552983543692</v>
       </c>
       <c r="AB65">
-        <v>66.894913336202478</v>
+        <v>74.698619683656872</v>
       </c>
       <c r="AD65" t="s">
         <v>417</v>
@@ -15358,16 +15358,16 @@
         <v>732</v>
       </c>
       <c r="AM65" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="AN65" t="s">
-        <v>820</v>
+        <v>783</v>
       </c>
       <c r="AO65">
-        <v>0.99074948308423383</v>
+        <v>0.99381230463557813</v>
       </c>
       <c r="AP65">
-        <v>169.59281012238051</v>
+        <v>113.44108168106689</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15432,16 +15432,16 @@
         <v>530</v>
       </c>
       <c r="Y66" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="Z66" t="s">
         <v>615</v>
       </c>
       <c r="AA66">
-        <v>0.99440507690252466</v>
+        <v>0.99463677905825021</v>
       </c>
       <c r="AB66">
-        <v>102.57359012038077</v>
+        <v>98.325717265413417</v>
       </c>
       <c r="AD66" t="s">
         <v>417</v>
@@ -15468,16 +15468,16 @@
         <v>734</v>
       </c>
       <c r="AM66" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="AN66" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="AO66">
-        <v>0.99270401267208797</v>
+        <v>0.99534539864304916</v>
       </c>
       <c r="AP66">
-        <v>133.75976767838793</v>
+        <v>85.3343582107656</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15542,16 +15542,16 @@
         <v>532</v>
       </c>
       <c r="Y67" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="Z67" t="s">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="AA67">
-        <v>0.99551989204648861</v>
+        <v>0.99667564038633161</v>
       </c>
       <c r="AB67">
-        <v>82.135312481041623</v>
+        <v>60.946592917253042</v>
       </c>
       <c r="AD67" t="s">
         <v>417</v>
@@ -15578,16 +15578,16 @@
         <v>736</v>
       </c>
       <c r="AM67" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="AN67" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="AO67">
-        <v>0.99764772442226368</v>
+        <v>0.99310873310996184</v>
       </c>
       <c r="AP67">
-        <v>43.125052258499352</v>
+        <v>126.33989298403215</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15652,16 +15652,16 @@
         <v>534</v>
       </c>
       <c r="Y68" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="Z68" t="s">
-        <v>594</v>
+        <v>616</v>
       </c>
       <c r="AA68">
-        <v>0.9979392050107273</v>
+        <v>0.99080344458411729</v>
       </c>
       <c r="AB68">
-        <v>37.781241469999252</v>
+        <v>168.60351595784994</v>
       </c>
       <c r="AD68" t="s">
         <v>417</v>
@@ -15688,16 +15688,16 @@
         <v>738</v>
       </c>
       <c r="AM68" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="AN68" t="s">
-        <v>798</v>
+        <v>588</v>
       </c>
       <c r="AO68">
-        <v>0.99703044337128366</v>
+        <v>0.99715437961127318</v>
       </c>
       <c r="AP68">
-        <v>54.441871526466279</v>
+        <v>52.169707126657627</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -15762,16 +15762,16 @@
         <v>536</v>
       </c>
       <c r="Y69" t="s">
-        <v>357</v>
+        <v>413</v>
       </c>
       <c r="Z69" t="s">
-        <v>579</v>
+        <v>617</v>
       </c>
       <c r="AA69">
-        <v>0.9982033297630386</v>
+        <v>0.98636012609964985</v>
       </c>
       <c r="AB69">
-        <v>32.938954344292306</v>
+        <v>250.06435483975247</v>
       </c>
       <c r="AD69" t="s">
         <v>417</v>
@@ -15798,16 +15798,16 @@
         <v>740</v>
       </c>
       <c r="AM69" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="AN69" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="AO69">
-        <v>0.99784941409648109</v>
+        <v>0.9950502580620818</v>
       </c>
       <c r="AP69">
-        <v>39.427408231180806</v>
+        <v>90.745268861833736</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -15872,16 +15872,16 @@
         <v>538</v>
       </c>
       <c r="Y70" t="s">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="Z70" t="s">
-        <v>580</v>
+        <v>618</v>
       </c>
       <c r="AA70">
-        <v>0.99769372286934066</v>
+        <v>0.99598850450039844</v>
       </c>
       <c r="AB70">
-        <v>42.281747395421668</v>
+        <v>73.544084159361034</v>
       </c>
       <c r="AD70" t="s">
         <v>417</v>
@@ -15908,16 +15908,16 @@
         <v>742</v>
       </c>
       <c r="AM70" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="AN70" t="s">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="AO70">
-        <v>0.99831921281104818</v>
+        <v>0.99425851119451991</v>
       </c>
       <c r="AP70">
-        <v>30.814431797450247</v>
+        <v>105.26062810046888</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -15982,16 +15982,16 @@
         <v>540</v>
       </c>
       <c r="Y71" t="s">
-        <v>339</v>
+        <v>412</v>
       </c>
       <c r="Z71" t="s">
-        <v>617</v>
+        <v>588</v>
       </c>
       <c r="AA71">
-        <v>0.99359748433922845</v>
+        <v>0.99310312827752323</v>
       </c>
       <c r="AB71">
-        <v>117.37945378081078</v>
+        <v>126.44264824540761</v>
       </c>
       <c r="AD71" t="s">
         <v>417</v>
@@ -16018,16 +16018,16 @@
         <v>744</v>
       </c>
       <c r="AM71" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="AN71" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="AO71">
-        <v>0.99845356202909108</v>
+        <v>0.99712282780353001</v>
       </c>
       <c r="AP71">
-        <v>28.351362799997673</v>
+        <v>52.74815693528295</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -16092,16 +16092,16 @@
         <v>542</v>
       </c>
       <c r="Y72" t="s">
-        <v>409</v>
+        <v>353</v>
       </c>
       <c r="Z72" t="s">
-        <v>578</v>
+        <v>619</v>
       </c>
       <c r="AA72">
-        <v>0.99592552983543692</v>
+        <v>0.99462937148232844</v>
       </c>
       <c r="AB72">
-        <v>74.698619683656872</v>
+        <v>98.461522823979266</v>
       </c>
       <c r="AD72" t="s">
         <v>417</v>
@@ -16128,16 +16128,16 @@
         <v>746</v>
       </c>
       <c r="AM72" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="AN72" t="s">
-        <v>828</v>
+        <v>621</v>
       </c>
       <c r="AO72">
-        <v>0.99474825047892679</v>
+        <v>0.99005506097810436</v>
       </c>
       <c r="AP72">
-        <v>96.282074553009053</v>
+        <v>182.32388206808599</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16202,16 +16202,16 @@
         <v>544</v>
       </c>
       <c r="Y73" t="s">
-        <v>369</v>
+        <v>408</v>
       </c>
       <c r="Z73" t="s">
-        <v>618</v>
+        <v>588</v>
       </c>
       <c r="AA73">
-        <v>0.99463677905825021</v>
+        <v>0.99462643269733408</v>
       </c>
       <c r="AB73">
-        <v>98.325717265413417</v>
+        <v>98.51540054887441</v>
       </c>
       <c r="AD73" t="s">
         <v>417</v>
@@ -16238,16 +16238,16 @@
         <v>748</v>
       </c>
       <c r="AM73" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="AN73" t="s">
-        <v>830</v>
+        <v>595</v>
       </c>
       <c r="AO73">
-        <v>0.99684527597966854</v>
+        <v>0.99631269816920021</v>
       </c>
       <c r="AP73">
-        <v>57.836607039410005</v>
+        <v>67.600533564663479</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -16312,16 +16312,16 @@
         <v>546</v>
       </c>
       <c r="Y74" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="Z74" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="AA74">
-        <v>0.99667564038633161</v>
+        <v>0.99755789282691543</v>
       </c>
       <c r="AB74">
-        <v>60.946592917253042</v>
+        <v>44.77196483988353</v>
       </c>
       <c r="AD74" t="s">
         <v>417</v>
@@ -16348,16 +16348,16 @@
         <v>750</v>
       </c>
       <c r="AM74" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AN74" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AO74">
-        <v>0.9943927545810437</v>
+        <v>0.99772400077475298</v>
       </c>
       <c r="AP74">
-        <v>102.79949934753229</v>
+        <v>41.726652462862774</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -16422,16 +16422,16 @@
         <v>548</v>
       </c>
       <c r="Y75" t="s">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="Z75" t="s">
-        <v>619</v>
+        <v>600</v>
       </c>
       <c r="AA75">
-        <v>0.99571525957109708</v>
+        <v>0.99246356041150996</v>
       </c>
       <c r="AB75">
-        <v>78.553574529886689</v>
+        <v>138.16805912231732</v>
       </c>
       <c r="AD75" t="s">
         <v>417</v>
@@ -16458,16 +16458,16 @@
         <v>752</v>
       </c>
       <c r="AM75" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AN75" t="s">
-        <v>833</v>
+        <v>812</v>
       </c>
       <c r="AO75">
-        <v>0.99439150850611324</v>
+        <v>0.99604673274056554</v>
       </c>
       <c r="AP75">
-        <v>102.82234405458999</v>
+        <v>72.476566422965192</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -16532,16 +16532,16 @@
         <v>550</v>
       </c>
       <c r="Y76" t="s">
-        <v>397</v>
+        <v>338</v>
       </c>
       <c r="Z76" t="s">
         <v>620</v>
       </c>
       <c r="AA76">
-        <v>0.99553579843385909</v>
+        <v>0.99578350963230966</v>
       </c>
       <c r="AB76">
-        <v>81.84369537924907</v>
+        <v>77.302323407656075</v>
       </c>
       <c r="AD76" t="s">
         <v>417</v>
@@ -16571,13 +16571,13 @@
         <v>834</v>
       </c>
       <c r="AN76" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="AO76">
-        <v>0.99595416313893737</v>
+        <v>0.99720397512579328</v>
       </c>
       <c r="AP76">
-        <v>74.173675786148877</v>
+        <v>51.260456027123361</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -16642,16 +16642,16 @@
         <v>552</v>
       </c>
       <c r="Y77" t="s">
-        <v>356</v>
+        <v>410</v>
       </c>
       <c r="Z77" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="AA77">
-        <v>0.99734372305564056</v>
+        <v>0.99720191150310689</v>
       </c>
       <c r="AB77">
-        <v>48.698410646589842</v>
+        <v>51.298289109706943</v>
       </c>
       <c r="AD77" t="s">
         <v>417</v>
@@ -16681,13 +16681,13 @@
         <v>835</v>
       </c>
       <c r="AN77" t="s">
-        <v>589</v>
+        <v>602</v>
       </c>
       <c r="AO77">
-        <v>0.99687821505939955</v>
+        <v>0.99565348329230585</v>
       </c>
       <c r="AP77">
-        <v>57.232723911007447</v>
+        <v>79.686139641060379</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -16752,16 +16752,16 @@
         <v>554</v>
       </c>
       <c r="Y78" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="Z78" t="s">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="AA78">
-        <v>0.99662670467221526</v>
+        <v>0.9954551465796494</v>
       </c>
       <c r="AB78">
-        <v>61.843747676054292</v>
+        <v>83.32231270642734</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -16826,16 +16826,16 @@
         <v>556</v>
       </c>
       <c r="Y79" t="s">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="Z79" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="AA79">
-        <v>0.99740761205901929</v>
+        <v>0.99552053983611355</v>
       </c>
       <c r="AB79">
-        <v>47.527112251312907</v>
+        <v>82.123436337918946</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -16900,16 +16900,16 @@
         <v>558</v>
       </c>
       <c r="Y80" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="Z80" t="s">
-        <v>601</v>
+        <v>621</v>
       </c>
       <c r="AA80">
-        <v>0.99730769203227776</v>
+        <v>0.98935435476104872</v>
       </c>
       <c r="AB80">
-        <v>49.358979408241737</v>
+        <v>195.1701627141077</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -16974,16 +16974,16 @@
         <v>560</v>
       </c>
       <c r="Y81" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="Z81" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="AA81">
-        <v>0.998073964784436</v>
+        <v>0.99775872574768198</v>
       </c>
       <c r="AB81">
-        <v>35.310645618673441</v>
+        <v>41.090027959164246</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -17048,16 +17048,16 @@
         <v>562</v>
       </c>
       <c r="Y82" t="s">
-        <v>400</v>
+        <v>344</v>
       </c>
       <c r="Z82" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AA82">
-        <v>0.99282834435956602</v>
+        <v>0.99571525957109708</v>
       </c>
       <c r="AB82">
-        <v>131.48035340795542</v>
+        <v>78.553574529886689</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -17122,16 +17122,16 @@
         <v>564</v>
       </c>
       <c r="Y83" t="s">
-        <v>347</v>
+        <v>397</v>
       </c>
       <c r="Z83" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AA83">
-        <v>0.99569310304523451</v>
+        <v>0.99553579843385909</v>
       </c>
       <c r="AB83">
-        <v>78.959777504033639</v>
+        <v>81.84369537924907</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -17196,16 +17196,16 @@
         <v>566</v>
       </c>
       <c r="Y84" t="s">
-        <v>414</v>
+        <v>356</v>
       </c>
       <c r="Z84" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="AA84">
-        <v>0.99502431999137919</v>
+        <v>0.99734372305564056</v>
       </c>
       <c r="AB84">
-        <v>91.220800158047325</v>
+        <v>48.698410646589842</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -17270,16 +17270,16 @@
         <v>568</v>
       </c>
       <c r="Y85" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="Z85" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="AA85">
-        <v>0.99584577617815018</v>
+        <v>0.99662670467221526</v>
       </c>
       <c r="AB85">
-        <v>76.16077006724673</v>
+        <v>61.843747676054292</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -17344,16 +17344,16 @@
         <v>570</v>
       </c>
       <c r="Y86" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Z86" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="AA86">
-        <v>0.99699505644961572</v>
+        <v>0.99740761205901929</v>
       </c>
       <c r="AB86">
-        <v>55.090631757044932</v>
+        <v>47.527112251312907</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -17418,16 +17418,16 @@
         <v>572</v>
       </c>
       <c r="Y87" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="Z87" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="AA87">
-        <v>0.99170691261633115</v>
+        <v>0.99730769203227776</v>
       </c>
       <c r="AB87">
-        <v>152.03993536726261</v>
+        <v>49.358979408241737</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -17492,16 +17492,16 @@
         <v>574</v>
       </c>
       <c r="Y88" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Z88" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="AA88">
-        <v>0.9904035062850528</v>
+        <v>0.998073964784436</v>
       </c>
       <c r="AB88">
-        <v>175.93571810736526</v>
+        <v>35.310645618673441</v>
       </c>
     </row>
   </sheetData>
@@ -17510,7 +17510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D26C7E-3AFB-4F96-80F3-4FC8E16BD0FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BA2C21-464C-4CE8-974C-618640D38619}">
   <dimension ref="B9:Z77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17622,7 +17622,7 @@
         <v>911</v>
       </c>
       <c r="K11" t="s">
-        <v>761</v>
+        <v>815</v>
       </c>
       <c r="L11">
         <v>29.7146465744454</v>
@@ -17655,7 +17655,7 @@
         <v>1045</v>
       </c>
       <c r="X11" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="Y11">
         <v>0.33825</v>
@@ -17690,7 +17690,7 @@
         <v>913</v>
       </c>
       <c r="K12" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="L12">
         <v>13.367096811591049</v>
@@ -17758,7 +17758,7 @@
         <v>915</v>
       </c>
       <c r="K13" t="s">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="L13">
         <v>24.156328337033791</v>
@@ -17791,7 +17791,7 @@
         <v>1049</v>
       </c>
       <c r="X13" t="s">
-        <v>887</v>
+        <v>897</v>
       </c>
       <c r="Y13">
         <v>26.983499999999999</v>
@@ -17826,7 +17826,7 @@
         <v>917</v>
       </c>
       <c r="K14" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="L14">
         <v>16.006796560234815</v>
@@ -17859,7 +17859,7 @@
         <v>1051</v>
       </c>
       <c r="X14" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
       <c r="Y14">
         <v>42.507750000000001</v>
@@ -17894,7 +17894,7 @@
         <v>919</v>
       </c>
       <c r="K15" t="s">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="L15">
         <v>17.682358378036344</v>
@@ -17927,7 +17927,7 @@
         <v>1053</v>
       </c>
       <c r="X15" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="Y15">
         <v>24.900749999999999</v>
@@ -17962,7 +17962,7 @@
         <v>921</v>
       </c>
       <c r="K16" t="s">
-        <v>826</v>
+        <v>773</v>
       </c>
       <c r="L16">
         <v>29.492382648463739</v>
@@ -17995,7 +17995,7 @@
         <v>1055</v>
       </c>
       <c r="X16" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="Y16">
         <v>18.545249999999999</v>
@@ -18030,7 +18030,7 @@
         <v>923</v>
       </c>
       <c r="K17" t="s">
-        <v>825</v>
+        <v>772</v>
       </c>
       <c r="L17">
         <v>8.6778699255653748</v>
@@ -18063,7 +18063,7 @@
         <v>1057</v>
       </c>
       <c r="X17" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="Y17">
         <v>29.838000000000001</v>
@@ -18098,7 +18098,7 @@
         <v>925</v>
       </c>
       <c r="K18" t="s">
-        <v>824</v>
+        <v>771</v>
       </c>
       <c r="L18">
         <v>12.772248157772113</v>
@@ -18131,7 +18131,7 @@
         <v>1059</v>
       </c>
       <c r="X18" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="Y18">
         <v>58.689</v>
@@ -18166,7 +18166,7 @@
         <v>927</v>
       </c>
       <c r="K19" t="s">
-        <v>799</v>
+        <v>834</v>
       </c>
       <c r="L19">
         <v>15.217638427037592</v>
@@ -18199,7 +18199,7 @@
         <v>1061</v>
       </c>
       <c r="X19" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="Y19">
         <v>48.432000000000002</v>
@@ -18234,7 +18234,7 @@
         <v>929</v>
       </c>
       <c r="K20" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="L20">
         <v>3.1385663053565613</v>
@@ -18267,7 +18267,7 @@
         <v>1063</v>
       </c>
       <c r="X20" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="Y20">
         <v>47.794499999999999</v>
@@ -18302,7 +18302,7 @@
         <v>931</v>
       </c>
       <c r="K21" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="L21">
         <v>4.0628682283884237</v>
@@ -18335,7 +18335,7 @@
         <v>1065</v>
       </c>
       <c r="X21" t="s">
-        <v>885</v>
+        <v>895</v>
       </c>
       <c r="Y21">
         <v>7.1767500000000002</v>
@@ -18370,7 +18370,7 @@
         <v>933</v>
       </c>
       <c r="K22" t="s">
-        <v>835</v>
+        <v>761</v>
       </c>
       <c r="L22">
         <v>19.408837136062758</v>
@@ -18403,7 +18403,7 @@
         <v>1067</v>
       </c>
       <c r="X22" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="Y22">
         <v>8.1052499999999998</v>
@@ -18438,7 +18438,7 @@
         <v>935</v>
       </c>
       <c r="K23" t="s">
-        <v>800</v>
+        <v>835</v>
       </c>
       <c r="L23">
         <v>15.054857587707319</v>
@@ -18471,7 +18471,7 @@
         <v>1069</v>
       </c>
       <c r="X23" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="Y23">
         <v>9.3810000000000002</v>
@@ -18506,7 +18506,7 @@
         <v>937</v>
       </c>
       <c r="K24" t="s">
-        <v>831</v>
+        <v>806</v>
       </c>
       <c r="L24">
         <v>13.019602602156084</v>
@@ -18539,7 +18539,7 @@
         <v>1071</v>
       </c>
       <c r="X24" t="s">
-        <v>899</v>
+        <v>908</v>
       </c>
       <c r="Y24">
         <v>11.47575</v>
@@ -18574,7 +18574,7 @@
         <v>939</v>
       </c>
       <c r="K25" t="s">
-        <v>794</v>
+        <v>830</v>
       </c>
       <c r="L25">
         <v>25.094411791551167</v>
@@ -18607,7 +18607,7 @@
         <v>1073</v>
       </c>
       <c r="X25" t="s">
-        <v>904</v>
+        <v>885</v>
       </c>
       <c r="Y25">
         <v>6.1372499999999999</v>
@@ -18642,7 +18642,7 @@
         <v>941</v>
       </c>
       <c r="K26" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="L26">
         <v>18.31221960055294</v>
@@ -18675,7 +18675,7 @@
         <v>1075</v>
       </c>
       <c r="X26" t="s">
-        <v>888</v>
+        <v>898</v>
       </c>
       <c r="Y26">
         <v>14.57325</v>
@@ -18710,7 +18710,7 @@
         <v>943</v>
       </c>
       <c r="K27" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="L27">
         <v>27.91719839668141</v>
@@ -18743,7 +18743,7 @@
         <v>1077</v>
       </c>
       <c r="X27" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="Y27">
         <v>10.491</v>
@@ -18778,7 +18778,7 @@
         <v>945</v>
       </c>
       <c r="K28" t="s">
-        <v>808</v>
+        <v>770</v>
       </c>
       <c r="L28">
         <v>8.5144758814389814</v>
@@ -18811,7 +18811,7 @@
         <v>1079</v>
       </c>
       <c r="X28" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="Y28">
         <v>17.414249999999999</v>
@@ -18846,7 +18846,7 @@
         <v>947</v>
       </c>
       <c r="K29" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="L29">
         <v>12.144708893333986</v>
@@ -18879,7 +18879,7 @@
         <v>1081</v>
       </c>
       <c r="X29" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="Y29">
         <v>10.968</v>
@@ -18914,7 +18914,7 @@
         <v>949</v>
       </c>
       <c r="K30" t="s">
-        <v>795</v>
+        <v>831</v>
       </c>
       <c r="L30">
         <v>1.6724491767694549</v>
@@ -18947,7 +18947,7 @@
         <v>1083</v>
       </c>
       <c r="X30" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="Y30">
         <v>10.79175</v>
@@ -18982,7 +18982,7 @@
         <v>951</v>
       </c>
       <c r="K31" t="s">
-        <v>796</v>
+        <v>832</v>
       </c>
       <c r="L31">
         <v>13.894741632015101</v>
@@ -19015,7 +19015,7 @@
         <v>1085</v>
       </c>
       <c r="X31" t="s">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="Y31">
         <v>20.114249999999998</v>
@@ -19050,7 +19050,7 @@
         <v>953</v>
       </c>
       <c r="K32" t="s">
-        <v>812</v>
+        <v>821</v>
       </c>
       <c r="L32">
         <v>11.876635800692616</v>
@@ -19083,7 +19083,7 @@
         <v>1087</v>
       </c>
       <c r="X32" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="Y32">
         <v>44.373750000000001</v>
@@ -19118,7 +19118,7 @@
         <v>955</v>
       </c>
       <c r="K33" t="s">
-        <v>797</v>
+        <v>833</v>
       </c>
       <c r="L33">
         <v>27.15579263061009</v>
@@ -19151,7 +19151,7 @@
         <v>1089</v>
       </c>
       <c r="X33" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="Y33">
         <v>18.57525</v>
@@ -19186,7 +19186,7 @@
         <v>957</v>
       </c>
       <c r="K34" t="s">
-        <v>762</v>
+        <v>816</v>
       </c>
       <c r="L34">
         <v>27.043339674957092</v>
@@ -19219,7 +19219,7 @@
         <v>1091</v>
       </c>
       <c r="X34" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="Y34">
         <v>18.241499999999998</v>
@@ -19254,7 +19254,7 @@
         <v>959</v>
       </c>
       <c r="K35" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="L35">
         <v>12.170927347824723</v>
@@ -19289,7 +19289,7 @@
         <v>961</v>
       </c>
       <c r="K36" t="s">
-        <v>763</v>
+        <v>817</v>
       </c>
       <c r="L36">
         <v>26.999240466622091</v>
@@ -19324,7 +19324,7 @@
         <v>963</v>
       </c>
       <c r="K37" t="s">
-        <v>779</v>
+        <v>801</v>
       </c>
       <c r="L37">
         <v>23.305350986470582</v>
@@ -19359,7 +19359,7 @@
         <v>965</v>
       </c>
       <c r="K38" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="L38">
         <v>19.293897715957783</v>
@@ -19394,7 +19394,7 @@
         <v>967</v>
       </c>
       <c r="K39" t="s">
-        <v>766</v>
+        <v>776</v>
       </c>
       <c r="L39">
         <v>34.8352470366899</v>
@@ -19429,7 +19429,7 @@
         <v>969</v>
       </c>
       <c r="K40" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="L40">
         <v>22.439012549480047</v>
@@ -19464,7 +19464,7 @@
         <v>971</v>
       </c>
       <c r="K41" t="s">
-        <v>777</v>
+        <v>799</v>
       </c>
       <c r="L41">
         <v>19.571302094407635</v>
@@ -19499,7 +19499,7 @@
         <v>973</v>
       </c>
       <c r="K42" t="s">
-        <v>807</v>
+        <v>769</v>
       </c>
       <c r="L42">
         <v>16.258507759053195</v>
@@ -19534,7 +19534,7 @@
         <v>975</v>
       </c>
       <c r="K43" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="L43">
         <v>48.074816212675138</v>
@@ -19569,7 +19569,7 @@
         <v>977</v>
       </c>
       <c r="K44" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="L44">
         <v>65.59399718970684</v>
@@ -19604,7 +19604,7 @@
         <v>979</v>
       </c>
       <c r="K45" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="L45">
         <v>65.706815294563484</v>
@@ -19639,7 +19639,7 @@
         <v>981</v>
       </c>
       <c r="K46" t="s">
-        <v>834</v>
+        <v>760</v>
       </c>
       <c r="L46">
         <v>13.859521883612567</v>
@@ -19674,7 +19674,7 @@
         <v>983</v>
       </c>
       <c r="K47" t="s">
-        <v>806</v>
+        <v>768</v>
       </c>
       <c r="L47">
         <v>32.682899602232801</v>
@@ -19709,7 +19709,7 @@
         <v>985</v>
       </c>
       <c r="K48" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="L48">
         <v>39.028686646898073</v>
@@ -19744,7 +19744,7 @@
         <v>987</v>
       </c>
       <c r="K49" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="L49">
         <v>25.808486809088087</v>
@@ -19779,7 +19779,7 @@
         <v>989</v>
       </c>
       <c r="K50" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="L50">
         <v>64.703394190718342</v>
@@ -19814,7 +19814,7 @@
         <v>991</v>
       </c>
       <c r="K51" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="L51">
         <v>46.777110562179843</v>
@@ -19849,7 +19849,7 @@
         <v>993</v>
       </c>
       <c r="K52" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="L52">
         <v>83.307298494129057</v>
@@ -19884,7 +19884,7 @@
         <v>995</v>
       </c>
       <c r="K53" t="s">
-        <v>775</v>
+        <v>797</v>
       </c>
       <c r="L53">
         <v>8.0718642408500934</v>
@@ -19919,7 +19919,7 @@
         <v>997</v>
       </c>
       <c r="K54" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="L54">
         <v>25.555956589747868</v>
@@ -19954,7 +19954,7 @@
         <v>999</v>
       </c>
       <c r="K55" t="s">
-        <v>776</v>
+        <v>798</v>
       </c>
       <c r="L55">
         <v>26.74310381624198</v>
@@ -19989,7 +19989,7 @@
         <v>1001</v>
       </c>
       <c r="K56" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="L56">
         <v>47.811917655816522</v>
@@ -20024,7 +20024,7 @@
         <v>1003</v>
       </c>
       <c r="K57" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="L57">
         <v>65.898010391046881</v>
@@ -20059,7 +20059,7 @@
         <v>1005</v>
       </c>
       <c r="K58" t="s">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="L58">
         <v>49.914822287456737</v>
@@ -20094,7 +20094,7 @@
         <v>1007</v>
       </c>
       <c r="K59" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="L59">
         <v>19.963633091222835</v>
@@ -20129,7 +20129,7 @@
         <v>1009</v>
       </c>
       <c r="K60" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="L60">
         <v>71.04376789192942</v>
@@ -20164,7 +20164,7 @@
         <v>1011</v>
       </c>
       <c r="K61" t="s">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="L61">
         <v>43.07229279461999</v>
@@ -20199,7 +20199,7 @@
         <v>1013</v>
       </c>
       <c r="K62" t="s">
-        <v>805</v>
+        <v>766</v>
       </c>
       <c r="L62">
         <v>38.769945374969119</v>
@@ -20234,7 +20234,7 @@
         <v>1015</v>
       </c>
       <c r="K63" t="s">
-        <v>832</v>
+        <v>758</v>
       </c>
       <c r="L63">
         <v>59.009737840109466</v>
@@ -20269,7 +20269,7 @@
         <v>1017</v>
       </c>
       <c r="K64" t="s">
-        <v>829</v>
+        <v>804</v>
       </c>
       <c r="L64">
         <v>28.865927665826828</v>
@@ -20304,7 +20304,7 @@
         <v>1019</v>
       </c>
       <c r="K65" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="L65">
         <v>37.976260419426943</v>
@@ -20339,7 +20339,7 @@
         <v>1021</v>
       </c>
       <c r="K66" t="s">
-        <v>827</v>
+        <v>802</v>
       </c>
       <c r="L66">
         <v>44.88386263672971</v>
@@ -20374,7 +20374,7 @@
         <v>1023</v>
       </c>
       <c r="K67" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="L67">
         <v>23.350121881103082</v>
@@ -20409,7 +20409,7 @@
         <v>1025</v>
       </c>
       <c r="K68" t="s">
-        <v>793</v>
+        <v>829</v>
       </c>
       <c r="L68">
         <v>15.289477961960474</v>
@@ -20444,7 +20444,7 @@
         <v>1027</v>
       </c>
       <c r="K69" t="s">
-        <v>778</v>
+        <v>800</v>
       </c>
       <c r="L69">
         <v>10.395885695189069</v>
@@ -20479,7 +20479,7 @@
         <v>1029</v>
       </c>
       <c r="K70" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="L70">
         <v>23.89105636564183</v>
@@ -20514,7 +20514,7 @@
         <v>1031</v>
       </c>
       <c r="K71" t="s">
-        <v>792</v>
+        <v>828</v>
       </c>
       <c r="L71">
         <v>18.959710131684457</v>
@@ -20549,7 +20549,7 @@
         <v>1033</v>
       </c>
       <c r="K72" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="L72">
         <v>6.6550975614073966</v>
@@ -20584,7 +20584,7 @@
         <v>1035</v>
       </c>
       <c r="K73" t="s">
-        <v>760</v>
+        <v>814</v>
       </c>
       <c r="L73">
         <v>13.961943802326671</v>
@@ -20619,7 +20619,7 @@
         <v>1037</v>
       </c>
       <c r="K74" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="L74">
         <v>51.937776653453852</v>
@@ -20654,7 +20654,7 @@
         <v>1039</v>
       </c>
       <c r="K75" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="L75">
         <v>21.246092446368579</v>
@@ -20689,7 +20689,7 @@
         <v>1041</v>
       </c>
       <c r="K76" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="L76">
         <v>19.42059121972445</v>
@@ -20724,7 +20724,7 @@
         <v>1043</v>
       </c>
       <c r="K77" t="s">
-        <v>758</v>
+        <v>813</v>
       </c>
       <c r="L77">
         <v>30.063621105864488</v>
@@ -20739,7 +20739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7454201F-E78F-40AD-BABA-7DDD522268A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80C9E26C-C699-430C-BD85-432D2844F234}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68616C16-9A92-45DC-9084-72F774CA4112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CD96F4-628E-4E27-AED8-2D896423BFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4224" uniqueCount="1127">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -660,7 +660,7 @@
     <t>e_spv_IND_001</t>
   </si>
   <si>
-    <t>solar resource in cluster 1</t>
+    <t>solar resource near Patan (cluster 1)</t>
   </si>
   <si>
     <t>annual</t>
@@ -672,463 +672,463 @@
     <t>e_spv_IND_002</t>
   </si>
   <si>
-    <t>solar resource in cluster 2</t>
+    <t>solar resource near Ahor (cluster 2)</t>
   </si>
   <si>
     <t>e_spv_IND_003</t>
   </si>
   <si>
-    <t>solar resource in cluster 3</t>
+    <t>solar resource near Bhilwara (cluster 3)</t>
   </si>
   <si>
     <t>e_spv_IND_004</t>
   </si>
   <si>
-    <t>solar resource in cluster 4</t>
+    <t>solar resource near Bhavnagar (cluster 4)</t>
   </si>
   <si>
     <t>e_spv_IND_005</t>
   </si>
   <si>
-    <t>solar resource in cluster 5</t>
+    <t>solar resource near Godhra (cluster 5)</t>
   </si>
   <si>
     <t>e_spv_IND_006</t>
   </si>
   <si>
-    <t>solar resource in cluster 6</t>
+    <t>solar resource near Barmhan Kalan (cluster 6)</t>
   </si>
   <si>
     <t>e_spv_IND_007</t>
   </si>
   <si>
-    <t>solar resource in cluster 7</t>
+    <t>solar resource near Dhulia (cluster 7)</t>
   </si>
   <si>
     <t>e_spv_IND_008</t>
   </si>
   <si>
-    <t>solar resource in cluster 8</t>
+    <t>solar resource near Amravati (cluster 8)</t>
   </si>
   <si>
     <t>e_spv_IND_009</t>
   </si>
   <si>
-    <t>solar resource in cluster 9</t>
+    <t>solar resource near Malkapur (cluster 9)</t>
   </si>
   <si>
     <t>e_spv_IND_010</t>
   </si>
   <si>
-    <t>solar resource in cluster 10</t>
+    <t>solar resource near Ujjain (cluster 10)</t>
   </si>
   <si>
     <t>e_spv_IND_011</t>
   </si>
   <si>
-    <t>solar resource in cluster 11</t>
+    <t>solar resource near Bhopal (cluster 11)</t>
   </si>
   <si>
     <t>e_spv_IND_012</t>
   </si>
   <si>
-    <t>solar resource in cluster 12</t>
+    <t>solar resource near Suratgarh (cluster 12)</t>
   </si>
   <si>
     <t>e_spv_IND_013</t>
   </si>
   <si>
-    <t>solar resource in cluster 13</t>
+    <t>solar resource near Moga (cluster 13)</t>
   </si>
   <si>
     <t>e_spv_IND_014</t>
   </si>
   <si>
-    <t>solar resource in cluster 14</t>
+    <t>solar resource near Phalodi (cluster 14)</t>
   </si>
   <si>
     <t>e_spv_IND_015</t>
   </si>
   <si>
-    <t>solar resource in cluster 15</t>
+    <t>solar resource near Fatehpur (cluster 15)</t>
   </si>
   <si>
     <t>e_spv_IND_016</t>
   </si>
   <si>
-    <t>solar resource in cluster 16</t>
+    <t>solar resource near Pathankot (cluster 16)</t>
   </si>
   <si>
     <t>e_spv_IND_017</t>
   </si>
   <si>
-    <t>solar resource in cluster 17</t>
+    <t>solar resource near Saharanpur (cluster 17)</t>
   </si>
   <si>
     <t>e_spv_IND_018</t>
   </si>
   <si>
-    <t>solar resource in cluster 18</t>
+    <t>solar resource near Shivpuri (cluster 18)</t>
   </si>
   <si>
     <t>e_spv_IND_019</t>
   </si>
   <si>
-    <t>solar resource in cluster 19</t>
+    <t>solar resource near Chhatarpur (cluster 19)</t>
   </si>
   <si>
     <t>e_spv_IND_020</t>
   </si>
   <si>
-    <t>solar resource in cluster 20</t>
+    <t>solar resource near Kanpur (cluster 20)</t>
   </si>
   <si>
     <t>e_spv_IND_021</t>
   </si>
   <si>
-    <t>solar resource in cluster 21</t>
+    <t>solar resource near Jaipur (cluster 21)</t>
   </si>
   <si>
     <t>e_spv_IND_022</t>
   </si>
   <si>
-    <t>solar resource in cluster 22</t>
+    <t>solar resource near Faridabad (cluster 22)</t>
   </si>
   <si>
     <t>e_spv_IND_023</t>
   </si>
   <si>
-    <t>solar resource in cluster 23</t>
+    <t>solar resource near Haldwani (cluster 23)</t>
   </si>
   <si>
     <t>e_spv_IND_024</t>
   </si>
   <si>
-    <t>solar resource in cluster 24</t>
+    <t>solar resource near Bareilly (cluster 24)</t>
   </si>
   <si>
     <t>e_spv_IND_025</t>
   </si>
   <si>
-    <t>solar resource in cluster 25</t>
+    <t>solar resource near Mothihari (cluster 25)</t>
   </si>
   <si>
     <t>e_spv_IND_026</t>
   </si>
   <si>
-    <t>solar resource in cluster 26</t>
+    <t>solar resource near Bahraigh (cluster 26)</t>
   </si>
   <si>
     <t>e_spv_IND_027</t>
   </si>
   <si>
-    <t>solar resource in cluster 27</t>
+    <t>solar resource near Prayagraj (cluster 27)</t>
   </si>
   <si>
     <t>e_spv_IND_028</t>
   </si>
   <si>
-    <t>solar resource in cluster 28</t>
+    <t>solar resource near Ghazipur (cluster 28)</t>
   </si>
   <si>
     <t>e_spv_IND_029</t>
   </si>
   <si>
-    <t>solar resource in cluster 29</t>
+    <t>solar resource near Jaisalmer (cluster 29)</t>
   </si>
   <si>
     <t>e_spv_IND_030</t>
   </si>
   <si>
-    <t>solar resource in cluster 30</t>
+    <t>solar resource near Rapar (cluster 30)</t>
   </si>
   <si>
     <t>e_spv_IND_031</t>
   </si>
   <si>
-    <t>solar resource in cluster 31</t>
+    <t>solar resource near Rajkot (cluster 31)</t>
   </si>
   <si>
     <t>e_spv_IND_032</t>
   </si>
   <si>
-    <t>solar resource in cluster 32</t>
+    <t>solar resource near Kharagpur (cluster 32)</t>
   </si>
   <si>
     <t>e_spv_IND_033</t>
   </si>
   <si>
-    <t>solar resource in cluster 33</t>
+    <t>solar resource near Purnea (cluster 33)</t>
   </si>
   <si>
     <t>e_spv_IND_034</t>
   </si>
   <si>
-    <t>solar resource in cluster 34</t>
+    <t>solar resource near Ingraj Bazar (cluster 34)</t>
   </si>
   <si>
     <t>e_spv_IND_035</t>
   </si>
   <si>
-    <t>solar resource in cluster 35</t>
+    <t>solar resource near Durgapur (cluster 35)</t>
   </si>
   <si>
     <t>e_spv_IND_036</t>
   </si>
   <si>
-    <t>solar resource in cluster 36</t>
+    <t>solar resource near Imphal (cluster 36)</t>
   </si>
   <si>
     <t>e_spv_IND_037</t>
   </si>
   <si>
-    <t>solar resource in cluster 37</t>
+    <t>solar resource near Dimapur (cluster 37)</t>
   </si>
   <si>
     <t>e_spv_IND_038</t>
   </si>
   <si>
-    <t>solar resource in cluster 38</t>
+    <t>solar resource near Karaikandi (cluster 38)</t>
   </si>
   <si>
     <t>e_spv_IND_039</t>
   </si>
   <si>
-    <t>solar resource in cluster 39</t>
+    <t>solar resource near Pangzawl (cluster 39)</t>
   </si>
   <si>
     <t>e_spv_IND_040</t>
   </si>
   <si>
-    <t>solar resource in cluster 40</t>
+    <t>solar resource near Agartala (cluster 40)</t>
   </si>
   <si>
     <t>e_spv_IND_041</t>
   </si>
   <si>
-    <t>solar resource in cluster 41</t>
+    <t>solar resource near Jorhat (cluster 41)</t>
   </si>
   <si>
     <t>e_spv_IND_042</t>
   </si>
   <si>
-    <t>solar resource in cluster 42</t>
+    <t>solar resource near Tinsukia (cluster 42)</t>
   </si>
   <si>
     <t>e_spv_IND_043</t>
   </si>
   <si>
-    <t>solar resource in cluster 43</t>
+    <t>solar resource near Dibrugarh (cluster 43)</t>
   </si>
   <si>
     <t>e_spv_IND_044</t>
   </si>
   <si>
-    <t>solar resource in cluster 44</t>
+    <t>solar resource near Tura (cluster 44)</t>
   </si>
   <si>
     <t>e_spv_IND_045</t>
   </si>
   <si>
-    <t>solar resource in cluster 45</t>
+    <t>solar resource near Jalpaiguri (cluster 45)</t>
   </si>
   <si>
     <t>e_spv_IND_046</t>
   </si>
   <si>
-    <t>solar resource in cluster 46</t>
+    <t>solar resource near Bongaigaon (cluster 46)</t>
   </si>
   <si>
     <t>e_spv_IND_047</t>
   </si>
   <si>
-    <t>solar resource in cluster 47</t>
+    <t>solar resource near Chicacole (cluster 47)</t>
   </si>
   <si>
     <t>e_spv_IND_048</t>
   </si>
   <si>
-    <t>solar resource in cluster 48</t>
+    <t>solar resource near Bhubaneshwar (cluster 48)</t>
   </si>
   <si>
     <t>e_spv_IND_049</t>
   </si>
   <si>
-    <t>solar resource in cluster 49</t>
+    <t>solar resource near Ramgundam (cluster 49)</t>
   </si>
   <si>
     <t>e_spv_IND_050</t>
   </si>
   <si>
-    <t>solar resource in cluster 50</t>
+    <t>solar resource near Jagdalpur (cluster 50)</t>
   </si>
   <si>
     <t>e_spv_IND_051</t>
   </si>
   <si>
-    <t>solar resource in cluster 51</t>
+    <t>solar resource near Jagdalpur (cluster 51)</t>
   </si>
   <si>
     <t>e_spv_IND_052</t>
   </si>
   <si>
-    <t>solar resource in cluster 52</t>
+    <t>solar resource near Mandla (cluster 52)</t>
   </si>
   <si>
     <t>e_spv_IND_053</t>
   </si>
   <si>
-    <t>solar resource in cluster 53</t>
+    <t>solar resource near Chanda (cluster 53)</t>
   </si>
   <si>
     <t>e_spv_IND_054</t>
   </si>
   <si>
-    <t>solar resource in cluster 54</t>
+    <t>solar resource near Raipur (cluster 54)</t>
   </si>
   <si>
     <t>e_spv_IND_055</t>
   </si>
   <si>
-    <t>solar resource in cluster 55</t>
+    <t>solar resource near Bargarh (cluster 55)</t>
   </si>
   <si>
     <t>e_spv_IND_056</t>
   </si>
   <si>
-    <t>solar resource in cluster 56</t>
+    <t>solar resource near Bada Barabil (cluster 56)</t>
   </si>
   <si>
     <t>e_spv_IND_057</t>
   </si>
   <si>
-    <t>solar resource in cluster 57</t>
+    <t>solar resource near Ambikapur (cluster 57)</t>
   </si>
   <si>
     <t>e_spv_IND_058</t>
   </si>
   <si>
-    <t>solar resource in cluster 58</t>
+    <t>solar resource near Gaya (cluster 58)</t>
   </si>
   <si>
     <t>e_spv_IND_059</t>
   </si>
   <si>
-    <t>solar resource in cluster 59</t>
+    <t>solar resource near Gulbarga (cluster 59)</t>
   </si>
   <si>
     <t>e_spv_IND_060</t>
   </si>
   <si>
-    <t>solar resource in cluster 60</t>
+    <t>solar resource near Nizamabad (cluster 60)</t>
   </si>
   <si>
     <t>e_spv_IND_061</t>
   </si>
   <si>
-    <t>solar resource in cluster 61</t>
+    <t>solar resource near Nanded (cluster 61)</t>
   </si>
   <si>
     <t>e_spv_IND_062</t>
   </si>
   <si>
-    <t>solar resource in cluster 62</t>
+    <t>solar resource near Karjat (cluster 62)</t>
   </si>
   <si>
     <t>e_spv_IND_063</t>
   </si>
   <si>
-    <t>solar resource in cluster 63</t>
+    <t>solar resource near Belgaum (cluster 63)</t>
   </si>
   <si>
     <t>e_spv_IND_064</t>
   </si>
   <si>
-    <t>solar resource in cluster 64</t>
+    <t>solar resource near Gadag (cluster 64)</t>
   </si>
   <si>
     <t>e_spv_IND_065</t>
   </si>
   <si>
-    <t>solar resource in cluster 65</t>
+    <t>solar resource near Rajahmundry (cluster 65)</t>
   </si>
   <si>
     <t>e_spv_IND_066</t>
   </si>
   <si>
-    <t>solar resource in cluster 66</t>
+    <t>solar resource near Khammam (cluster 66)</t>
   </si>
   <si>
     <t>e_spv_IND_067</t>
   </si>
   <si>
-    <t>solar resource in cluster 67</t>
+    <t>solar resource near Kadiri (cluster 67)</t>
   </si>
   <si>
     <t>e_spv_IND_068</t>
   </si>
   <si>
-    <t>solar resource in cluster 68</t>
+    <t>solar resource near Kurnool (cluster 68)</t>
   </si>
   <si>
     <t>e_spv_IND_069</t>
   </si>
   <si>
-    <t>solar resource in cluster 69</t>
+    <t>solar resource near Arcot (cluster 69)</t>
   </si>
   <si>
     <t>e_spv_IND_070</t>
   </si>
   <si>
-    <t>solar resource in cluster 70</t>
+    <t>solar resource near Nellore (cluster 70)</t>
   </si>
   <si>
     <t>e_spv_IND_071</t>
   </si>
   <si>
-    <t>solar resource in cluster 71</t>
+    <t>solar resource near Paramagudi (cluster 71)</t>
   </si>
   <si>
     <t>e_spv_IND_072</t>
   </si>
   <si>
-    <t>solar resource in cluster 72</t>
+    <t>solar resource near Tanjore (cluster 72)</t>
   </si>
   <si>
     <t>e_spv_IND_073</t>
   </si>
   <si>
-    <t>solar resource in cluster 73</t>
+    <t>solar resource near Trichinopoly (cluster 73)</t>
   </si>
   <si>
     <t>e_spv_IND_074</t>
   </si>
   <si>
-    <t>solar resource in cluster 74</t>
+    <t>solar resource near Malappuram (cluster 74)</t>
   </si>
   <si>
     <t>e_spv_IND_075</t>
   </si>
   <si>
-    <t>solar resource in cluster 75</t>
+    <t>solar resource near Kalleli (cluster 75)</t>
   </si>
   <si>
     <t>e_spv_IND_076</t>
   </si>
   <si>
-    <t>solar resource in cluster 76</t>
+    <t>solar resource near Mangalore (cluster 76)</t>
   </si>
   <si>
     <t>e_spv_IND_077</t>
   </si>
   <si>
-    <t>solar resource in cluster 77</t>
+    <t>solar resource near Chamrajnagar (cluster 77)</t>
   </si>
   <si>
     <t>e_spv_IND_078</t>
   </si>
   <si>
-    <t>solar resource in cluster 78</t>
+    <t>solar resource near Arsikere (cluster 78)</t>
   </si>
   <si>
     <t>~fi_t</t>
@@ -1383,18 +1383,432 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_061</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 61</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_017</t>
   </si>
   <si>
@@ -1419,318 +1833,6 @@
     <t>connecting solar to buses in cluster 47</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_004</t>
   </si>
   <si>
@@ -1755,228 +1857,141 @@
     <t>connecting solar to buses in cluster 75</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Wardha_IND,e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND,e_Dharmapuri_IND,e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Sikandarabad_IND,e_Korba_IND,e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Rajahmundry_IND,e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND,e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND,e_Fatehpur_IND,e_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND,e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND,e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND,e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND,e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND,e_Jaipur_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND,e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Moga_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Sikandarabad_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Medinipur_IND,e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Vadodara_IND,e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND,e_Indore_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND,e_Phalodi_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND,e_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND,e_Wardha_IND,e_Korba_IND,e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND,e_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND,e_Vadodara_IND,e_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND,e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND,e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND,e_Kurnool_IND</t>
+  </si>
+  <si>
     <t>e_Solapur_IND,e_Wardha_IND</t>
   </si>
   <si>
     <t>e_Sikandarabad_IND,e_Moga_IND</t>
   </si>
   <si>
-    <t>e_Kurnool_IND,e_Rajahmundry_IND</t>
-  </si>
-  <si>
     <t>e_Wardha_IND,e_Korba_IND</t>
   </si>
   <si>
-    <t>e_Rajahmundry_IND,e_Korba_IND</t>
-  </si>
-  <si>
-    <t>e_Bhuj_IND,e_Vadodara_IND,e_Phalodi_IND</t>
-  </si>
-  <si>
-    <t>e_Bhuj_IND</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>e_Vadodara_IND,e_Indore_IND</t>
-  </si>
-  <si>
-    <t>e_Phalodi_IND,e_Moga_IND</t>
-  </si>
-  <si>
-    <t>e_Dharmapuri_IND</t>
-  </si>
-  <si>
-    <t>e_Solapur_IND,e_Kurnool_IND</t>
-  </si>
-  <si>
-    <t>e_Jaipur_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Fatehpur_IND</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND,e_Solapur_IND</t>
-  </si>
-  <si>
-    <t>e_Solapur_IND,e_Dharmapuri_IND,e_Kurnool_IND</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND,e_Sikandarabad_IND,e_Korba_IND,e_Fatehpur_IND</t>
-  </si>
-  <si>
-    <t>e_Korba_IND,e_Fatehpur_IND</t>
-  </si>
-  <si>
-    <t>e_Korba_IND,e_Fatehpur_IND,e_Medinipur_IND</t>
-  </si>
-  <si>
-    <t>e_Indore_IND,e_Jaipur_IND</t>
-  </si>
-  <si>
-    <t>e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Sikandarabad_IND,e_Fatehpur_IND</t>
-  </si>
-  <si>
-    <t>e_Tezpur_IND</t>
-  </si>
-  <si>
-    <t>e_Phalodi_IND,e_Jaipur_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Korba_IND</t>
-  </si>
-  <si>
-    <t>e_Solapur_IND</t>
-  </si>
-  <si>
-    <t>e_Vadodara_IND,e_Indore_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Kurnool_IND</t>
-  </si>
-  <si>
-    <t>e_Phalodi_IND</t>
-  </si>
-  <si>
-    <t>e_Kurnool_IND,e_Wardha_IND,e_Korba_IND,e_Rajahmundry_IND</t>
-  </si>
-  <si>
-    <t>e_Fatehpur_IND,e_Tezpur_IND</t>
-  </si>
-  <si>
-    <t>e_Moga_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Indore_IND,e_Sikandarabad_IND,e_Jaipur_IND</t>
-  </si>
-  <si>
-    <t>e_Indore_IND,e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>e_Dharmapuri_IND,e_Kurnool_IND</t>
-  </si>
-  <si>
-    <t>e_Medinipur_IND,e_Fatehpur_IND</t>
-  </si>
-  <si>
-    <t>e_Vadodara_IND,e_Phalodi_IND,e_Jaipur_IND</t>
-  </si>
-  <si>
-    <t>e_Korba_IND,e_Medinipur_IND</t>
-  </si>
-  <si>
     <t>e_Wardha_IND,e_Bhuj_IND,e_Vadodara_IND</t>
   </si>
   <si>
@@ -1986,19 +2001,388 @@
     <t>e_Wardha_IND,e_Indore_IND</t>
   </si>
   <si>
-    <t>e_Moga_IND</t>
-  </si>
-  <si>
-    <t>e_Bhuj_IND,e_Vadodara_IND</t>
-  </si>
-  <si>
-    <t>e_Korba_IND,e_Rajahmundry_IND</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND,e_Vadodara_IND,e_Indore_IND</t>
-  </si>
-  <si>
-    <t>e_Kurnool_IND,e_Wardha_IND</t>
+    <t>distr_wonelc_won_IND_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_053</t>
@@ -2019,388 +2403,226 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
+    <t>elc_won_IND_061</t>
+  </si>
+  <si>
+    <t>elc_won_IND_058</t>
+  </si>
+  <si>
+    <t>elc_won_IND_015</t>
+  </si>
+  <si>
+    <t>elc_won_IND_020</t>
+  </si>
+  <si>
+    <t>elc_won_IND_021</t>
+  </si>
+  <si>
+    <t>elc_won_IND_023</t>
+  </si>
+  <si>
+    <t>e_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_008</t>
+  </si>
+  <si>
+    <t>elc_won_IND_007</t>
+  </si>
+  <si>
+    <t>elc_won_IND_006</t>
+  </si>
+  <si>
+    <t>elc_won_IND_050</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND,e_Wardha_IND,e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_064</t>
+  </si>
+  <si>
+    <t>elc_won_IND_011</t>
+  </si>
+  <si>
+    <t>elc_won_IND_025</t>
+  </si>
+  <si>
+    <t>elc_won_IND_065</t>
+  </si>
+  <si>
+    <t>elc_won_IND_044</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND,e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_042</t>
+  </si>
+  <si>
+    <t>elc_won_IND_005</t>
+  </si>
+  <si>
+    <t>elc_won_IND_039</t>
+  </si>
+  <si>
+    <t>elc_won_IND_002</t>
+  </si>
+  <si>
+    <t>elc_won_IND_051</t>
+  </si>
+  <si>
+    <t>elc_won_IND_004</t>
+  </si>
+  <si>
+    <t>elc_won_IND_029</t>
+  </si>
+  <si>
+    <t>elc_won_IND_003</t>
+  </si>
+  <si>
+    <t>elc_won_IND_067</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_063</t>
+  </si>
+  <si>
+    <t>elc_won_IND_001</t>
+  </si>
+  <si>
+    <t>elc_won_IND_024</t>
+  </si>
+  <si>
+    <t>elc_won_IND_026</t>
+  </si>
+  <si>
+    <t>elc_won_IND_049</t>
+  </si>
+  <si>
+    <t>elc_won_IND_047</t>
+  </si>
+  <si>
+    <t>elc_won_IND_035</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Vadodara_IND,e_Indore_IND,e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_062</t>
+  </si>
+  <si>
+    <t>elc_won_IND_033</t>
+  </si>
+  <si>
+    <t>elc_won_IND_060</t>
+  </si>
+  <si>
+    <t>elc_won_IND_010</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND,e_Korba_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_019</t>
+  </si>
+  <si>
+    <t>elc_won_IND_017</t>
+  </si>
+  <si>
+    <t>elc_won_IND_055</t>
+  </si>
+  <si>
+    <t>elc_won_IND_016</t>
+  </si>
+  <si>
+    <t>elc_won_IND_028</t>
+  </si>
+  <si>
+    <t>elc_won_IND_056</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Jaipur_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_054</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_014</t>
+  </si>
+  <si>
+    <t>elc_won_IND_043</t>
+  </si>
+  <si>
+    <t>elc_won_IND_045</t>
+  </si>
+  <si>
+    <t>elc_won_IND_031</t>
+  </si>
+  <si>
+    <t>elc_won_IND_059</t>
+  </si>
+  <si>
+    <t>elc_won_IND_027</t>
+  </si>
+  <si>
+    <t>elc_won_IND_009</t>
+  </si>
+  <si>
+    <t>elc_won_IND_013</t>
+  </si>
+  <si>
+    <t>elc_won_IND_057</t>
+  </si>
+  <si>
+    <t>elc_won_IND_041</t>
+  </si>
+  <si>
+    <t>elc_won_IND_030</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND,e_Kurnool_IND,e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_048</t>
+  </si>
+  <si>
+    <t>elc_won_IND_034</t>
+  </si>
+  <si>
+    <t>elc_won_IND_046</t>
+  </si>
+  <si>
+    <t>elc_won_IND_022</t>
+  </si>
+  <si>
+    <t>elc_won_IND_066</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND,e_Phalodi_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_040</t>
+  </si>
+  <si>
+    <t>elc_won_IND_038</t>
+  </si>
+  <si>
+    <t>elc_won_IND_052</t>
+  </si>
+  <si>
+    <t>elc_won_IND_037</t>
+  </si>
+  <si>
+    <t>elc_won_IND_032</t>
+  </si>
+  <si>
+    <t>elc_won_IND_018</t>
   </si>
   <si>
     <t>elc_won_IND_053</t>
@@ -2415,226 +2637,28 @@
     <t>elc_won_IND_012</t>
   </si>
   <si>
-    <t>elc_won_IND_066</t>
-  </si>
-  <si>
-    <t>e_Jaipur_IND,e_Phalodi_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_040</t>
-  </si>
-  <si>
-    <t>elc_won_IND_038</t>
-  </si>
-  <si>
-    <t>elc_won_IND_052</t>
-  </si>
-  <si>
-    <t>e_Phalodi_IND,e_Jaipur_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_037</t>
-  </si>
-  <si>
-    <t>elc_won_IND_032</t>
-  </si>
-  <si>
-    <t>elc_won_IND_018</t>
-  </si>
-  <si>
-    <t>elc_won_IND_008</t>
-  </si>
-  <si>
-    <t>elc_won_IND_007</t>
-  </si>
-  <si>
-    <t>elc_won_IND_006</t>
-  </si>
-  <si>
-    <t>elc_won_IND_051</t>
-  </si>
-  <si>
-    <t>elc_won_IND_004</t>
-  </si>
-  <si>
-    <t>elc_won_IND_029</t>
-  </si>
-  <si>
-    <t>elc_won_IND_003</t>
-  </si>
-  <si>
-    <t>elc_won_IND_055</t>
-  </si>
-  <si>
-    <t>elc_won_IND_016</t>
-  </si>
-  <si>
-    <t>elc_won_IND_028</t>
-  </si>
-  <si>
-    <t>elc_won_IND_049</t>
-  </si>
-  <si>
-    <t>elc_won_IND_047</t>
-  </si>
-  <si>
-    <t>e_Solapur_IND,e_Dharmapuri_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_035</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND,e_Vadodara_IND,e_Indore_IND,e_Solapur_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_062</t>
-  </si>
-  <si>
-    <t>elc_won_IND_033</t>
-  </si>
-  <si>
-    <t>elc_won_IND_060</t>
-  </si>
-  <si>
-    <t>elc_won_IND_010</t>
-  </si>
-  <si>
-    <t>e_Fatehpur_IND,e_Korba_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_019</t>
-  </si>
-  <si>
-    <t>elc_won_IND_017</t>
-  </si>
-  <si>
-    <t>elc_won_IND_057</t>
-  </si>
-  <si>
-    <t>elc_won_IND_041</t>
-  </si>
-  <si>
-    <t>elc_won_IND_030</t>
-  </si>
-  <si>
-    <t>e_Dharmapuri_IND,e_Kurnool_IND,e_Rajahmundry_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_043</t>
-  </si>
-  <si>
-    <t>elc_won_IND_045</t>
-  </si>
-  <si>
-    <t>elc_won_IND_031</t>
-  </si>
-  <si>
-    <t>elc_won_IND_059</t>
-  </si>
-  <si>
-    <t>elc_won_IND_027</t>
-  </si>
-  <si>
-    <t>elc_won_IND_056</t>
-  </si>
-  <si>
-    <t>e_Indore_IND,e_Jaipur_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_054</t>
-  </si>
-  <si>
-    <t>e_Sikandarabad_IND,e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_014</t>
-  </si>
-  <si>
-    <t>elc_won_IND_050</t>
-  </si>
-  <si>
-    <t>e_Bhuj_IND,e_Wardha_IND,e_Vadodara_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_064</t>
-  </si>
-  <si>
-    <t>elc_won_IND_011</t>
-  </si>
-  <si>
-    <t>elc_won_IND_025</t>
-  </si>
-  <si>
-    <t>e_Medinipur_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_067</t>
-  </si>
-  <si>
-    <t>elc_won_IND_063</t>
-  </si>
-  <si>
-    <t>elc_won_IND_001</t>
-  </si>
-  <si>
-    <t>elc_won_IND_024</t>
-  </si>
-  <si>
-    <t>elc_won_IND_026</t>
-  </si>
-  <si>
-    <t>elc_won_IND_048</t>
-  </si>
-  <si>
-    <t>elc_won_IND_034</t>
-  </si>
-  <si>
-    <t>elc_won_IND_046</t>
-  </si>
-  <si>
-    <t>elc_won_IND_022</t>
-  </si>
-  <si>
-    <t>elc_won_IND_065</t>
-  </si>
-  <si>
-    <t>elc_won_IND_044</t>
-  </si>
-  <si>
-    <t>elc_won_IND_042</t>
-  </si>
-  <si>
-    <t>elc_won_IND_005</t>
-  </si>
-  <si>
-    <t>elc_won_IND_039</t>
-  </si>
-  <si>
-    <t>elc_won_IND_002</t>
-  </si>
-  <si>
-    <t>elc_won_IND_061</t>
-  </si>
-  <si>
-    <t>elc_won_IND_058</t>
-  </si>
-  <si>
-    <t>elc_won_IND_015</t>
-  </si>
-  <si>
-    <t>elc_won_IND_020</t>
-  </si>
-  <si>
-    <t>elc_won_IND_021</t>
-  </si>
-  <si>
-    <t>elc_won_IND_023</t>
-  </si>
-  <si>
-    <t>elc_won_IND_009</t>
-  </si>
-  <si>
-    <t>elc_won_IND_013</t>
+    <t>distr_wofelc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_002</t>
@@ -2649,6 +2673,60 @@
     <t>connecting wind offshore to buses in cluster 15</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_IND_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_IND_013</t>
   </si>
   <si>
@@ -2661,48 +2739,6 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_011</t>
   </si>
   <si>
@@ -2721,12 +2757,6 @@
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_007</t>
   </si>
   <si>
@@ -2751,34 +2781,19 @@
     <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
+    <t>elc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_014</t>
   </si>
   <si>
     <t>elc_wof_IND_002</t>
@@ -2787,33 +2802,42 @@
     <t>elc_wof_IND_015</t>
   </si>
   <si>
+    <t>elc_wof_IND_021</t>
+  </si>
+  <si>
+    <t>e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_010</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_018</t>
+  </si>
+  <si>
     <t>elc_wof_IND_013</t>
   </si>
   <si>
     <t>elc_wof_IND_023</t>
   </si>
   <si>
-    <t>elc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_018</t>
-  </si>
-  <si>
     <t>elc_wof_IND_011</t>
   </si>
   <si>
@@ -2826,9 +2850,6 @@
     <t>elc_wof_IND_016</t>
   </si>
   <si>
-    <t>elc_wof_IND_010</t>
-  </si>
-  <si>
     <t>elc_wof_IND_007</t>
   </si>
   <si>
@@ -2841,571 +2862,550 @@
     <t>elc_wof_IND_024</t>
   </si>
   <si>
-    <t>elc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_009</t>
-  </si>
-  <si>
-    <t>e_Bhuj_IND,e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_014</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_021</t>
-  </si>
-  <si>
-    <t>e_Rajahmundry_IND</t>
-  </si>
-  <si>
     <t>e_won_IND_001</t>
   </si>
   <si>
-    <t>wind resource in cluster 1</t>
+    <t>wind onshore resource near Sitapur (cluster 1)</t>
   </si>
   <si>
     <t>e_won_IND_002</t>
   </si>
   <si>
-    <t>wind resource in cluster 2</t>
+    <t>wind onshore resource near Gorakhpur (cluster 2)</t>
   </si>
   <si>
     <t>e_won_IND_003</t>
   </si>
   <si>
-    <t>wind resource in cluster 3</t>
+    <t>wind onshore resource near Sultanpur (cluster 3)</t>
   </si>
   <si>
     <t>e_won_IND_004</t>
   </si>
   <si>
-    <t>wind resource in cluster 4</t>
+    <t>wind onshore resource near Moradabad (cluster 4)</t>
   </si>
   <si>
     <t>e_won_IND_005</t>
   </si>
   <si>
-    <t>wind resource in cluster 5</t>
+    <t>wind onshore resource near Karnal (cluster 5)</t>
   </si>
   <si>
     <t>e_won_IND_006</t>
   </si>
   <si>
-    <t>wind resource in cluster 6</t>
+    <t>wind onshore resource near Farrukhabad (cluster 6)</t>
   </si>
   <si>
     <t>e_won_IND_007</t>
   </si>
   <si>
-    <t>wind resource in cluster 7</t>
+    <t>wind onshore resource near Agra (cluster 7)</t>
   </si>
   <si>
     <t>e_won_IND_008</t>
   </si>
   <si>
-    <t>wind resource in cluster 8</t>
+    <t>wind onshore resource near Delhi (cluster 8)</t>
   </si>
   <si>
     <t>e_won_IND_009</t>
   </si>
   <si>
-    <t>wind resource in cluster 9</t>
+    <t>wind onshore resource near Katri (cluster 9)</t>
   </si>
   <si>
     <t>e_won_IND_010</t>
   </si>
   <si>
-    <t>wind resource in cluster 10</t>
+    <t>wind onshore resource near Shahdol (cluster 10)</t>
   </si>
   <si>
     <t>e_won_IND_011</t>
   </si>
   <si>
-    <t>wind resource in cluster 11</t>
+    <t>wind onshore resource near Sidhi (cluster 11)</t>
   </si>
   <si>
     <t>e_won_IND_012</t>
   </si>
   <si>
-    <t>wind resource in cluster 12</t>
+    <t>wind onshore resource near Waraseoni (cluster 12)</t>
   </si>
   <si>
     <t>e_won_IND_013</t>
   </si>
   <si>
-    <t>wind resource in cluster 13</t>
+    <t>wind onshore resource near Mahasamund (cluster 13)</t>
   </si>
   <si>
     <t>e_won_IND_014</t>
   </si>
   <si>
-    <t>wind resource in cluster 14</t>
+    <t>wind onshore resource near Bhilai (cluster 14)</t>
   </si>
   <si>
     <t>e_won_IND_015</t>
   </si>
   <si>
-    <t>wind resource in cluster 15</t>
+    <t>wind onshore resource near Jagdalpur (cluster 15)</t>
   </si>
   <si>
     <t>e_won_IND_016</t>
   </si>
   <si>
-    <t>wind resource in cluster 16</t>
+    <t>wind onshore resource near Mothihari (cluster 16)</t>
   </si>
   <si>
     <t>e_won_IND_017</t>
   </si>
   <si>
-    <t>wind resource in cluster 17</t>
+    <t>wind onshore resource near Bihta (cluster 17)</t>
   </si>
   <si>
     <t>e_won_IND_018</t>
   </si>
   <si>
-    <t>wind resource in cluster 18</t>
+    <t>wind onshore resource near Sasaram (cluster 18)</t>
   </si>
   <si>
     <t>e_won_IND_019</t>
   </si>
   <si>
-    <t>wind resource in cluster 19</t>
+    <t>wind onshore resource near Mirzapur (cluster 19)</t>
   </si>
   <si>
     <t>e_won_IND_020</t>
   </si>
   <si>
-    <t>wind resource in cluster 20</t>
+    <t>wind onshore resource near Gumla (cluster 20)</t>
   </si>
   <si>
     <t>e_won_IND_021</t>
   </si>
   <si>
-    <t>wind resource in cluster 21</t>
+    <t>wind onshore resource near Hazaribagh (cluster 21)</t>
   </si>
   <si>
     <t>e_won_IND_022</t>
   </si>
   <si>
-    <t>wind resource in cluster 22</t>
+    <t>wind onshore resource near Agartala (cluster 22)</t>
   </si>
   <si>
     <t>e_won_IND_023</t>
   </si>
   <si>
-    <t>wind resource in cluster 23</t>
+    <t>wind onshore resource near Kolkata (cluster 23)</t>
   </si>
   <si>
     <t>e_won_IND_024</t>
   </si>
   <si>
-    <t>wind resource in cluster 24</t>
+    <t>wind onshore resource near Bhubaneshwar (cluster 24)</t>
   </si>
   <si>
     <t>e_won_IND_025</t>
   </si>
   <si>
-    <t>wind resource in cluster 25</t>
+    <t>wind onshore resource near Bankura (cluster 25)</t>
   </si>
   <si>
     <t>e_won_IND_026</t>
   </si>
   <si>
-    <t>wind resource in cluster 26</t>
+    <t>wind onshore resource near Raneswar (cluster 26)</t>
   </si>
   <si>
     <t>e_won_IND_027</t>
   </si>
   <si>
-    <t>wind resource in cluster 27</t>
+    <t>wind onshore resource near Supaul (cluster 27)</t>
   </si>
   <si>
     <t>e_won_IND_028</t>
   </si>
   <si>
-    <t>wind resource in cluster 28</t>
+    <t>wind onshore resource near Balurghat (cluster 28)</t>
   </si>
   <si>
     <t>e_won_IND_029</t>
   </si>
   <si>
-    <t>wind resource in cluster 29</t>
+    <t>wind onshore resource near Peruvancha (cluster 29)</t>
   </si>
   <si>
     <t>e_won_IND_030</t>
   </si>
   <si>
-    <t>wind resource in cluster 30</t>
+    <t>wind onshore resource near Ongole (cluster 30)</t>
   </si>
   <si>
     <t>e_won_IND_031</t>
   </si>
   <si>
-    <t>wind resource in cluster 31</t>
+    <t>wind onshore resource near Kothapet (cluster 31)</t>
   </si>
   <si>
     <t>e_won_IND_032</t>
   </si>
   <si>
-    <t>wind resource in cluster 32</t>
+    <t>wind onshore resource near Jeypore (cluster 32)</t>
   </si>
   <si>
     <t>e_won_IND_033</t>
   </si>
   <si>
-    <t>wind resource in cluster 33</t>
+    <t>wind onshore resource near Amravati (cluster 33)</t>
   </si>
   <si>
     <t>e_won_IND_034</t>
   </si>
   <si>
-    <t>wind resource in cluster 34</t>
+    <t>wind onshore resource near Sirur (cluster 34)</t>
   </si>
   <si>
     <t>e_won_IND_035</t>
   </si>
   <si>
-    <t>wind resource in cluster 35</t>
+    <t>wind onshore resource near Jalgaon (cluster 35)</t>
   </si>
   <si>
     <t>e_won_IND_036</t>
   </si>
   <si>
-    <t>wind resource in cluster 36</t>
+    <t>wind onshore resource near Paramagudi (cluster 36)</t>
   </si>
   <si>
     <t>e_won_IND_037</t>
   </si>
   <si>
-    <t>wind resource in cluster 37</t>
+    <t>wind onshore resource near Oulgaret (cluster 37)</t>
   </si>
   <si>
     <t>e_won_IND_038</t>
   </si>
   <si>
-    <t>wind resource in cluster 38</t>
+    <t>wind onshore resource near Markapur (cluster 38)</t>
   </si>
   <si>
     <t>e_won_IND_039</t>
   </si>
   <si>
-    <t>wind resource in cluster 39</t>
+    <t>wind onshore resource near Tiruvannamalai (cluster 39)</t>
   </si>
   <si>
     <t>e_won_IND_040</t>
   </si>
   <si>
-    <t>wind resource in cluster 40</t>
+    <t>wind onshore resource near Malkajgiri (cluster 40)</t>
   </si>
   <si>
     <t>e_won_IND_041</t>
   </si>
   <si>
-    <t>wind resource in cluster 41</t>
+    <t>wind onshore resource near Solapur (cluster 41)</t>
   </si>
   <si>
     <t>e_won_IND_042</t>
   </si>
   <si>
-    <t>wind resource in cluster 42</t>
+    <t>wind onshore resource near Anantapur (cluster 42)</t>
   </si>
   <si>
     <t>e_won_IND_043</t>
   </si>
   <si>
-    <t>wind resource in cluster 43</t>
+    <t>wind onshore resource near Mahad (cluster 43)</t>
   </si>
   <si>
     <t>e_won_IND_044</t>
   </si>
   <si>
-    <t>wind resource in cluster 44</t>
+    <t>wind onshore resource near Kolhapur (cluster 44)</t>
   </si>
   <si>
     <t>e_won_IND_045</t>
   </si>
   <si>
-    <t>wind resource in cluster 45</t>
+    <t>wind onshore resource near Bodinayakkanur (cluster 45)</t>
   </si>
   <si>
     <t>e_won_IND_046</t>
   </si>
   <si>
-    <t>wind resource in cluster 46</t>
+    <t>wind onshore resource near Mysore (cluster 46)</t>
   </si>
   <si>
     <t>e_won_IND_047</t>
   </si>
   <si>
-    <t>wind resource in cluster 47</t>
+    <t>wind onshore resource near Hubli (cluster 47)</t>
   </si>
   <si>
     <t>e_won_IND_048</t>
   </si>
   <si>
-    <t>wind resource in cluster 48</t>
+    <t>wind onshore resource near Gandhidham (cluster 48)</t>
   </si>
   <si>
     <t>e_won_IND_049</t>
   </si>
   <si>
-    <t>wind resource in cluster 49</t>
+    <t>wind onshore resource near Nasik (cluster 49)</t>
   </si>
   <si>
     <t>e_won_IND_050</t>
   </si>
   <si>
-    <t>wind resource in cluster 50</t>
+    <t>wind onshore resource near Bhavnagar (cluster 50)</t>
   </si>
   <si>
     <t>e_won_IND_051</t>
   </si>
   <si>
-    <t>wind resource in cluster 51</t>
+    <t>wind onshore resource near Modasa (cluster 51)</t>
   </si>
   <si>
     <t>e_won_IND_052</t>
   </si>
   <si>
-    <t>wind resource in cluster 52</t>
+    <t>wind onshore resource near Jodhpur (cluster 52)</t>
   </si>
   <si>
     <t>e_won_IND_053</t>
   </si>
   <si>
-    <t>wind resource in cluster 53</t>
+    <t>wind onshore resource near Raniwara Kalan (cluster 53)</t>
   </si>
   <si>
     <t>e_won_IND_054</t>
   </si>
   <si>
-    <t>wind resource in cluster 54</t>
+    <t>wind onshore resource near Gadarwara (cluster 54)</t>
   </si>
   <si>
     <t>e_won_IND_055</t>
   </si>
   <si>
-    <t>wind resource in cluster 55</t>
+    <t>wind onshore resource near Indore (cluster 55)</t>
   </si>
   <si>
     <t>e_won_IND_056</t>
   </si>
   <si>
-    <t>wind resource in cluster 56</t>
+    <t>wind onshore resource near Shujalpur (cluster 56)</t>
   </si>
   <si>
     <t>e_won_IND_057</t>
   </si>
   <si>
-    <t>wind resource in cluster 57</t>
+    <t>wind onshore resource near Bijaynagar (cluster 57)</t>
   </si>
   <si>
     <t>e_won_IND_058</t>
   </si>
   <si>
-    <t>wind resource in cluster 58</t>
+    <t>wind onshore resource near Sawai Madhopur (cluster 58)</t>
   </si>
   <si>
     <t>e_won_IND_059</t>
   </si>
   <si>
-    <t>wind resource in cluster 59</t>
+    <t>wind onshore resource near Rath (cluster 59)</t>
   </si>
   <si>
     <t>e_won_IND_060</t>
   </si>
   <si>
-    <t>wind resource in cluster 60</t>
+    <t>wind onshore resource near Jhansi (cluster 60)</t>
   </si>
   <si>
     <t>e_won_IND_061</t>
   </si>
   <si>
-    <t>wind resource in cluster 61</t>
+    <t>wind onshore resource near Mansa (cluster 61)</t>
   </si>
   <si>
     <t>e_won_IND_062</t>
   </si>
   <si>
-    <t>wind resource in cluster 62</t>
+    <t>wind onshore resource near Alwar (cluster 62)</t>
   </si>
   <si>
     <t>e_won_IND_063</t>
   </si>
   <si>
-    <t>wind resource in cluster 63</t>
+    <t>wind onshore resource near Hisar (cluster 63)</t>
   </si>
   <si>
     <t>e_won_IND_064</t>
   </si>
   <si>
-    <t>wind resource in cluster 64</t>
+    <t>wind onshore resource near Jaisalmer (cluster 64)</t>
   </si>
   <si>
     <t>e_won_IND_065</t>
   </si>
   <si>
-    <t>wind resource in cluster 65</t>
+    <t>wind onshore resource near Suratgarh (cluster 65)</t>
   </si>
   <si>
     <t>e_won_IND_066</t>
   </si>
   <si>
-    <t>wind resource in cluster 66</t>
+    <t>wind onshore resource near Sikar (cluster 66)</t>
   </si>
   <si>
     <t>e_won_IND_067</t>
   </si>
   <si>
-    <t>wind resource in cluster 67</t>
+    <t>wind onshore resource near Nokha (cluster 67)</t>
   </si>
   <si>
     <t>e_wof_IND_001</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 1</t>
+    <t>wind offshore resource near Attadappa (cluster 1)</t>
   </si>
   <si>
     <t>e_wof_IND_002</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 2</t>
+    <t>wind offshore resource near Mangalore (cluster 2)</t>
   </si>
   <si>
     <t>e_wof_IND_003</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 3</t>
+    <t>wind offshore resource near Karwar (cluster 3)</t>
   </si>
   <si>
     <t>e_wof_IND_004</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 4</t>
+    <t>wind offshore resource near Ratnagiri (cluster 4)</t>
   </si>
   <si>
     <t>e_wof_IND_005</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 5</t>
+    <t>wind offshore resource near Vasco Da Gama (cluster 5)</t>
   </si>
   <si>
     <t>e_wof_IND_006</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 6</t>
+    <t>wind offshore resource near Okha (cluster 6)</t>
   </si>
   <si>
     <t>e_wof_IND_007</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 7</t>
+    <t>wind offshore resource near Okha (cluster 7)</t>
   </si>
   <si>
     <t>e_wof_IND_008</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 8</t>
+    <t>wind offshore resource near Mumbai (cluster 8)</t>
   </si>
   <si>
     <t>e_wof_IND_009</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 9</t>
+    <t>wind offshore resource near Veraval (cluster 9)</t>
   </si>
   <si>
     <t>e_wof_IND_010</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 10</t>
+    <t>wind offshore resource near Veraval (cluster 10)</t>
   </si>
   <si>
     <t>e_wof_IND_011</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 11</t>
+    <t>wind offshore resource near Veraval (cluster 11)</t>
   </si>
   <si>
     <t>e_wof_IND_012</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 12</t>
+    <t>wind offshore resource near Mumbai (cluster 12)</t>
   </si>
   <si>
     <t>e_wof_IND_013</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 13</t>
+    <t>wind offshore resource near Chennai (cluster 13)</t>
   </si>
   <si>
     <t>e_wof_IND_014</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 14</t>
+    <t>wind offshore resource near Negapatam (cluster 14)</t>
   </si>
   <si>
     <t>e_wof_IND_015</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 15</t>
+    <t>wind offshore resource near Puducherry (cluster 15)</t>
   </si>
   <si>
     <t>e_wof_IND_016</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 16</t>
+    <t>wind offshore resource near Peyanvilai (cluster 16)</t>
   </si>
   <si>
     <t>e_wof_IND_017</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 17</t>
+    <t>wind offshore resource near Thiruvananthapuram (cluster 17)</t>
   </si>
   <si>
     <t>e_wof_IND_018</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 18</t>
+    <t>wind offshore resource near Nagercoil (cluster 18)</t>
   </si>
   <si>
     <t>e_wof_IND_019</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 19</t>
+    <t>wind offshore resource near Ongole (cluster 19)</t>
   </si>
   <si>
     <t>e_wof_IND_020</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 20</t>
+    <t>wind offshore resource near Vishakhapatnam (cluster 20)</t>
   </si>
   <si>
     <t>e_wof_IND_021</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 21</t>
+    <t>wind offshore resource near Kakinada (cluster 21)</t>
   </si>
   <si>
     <t>e_wof_IND_022</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 22</t>
+    <t>wind offshore resource near Haldia (cluster 22)</t>
   </si>
   <si>
     <t>e_wof_IND_023</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 23</t>
+    <t>wind offshore resource near Aul (cluster 23)</t>
   </si>
   <si>
     <t>e_wof_IND_024</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 24</t>
+    <t>wind offshore resource near Brahmapur (cluster 24)</t>
   </si>
   <si>
     <t>~fi_t: UP</t>
@@ -8280,7 +8280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A24A560-DA28-4BDD-AE41-EB216959A8BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFA3D80-4287-46A1-914D-71857FDD2C91}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -8518,16 +8518,16 @@
         <v>418</v>
       </c>
       <c r="Y11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z11" t="s">
         <v>578</v>
       </c>
       <c r="AA11">
-        <v>0.99540885392130762</v>
+        <v>0.99557960200072415</v>
       </c>
       <c r="AB11">
-        <v>84.171011442693441</v>
+        <v>81.040629986723459</v>
       </c>
       <c r="AD11" t="s">
         <v>417</v>
@@ -8557,13 +8557,13 @@
         <v>758</v>
       </c>
       <c r="AN11" t="s">
-        <v>759</v>
+        <v>595</v>
       </c>
       <c r="AO11">
-        <v>0.99439150850611324</v>
+        <v>0.99425851119451991</v>
       </c>
       <c r="AP11">
-        <v>102.82234405458999</v>
+        <v>105.26062810046888</v>
       </c>
       <c r="AR11" t="s">
         <v>417</v>
@@ -8593,13 +8593,13 @@
         <v>884</v>
       </c>
       <c r="BB11" t="s">
-        <v>603</v>
+        <v>618</v>
       </c>
       <c r="BC11">
-        <v>0.97123008268954114</v>
+        <v>0.98734896749216872</v>
       </c>
       <c r="BD11">
-        <v>527.44848402507967</v>
+        <v>898.7317460537439</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8664,16 +8664,16 @@
         <v>422</v>
       </c>
       <c r="Y12" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="Z12" t="s">
         <v>579</v>
       </c>
       <c r="AA12">
-        <v>0.99360802526828129</v>
+        <v>0.99295357769237991</v>
       </c>
       <c r="AB12">
-        <v>117.18620341484296</v>
+        <v>129.18440897303603</v>
       </c>
       <c r="AD12" t="s">
         <v>417</v>
@@ -8700,16 +8700,16 @@
         <v>626</v>
       </c>
       <c r="AM12" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AN12" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="AO12">
-        <v>0.99595416313893737</v>
+        <v>0.99712282780353001</v>
       </c>
       <c r="AP12">
-        <v>74.173675786148877</v>
+        <v>52.74815693528295</v>
       </c>
       <c r="AR12" t="s">
         <v>417</v>
@@ -8739,13 +8739,13 @@
         <v>885</v>
       </c>
       <c r="BB12" t="s">
-        <v>588</v>
+        <v>886</v>
       </c>
       <c r="BC12">
-        <v>0.99603877136023145</v>
+        <v>0.98137594918937099</v>
       </c>
       <c r="BD12">
-        <v>72.622525062424401</v>
+        <v>971.50301904282946</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8810,16 +8810,16 @@
         <v>424</v>
       </c>
       <c r="Y13" t="s">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="Z13" t="s">
         <v>580</v>
       </c>
       <c r="AA13">
-        <v>0.99515679011930902</v>
+        <v>0.99696751363483405</v>
       </c>
       <c r="AB13">
-        <v>88.792181146001369</v>
+        <v>55.595583361375894</v>
       </c>
       <c r="AD13" t="s">
         <v>417</v>
@@ -8846,16 +8846,16 @@
         <v>628</v>
       </c>
       <c r="AM13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AN13" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="AO13">
-        <v>0.99687821505939955</v>
+        <v>0.99005506097810436</v>
       </c>
       <c r="AP13">
-        <v>57.232723911007447</v>
+        <v>182.32388206808599</v>
       </c>
       <c r="AR13" t="s">
         <v>417</v>
@@ -8882,16 +8882,16 @@
         <v>840</v>
       </c>
       <c r="BA13" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="BB13" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="BC13">
-        <v>0.99526782804010661</v>
+        <v>0.9889956676941275</v>
       </c>
       <c r="BD13">
-        <v>86.756485931379871</v>
+        <v>878.66944859321336</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8956,16 +8956,16 @@
         <v>426</v>
       </c>
       <c r="Y14" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="Z14" t="s">
         <v>581</v>
       </c>
       <c r="AA14">
-        <v>0.99409145347725225</v>
+        <v>0.98964014500078279</v>
       </c>
       <c r="AB14">
-        <v>108.32335291704148</v>
+        <v>189.93067498564957</v>
       </c>
       <c r="AD14" t="s">
         <v>417</v>
@@ -8992,16 +8992,16 @@
         <v>630</v>
       </c>
       <c r="AM14" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AN14" t="s">
-        <v>763</v>
+        <v>584</v>
       </c>
       <c r="AO14">
-        <v>0.99618121233373258</v>
+        <v>0.99631269816920021</v>
       </c>
       <c r="AP14">
-        <v>70.011107214903078</v>
+        <v>67.600533564663479</v>
       </c>
       <c r="AR14" t="s">
         <v>417</v>
@@ -9028,16 +9028,16 @@
         <v>842</v>
       </c>
       <c r="BA14" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="BB14" t="s">
-        <v>615</v>
+        <v>581</v>
       </c>
       <c r="BC14">
-        <v>0.98605138538291048</v>
+        <v>0.99193721244794397</v>
       </c>
       <c r="BD14">
-        <v>255.7246013133088</v>
+        <v>765.01824997048959</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9102,16 +9102,16 @@
         <v>428</v>
       </c>
       <c r="Y15" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="Z15" t="s">
         <v>582</v>
       </c>
       <c r="AA15">
-        <v>0.99464051280908794</v>
+        <v>0.9966137462997855</v>
       </c>
       <c r="AB15">
-        <v>98.257265166721183</v>
+        <v>62.081317837266766</v>
       </c>
       <c r="AD15" t="s">
         <v>417</v>
@@ -9138,16 +9138,16 @@
         <v>632</v>
       </c>
       <c r="AM15" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="AN15" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO15">
-        <v>0.99592364356186902</v>
+        <v>0.99772400077475298</v>
       </c>
       <c r="AP15">
-        <v>74.733201365734146</v>
+        <v>41.726652462862774</v>
       </c>
       <c r="AR15" t="s">
         <v>417</v>
@@ -9174,16 +9174,16 @@
         <v>844</v>
       </c>
       <c r="BA15" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="BB15" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="BC15">
-        <v>0.99307601382667698</v>
+        <v>0.97123008268954114</v>
       </c>
       <c r="BD15">
-        <v>126.93974651092147</v>
+        <v>1095.1134925657575</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9248,16 +9248,16 @@
         <v>430</v>
       </c>
       <c r="Y16" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="Z16" t="s">
         <v>583</v>
       </c>
       <c r="AA16">
-        <v>0.99579357955795456</v>
+        <v>0.99011796851295664</v>
       </c>
       <c r="AB16">
-        <v>77.117708104165573</v>
+        <v>181.17057726246117</v>
       </c>
       <c r="AD16" t="s">
         <v>417</v>
@@ -9284,16 +9284,16 @@
         <v>634</v>
       </c>
       <c r="AM16" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="AN16" t="s">
-        <v>612</v>
+        <v>764</v>
       </c>
       <c r="AO16">
-        <v>0.99641167752379312</v>
+        <v>0.99604673274056554</v>
       </c>
       <c r="AP16">
-        <v>65.785912063792665</v>
+        <v>72.476566422965192</v>
       </c>
       <c r="AR16" t="s">
         <v>417</v>
@@ -9320,16 +9320,16 @@
         <v>846</v>
       </c>
       <c r="BA16" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="BB16" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="BC16">
-        <v>0.99275904397179515</v>
+        <v>0.99603877136023145</v>
       </c>
       <c r="BD16">
-        <v>132.75086051708826</v>
+        <v>504.70597767064743</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9394,16 +9394,16 @@
         <v>432</v>
       </c>
       <c r="Y17" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="Z17" t="s">
         <v>584</v>
       </c>
       <c r="AA17">
-        <v>0.99066346416517681</v>
+        <v>0.99635118654529808</v>
       </c>
       <c r="AB17">
-        <v>171.16982363842584</v>
+        <v>66.894913336202478</v>
       </c>
       <c r="AD17" t="s">
         <v>417</v>
@@ -9430,16 +9430,16 @@
         <v>636</v>
       </c>
       <c r="AM17" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AN17" t="s">
-        <v>767</v>
+        <v>598</v>
       </c>
       <c r="AO17">
-        <v>0.99540934349034305</v>
+        <v>0.99784941409648109</v>
       </c>
       <c r="AP17">
-        <v>84.162036010377406</v>
+        <v>39.427408231180806</v>
       </c>
       <c r="AR17" t="s">
         <v>417</v>
@@ -9466,16 +9466,16 @@
         <v>848</v>
       </c>
       <c r="BA17" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="BB17" t="s">
-        <v>584</v>
+        <v>892</v>
       </c>
       <c r="BC17">
-        <v>0.98787195157138663</v>
+        <v>0.99308209783432144</v>
       </c>
       <c r="BD17">
-        <v>222.34755452457901</v>
+        <v>692.35619078172965</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9540,16 +9540,16 @@
         <v>434</v>
       </c>
       <c r="Y18" t="s">
-        <v>343</v>
+        <v>393</v>
       </c>
       <c r="Z18" t="s">
         <v>585</v>
       </c>
       <c r="AA18">
-        <v>0.99560939477262078</v>
+        <v>0.99440507690252466</v>
       </c>
       <c r="AB18">
-        <v>80.494429168619106</v>
+        <v>102.57359012038077</v>
       </c>
       <c r="AD18" t="s">
         <v>417</v>
@@ -9576,16 +9576,16 @@
         <v>638</v>
       </c>
       <c r="AM18" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="AN18" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="AO18">
-        <v>0.99657664224037934</v>
+        <v>0.99831921281104818</v>
       </c>
       <c r="AP18">
-        <v>62.761558926379031</v>
+        <v>30.814431797450247</v>
       </c>
       <c r="AR18" t="s">
         <v>417</v>
@@ -9612,16 +9612,16 @@
         <v>850</v>
       </c>
       <c r="BA18" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="BB18" t="s">
-        <v>585</v>
+        <v>614</v>
       </c>
       <c r="BC18">
-        <v>0.98853599644984702</v>
+        <v>0.98154438143849254</v>
       </c>
       <c r="BD18">
-        <v>210.17339841947171</v>
+        <v>969.45095280769931</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9686,16 +9686,16 @@
         <v>436</v>
       </c>
       <c r="Y19" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="Z19" t="s">
         <v>586</v>
       </c>
       <c r="AA19">
-        <v>0.99544039231362502</v>
+        <v>0.99578350963230966</v>
       </c>
       <c r="AB19">
-        <v>83.592807583541571</v>
+        <v>77.302323407656075</v>
       </c>
       <c r="AD19" t="s">
         <v>417</v>
@@ -9722,16 +9722,16 @@
         <v>640</v>
       </c>
       <c r="AM19" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="AN19" t="s">
-        <v>621</v>
+        <v>594</v>
       </c>
       <c r="AO19">
-        <v>0.99091245964276031</v>
+        <v>0.99845356202909108</v>
       </c>
       <c r="AP19">
-        <v>166.60490654939525</v>
+        <v>28.351362799997673</v>
       </c>
       <c r="AR19" t="s">
         <v>417</v>
@@ -9758,16 +9758,16 @@
         <v>852</v>
       </c>
       <c r="BA19" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="BB19" t="s">
-        <v>578</v>
+        <v>613</v>
       </c>
       <c r="BC19">
-        <v>0.98734896749216872</v>
+        <v>0.98787195157138663</v>
       </c>
       <c r="BD19">
-        <v>231.9355959769062</v>
+        <v>892.36005668860651</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9832,16 +9832,16 @@
         <v>438</v>
       </c>
       <c r="Y20" t="s">
-        <v>349</v>
+        <v>410</v>
       </c>
       <c r="Z20" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="AA20">
-        <v>0.99190124970484694</v>
+        <v>0.99720191150310689</v>
       </c>
       <c r="AB20">
-        <v>148.47708874447352</v>
+        <v>51.298289109706943</v>
       </c>
       <c r="AD20" t="s">
         <v>417</v>
@@ -9868,16 +9868,16 @@
         <v>642</v>
       </c>
       <c r="AM20" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="AN20" t="s">
-        <v>591</v>
+        <v>769</v>
       </c>
       <c r="AO20">
-        <v>0.99846230399777702</v>
+        <v>0.99074948308423383</v>
       </c>
       <c r="AP20">
-        <v>28.191093374087806</v>
+        <v>169.59281012238051</v>
       </c>
       <c r="AR20" t="s">
         <v>417</v>
@@ -9904,16 +9904,16 @@
         <v>854</v>
       </c>
       <c r="BA20" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="BB20" t="s">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="BC20">
-        <v>0.96206044130113966</v>
+        <v>0.98853599644984702</v>
       </c>
       <c r="BD20">
-        <v>695.55857614577315</v>
+        <v>884.26977658603062</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9978,16 +9978,16 @@
         <v>440</v>
       </c>
       <c r="Y21" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="Z21" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AA21">
-        <v>0.9940089461809174</v>
+        <v>0.9954551465796494</v>
       </c>
       <c r="AB21">
-        <v>109.83598668318054</v>
+        <v>83.32231270642734</v>
       </c>
       <c r="AD21" t="s">
         <v>417</v>
@@ -10014,16 +10014,16 @@
         <v>644</v>
       </c>
       <c r="AM21" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AN21" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="AO21">
-        <v>0.99784941409648109</v>
+        <v>0.99270401267208797</v>
       </c>
       <c r="AP21">
-        <v>39.427408231180806</v>
+        <v>133.75976767838793</v>
       </c>
       <c r="AR21" t="s">
         <v>417</v>
@@ -10050,16 +10050,16 @@
         <v>856</v>
       </c>
       <c r="BA21" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="BB21" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="BC21">
-        <v>0.98742179529179352</v>
+        <v>0.99307601382667698</v>
       </c>
       <c r="BD21">
-        <v>230.6004196504513</v>
+        <v>692.74232246689905</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10124,16 +10124,16 @@
         <v>442</v>
       </c>
       <c r="Y22" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="Z22" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AA22">
-        <v>0.99600761890991041</v>
+        <v>0.99552053983611355</v>
       </c>
       <c r="AB22">
-        <v>73.193653318309615</v>
+        <v>82.123436337918946</v>
       </c>
       <c r="AD22" t="s">
         <v>417</v>
@@ -10160,16 +10160,16 @@
         <v>646</v>
       </c>
       <c r="AM22" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AN22" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="AO22">
-        <v>0.99831921281104818</v>
+        <v>0.99764772442226368</v>
       </c>
       <c r="AP22">
-        <v>30.814431797450247</v>
+        <v>43.125052258499352</v>
       </c>
       <c r="AR22" t="s">
         <v>417</v>
@@ -10196,16 +10196,16 @@
         <v>858</v>
       </c>
       <c r="BA22" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="BB22" t="s">
-        <v>896</v>
+        <v>592</v>
       </c>
       <c r="BC22">
-        <v>0.98158890816872557</v>
+        <v>0.99275904397179515</v>
       </c>
       <c r="BD22">
-        <v>337.53668357336363</v>
+        <v>712.85934259006547</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10270,16 +10270,16 @@
         <v>444</v>
       </c>
       <c r="Y23" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="Z23" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AA23">
-        <v>0.99700029739711071</v>
+        <v>0.98935435476104872</v>
       </c>
       <c r="AB23">
-        <v>54.994547719637801</v>
+        <v>195.1701627141077</v>
       </c>
       <c r="AD23" t="s">
         <v>417</v>
@@ -10306,16 +10306,16 @@
         <v>648</v>
       </c>
       <c r="AM23" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AN23" t="s">
-        <v>599</v>
+        <v>764</v>
       </c>
       <c r="AO23">
-        <v>0.99845356202909108</v>
+        <v>0.99703044337128366</v>
       </c>
       <c r="AP23">
-        <v>28.351362799997673</v>
+        <v>54.441871526466279</v>
       </c>
       <c r="AR23" t="s">
         <v>417</v>
@@ -10342,16 +10342,16 @@
         <v>860</v>
       </c>
       <c r="BA23" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="BB23" t="s">
-        <v>603</v>
+        <v>764</v>
       </c>
       <c r="BC23">
-        <v>0.98402494782096717</v>
+        <v>0.98389167860462323</v>
       </c>
       <c r="BD23">
-        <v>292.87595661560192</v>
+        <v>940.85304900034021</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10416,16 +10416,16 @@
         <v>446</v>
       </c>
       <c r="Y24" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="Z24" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AA24">
-        <v>0.99408511741207395</v>
+        <v>0.99775872574768198</v>
       </c>
       <c r="AB24">
-        <v>108.43951411197776</v>
+        <v>41.090027959164246</v>
       </c>
       <c r="AD24" t="s">
         <v>417</v>
@@ -10452,16 +10452,16 @@
         <v>650</v>
       </c>
       <c r="AM24" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AN24" t="s">
-        <v>586</v>
+        <v>616</v>
       </c>
       <c r="AO24">
-        <v>0.99533901157332205</v>
+        <v>0.99245794727704639</v>
       </c>
       <c r="AP24">
-        <v>85.451454489096079</v>
+        <v>138.27096658748206</v>
       </c>
       <c r="AR24" t="s">
         <v>417</v>
@@ -10488,16 +10488,16 @@
         <v>862</v>
       </c>
       <c r="BA24" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="BB24" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="BC24">
-        <v>0.99223982078870177</v>
+        <v>0.96206044130113966</v>
       </c>
       <c r="BD24">
-        <v>142.26995220713331</v>
+        <v>1206.8302901477819</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10562,16 +10562,16 @@
         <v>448</v>
       </c>
       <c r="Y25" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="Z25" t="s">
         <v>591</v>
       </c>
       <c r="AA25">
-        <v>0.99529948277209723</v>
+        <v>0.99569491323214321</v>
       </c>
       <c r="AB25">
-        <v>86.176149178218239</v>
+        <v>78.926590744041093</v>
       </c>
       <c r="AD25" t="s">
         <v>417</v>
@@ -10598,16 +10598,16 @@
         <v>652</v>
       </c>
       <c r="AM25" t="s">
+        <v>774</v>
+      </c>
+      <c r="AN25" t="s">
         <v>775</v>
       </c>
-      <c r="AN25" t="s">
-        <v>598</v>
-      </c>
       <c r="AO25">
-        <v>0.99754339130519476</v>
+        <v>0.99381230463557813</v>
       </c>
       <c r="AP25">
-        <v>45.037826071429087</v>
+        <v>113.44108168106689</v>
       </c>
       <c r="AR25" t="s">
         <v>417</v>
@@ -10634,16 +10634,16 @@
         <v>864</v>
       </c>
       <c r="BA25" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="BB25" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="BC25">
-        <v>0.98154438143849254</v>
+        <v>0.98742179529179352</v>
       </c>
       <c r="BD25">
-        <v>338.35300696097039</v>
+        <v>897.84446069498176</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10708,16 +10708,16 @@
         <v>450</v>
       </c>
       <c r="Y26" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="Z26" t="s">
         <v>592</v>
       </c>
       <c r="AA26">
-        <v>0.99557960200072415</v>
+        <v>0.99484118006716937</v>
       </c>
       <c r="AB26">
-        <v>81.040629986723459</v>
+        <v>94.578365435227795</v>
       </c>
       <c r="AD26" t="s">
         <v>417</v>
@@ -10747,13 +10747,13 @@
         <v>776</v>
       </c>
       <c r="AN26" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AO26">
-        <v>0.99542398891280204</v>
+        <v>0.99534539864304916</v>
       </c>
       <c r="AP26">
-        <v>83.893536598629126</v>
+        <v>85.3343582107656</v>
       </c>
       <c r="AR26" t="s">
         <v>417</v>
@@ -10780,16 +10780,16 @@
         <v>866</v>
       </c>
       <c r="BA26" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="BB26" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="BC26">
-        <v>0.98838558997012138</v>
+        <v>0.99526782804010661</v>
       </c>
       <c r="BD26">
-        <v>212.93085054777492</v>
+        <v>553.63518038790414</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10854,16 +10854,16 @@
         <v>452</v>
       </c>
       <c r="Y27" t="s">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="Z27" t="s">
         <v>593</v>
       </c>
       <c r="AA27">
-        <v>0.99295357769237991</v>
+        <v>0.99539558382203508</v>
       </c>
       <c r="AB27">
-        <v>129.18440897303603</v>
+        <v>84.414296596023817</v>
       </c>
       <c r="AD27" t="s">
         <v>417</v>
@@ -10893,13 +10893,13 @@
         <v>777</v>
       </c>
       <c r="AN27" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="AO27">
-        <v>0.99617615910816915</v>
+        <v>0.99310873310996184</v>
       </c>
       <c r="AP27">
-        <v>70.103749683564772</v>
+        <v>126.33989298403215</v>
       </c>
       <c r="AR27" t="s">
         <v>417</v>
@@ -10926,16 +10926,16 @@
         <v>868</v>
       </c>
       <c r="BA27" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="BB27" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="BC27">
-        <v>0.98730637899749651</v>
+        <v>0.98605138538291048</v>
       </c>
       <c r="BD27">
-        <v>232.71638504589731</v>
+        <v>914.54062141820793</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -11000,16 +11000,16 @@
         <v>454</v>
       </c>
       <c r="Y28" t="s">
-        <v>358</v>
+        <v>406</v>
       </c>
       <c r="Z28" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="AA28">
-        <v>0.99696751363483405</v>
+        <v>0.99670408962762203</v>
       </c>
       <c r="AB28">
-        <v>55.595583361375894</v>
+        <v>60.425023493595695</v>
       </c>
       <c r="AD28" t="s">
         <v>417</v>
@@ -11039,13 +11039,13 @@
         <v>778</v>
       </c>
       <c r="AN28" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="AO28">
-        <v>0.99611612132862803</v>
+        <v>0.99715437961127318</v>
       </c>
       <c r="AP28">
-        <v>71.204442308486065</v>
+        <v>52.169707126657627</v>
       </c>
       <c r="AR28" t="s">
         <v>417</v>
@@ -11072,16 +11072,16 @@
         <v>870</v>
       </c>
       <c r="BA28" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="BB28" t="s">
-        <v>603</v>
+        <v>904</v>
       </c>
       <c r="BC28">
-        <v>0.98809190602642238</v>
+        <v>0.98158890816872557</v>
       </c>
       <c r="BD28">
-        <v>218.31505618225569</v>
+        <v>968.90846881102618</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11146,16 +11146,16 @@
         <v>456</v>
       </c>
       <c r="Y29" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="Z29" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="AA29">
-        <v>0.98964014500078279</v>
+        <v>0.9960389195261472</v>
       </c>
       <c r="AB29">
-        <v>189.93067498564957</v>
+        <v>72.619808687301173</v>
       </c>
       <c r="AD29" t="s">
         <v>417</v>
@@ -11185,13 +11185,13 @@
         <v>779</v>
       </c>
       <c r="AN29" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AO29">
-        <v>0.99761105057437038</v>
+        <v>0.9950502580620818</v>
       </c>
       <c r="AP29">
-        <v>43.797406136543607</v>
+        <v>90.745268861833736</v>
       </c>
       <c r="AR29" t="s">
         <v>417</v>
@@ -11218,16 +11218,16 @@
         <v>872</v>
       </c>
       <c r="BA29" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="BB29" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="BC29">
-        <v>0.994208528887633</v>
+        <v>0.98402494782096717</v>
       </c>
       <c r="BD29">
-        <v>106.17697039339514</v>
+        <v>939.22938571455006</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11292,16 +11292,16 @@
         <v>458</v>
       </c>
       <c r="Y30" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="Z30" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AA30">
-        <v>0.9966137462997855</v>
+        <v>0.99707957985864093</v>
       </c>
       <c r="AB30">
-        <v>62.081317837266766</v>
+        <v>53.541035924916123</v>
       </c>
       <c r="AD30" t="s">
         <v>417</v>
@@ -11331,13 +11331,13 @@
         <v>780</v>
       </c>
       <c r="AN30" t="s">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="AO30">
-        <v>0.99615289372526561</v>
+        <v>0.99533901157332205</v>
       </c>
       <c r="AP30">
-        <v>70.530281703464368</v>
+        <v>85.451454489096079</v>
       </c>
       <c r="AR30" t="s">
         <v>417</v>
@@ -11364,16 +11364,16 @@
         <v>874</v>
       </c>
       <c r="BA30" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="BB30" t="s">
-        <v>812</v>
+        <v>581</v>
       </c>
       <c r="BC30">
-        <v>0.98389167860462323</v>
+        <v>0.99223982078870177</v>
       </c>
       <c r="BD30">
-        <v>295.31922558190735</v>
+        <v>745.81270727705794</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11438,16 +11438,16 @@
         <v>460</v>
       </c>
       <c r="Y31" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="Z31" t="s">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="AA31">
-        <v>0.99011796851295664</v>
+        <v>0.99478609753984348</v>
       </c>
       <c r="AB31">
-        <v>181.17057726246117</v>
+        <v>95.588211769535249</v>
       </c>
       <c r="AD31" t="s">
         <v>417</v>
@@ -11477,13 +11477,13 @@
         <v>781</v>
       </c>
       <c r="AN31" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="AO31">
-        <v>0.99418244113372889</v>
+        <v>0.99754339130519476</v>
       </c>
       <c r="AP31">
-        <v>106.6552458816375</v>
+        <v>45.037826071429087</v>
       </c>
       <c r="AR31" t="s">
         <v>417</v>
@@ -11510,16 +11510,16 @@
         <v>876</v>
       </c>
       <c r="BA31" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="BB31" t="s">
-        <v>906</v>
+        <v>613</v>
       </c>
       <c r="BC31">
-        <v>0.98137594918937099</v>
+        <v>0.98838558997012138</v>
       </c>
       <c r="BD31">
-        <v>341.44093152819772</v>
+        <v>886.10222886402141</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11584,16 +11584,16 @@
         <v>462</v>
       </c>
       <c r="Y32" t="s">
-        <v>394</v>
+        <v>348</v>
       </c>
       <c r="Z32" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA32">
-        <v>0.99635118654529808</v>
+        <v>0.99568525132868968</v>
       </c>
       <c r="AB32">
-        <v>66.894913336202478</v>
+        <v>79.10372564068922</v>
       </c>
       <c r="AD32" t="s">
         <v>417</v>
@@ -11623,13 +11623,13 @@
         <v>782</v>
       </c>
       <c r="AN32" t="s">
-        <v>783</v>
+        <v>588</v>
       </c>
       <c r="AO32">
-        <v>0.99206751173516827</v>
+        <v>0.99542398891280204</v>
       </c>
       <c r="AP32">
-        <v>145.42895152191466</v>
+        <v>83.893536598629126</v>
       </c>
       <c r="AR32" t="s">
         <v>417</v>
@@ -11656,16 +11656,16 @@
         <v>878</v>
       </c>
       <c r="BA32" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="BB32" t="s">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="BC32">
-        <v>0.9889956676941275</v>
+        <v>0.98730637899749651</v>
       </c>
       <c r="BD32">
-        <v>201.74609227432916</v>
+        <v>899.25061588050085</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11730,16 +11730,16 @@
         <v>464</v>
       </c>
       <c r="Y33" t="s">
-        <v>393</v>
+        <v>345</v>
       </c>
       <c r="Z33" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AA33">
-        <v>0.99440507690252466</v>
+        <v>0.99590266392783655</v>
       </c>
       <c r="AB33">
-        <v>102.57359012038077</v>
+        <v>75.117827989662302</v>
       </c>
       <c r="AD33" t="s">
         <v>417</v>
@@ -11766,16 +11766,16 @@
         <v>668</v>
       </c>
       <c r="AM33" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AN33" t="s">
-        <v>785</v>
+        <v>590</v>
       </c>
       <c r="AO33">
-        <v>0.99566554346996428</v>
+        <v>0.99617615910816915</v>
       </c>
       <c r="AP33">
-        <v>79.46503638398778</v>
+        <v>70.103749683564772</v>
       </c>
       <c r="AR33" t="s">
         <v>417</v>
@@ -11802,16 +11802,16 @@
         <v>880</v>
       </c>
       <c r="BA33" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="BB33" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="BC33">
-        <v>0.99193721244794397</v>
+        <v>0.98809190602642238</v>
       </c>
       <c r="BD33">
-        <v>147.81777178769397</v>
+        <v>889.68027824475359</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11876,16 +11876,16 @@
         <v>466</v>
       </c>
       <c r="Y34" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="Z34" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA34">
-        <v>0.99551989204648861</v>
+        <v>0.99449671322390631</v>
       </c>
       <c r="AB34">
-        <v>82.135312481041623</v>
+        <v>100.89359089505045</v>
       </c>
       <c r="AD34" t="s">
         <v>417</v>
@@ -11912,16 +11912,16 @@
         <v>670</v>
       </c>
       <c r="AM34" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AN34" t="s">
-        <v>590</v>
+        <v>785</v>
       </c>
       <c r="AO34">
-        <v>0.99667664296701652</v>
+        <v>0.99584476105827657</v>
       </c>
       <c r="AP34">
-        <v>60.928212271363194</v>
+        <v>76.179380598263194</v>
       </c>
       <c r="AR34" t="s">
         <v>417</v>
@@ -11948,16 +11948,16 @@
         <v>882</v>
       </c>
       <c r="BA34" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="BB34" t="s">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="BC34">
-        <v>0.99308209783432144</v>
+        <v>0.994208528887633</v>
       </c>
       <c r="BD34">
-        <v>126.82820637077275</v>
+        <v>620.86536659822605</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -12022,16 +12022,16 @@
         <v>468</v>
       </c>
       <c r="Y35" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="Z35" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="AA35">
-        <v>0.9979392050107273</v>
+        <v>0.99701127670202949</v>
       </c>
       <c r="AB35">
-        <v>37.781241469999252</v>
+        <v>54.793260462791778</v>
       </c>
       <c r="AD35" t="s">
         <v>417</v>
@@ -12058,16 +12058,16 @@
         <v>672</v>
       </c>
       <c r="AM35" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AN35" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="AO35">
-        <v>0.99608442334318104</v>
+        <v>0.9961146125371938</v>
       </c>
       <c r="AP35">
-        <v>71.785572041680055</v>
+        <v>71.232103484781334</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -12132,16 +12132,16 @@
         <v>470</v>
       </c>
       <c r="Y36" t="s">
-        <v>357</v>
+        <v>407</v>
       </c>
       <c r="Z36" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="AA36">
-        <v>0.9982033297630386</v>
+        <v>0.99675394464629852</v>
       </c>
       <c r="AB36">
-        <v>32.938954344292306</v>
+        <v>59.511014817860868</v>
       </c>
       <c r="AD36" t="s">
         <v>417</v>
@@ -12168,16 +12168,16 @@
         <v>674</v>
       </c>
       <c r="AM36" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AN36" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="AO36">
-        <v>0.9967907157363165</v>
+        <v>0.99607298561021362</v>
       </c>
       <c r="AP36">
-        <v>58.836878167530941</v>
+        <v>71.995263812749926</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12242,16 +12242,16 @@
         <v>472</v>
       </c>
       <c r="Y37" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="Z37" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AA37">
-        <v>0.99769372286934066</v>
+        <v>0.9962437778559039</v>
       </c>
       <c r="AB37">
-        <v>42.281747395421668</v>
+        <v>68.86407264176249</v>
       </c>
       <c r="AD37" t="s">
         <v>417</v>
@@ -12278,16 +12278,16 @@
         <v>676</v>
       </c>
       <c r="AM37" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AN37" t="s">
-        <v>790</v>
+        <v>608</v>
       </c>
       <c r="AO37">
-        <v>0.99443964677468366</v>
+        <v>0.9929182563937401</v>
       </c>
       <c r="AP37">
-        <v>101.93980913079895</v>
+        <v>129.83196611476453</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12352,16 +12352,16 @@
         <v>474</v>
       </c>
       <c r="Y38" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="Z38" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="AA38">
-        <v>0.99569491323214321</v>
+        <v>0.99617006411660358</v>
       </c>
       <c r="AB38">
-        <v>78.926590744041093</v>
+        <v>70.215491195600634</v>
       </c>
       <c r="AD38" t="s">
         <v>417</v>
@@ -12388,16 +12388,16 @@
         <v>678</v>
       </c>
       <c r="AM38" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="AN38" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="AO38">
-        <v>0.99761003390352465</v>
+        <v>0.99628542339510884</v>
       </c>
       <c r="AP38">
-        <v>43.816045102048356</v>
+        <v>68.100571089671959</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12462,16 +12462,16 @@
         <v>476</v>
       </c>
       <c r="Y39" t="s">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="Z39" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AA39">
-        <v>0.99484118006716937</v>
+        <v>0.99462937148232844</v>
       </c>
       <c r="AB39">
-        <v>94.578365435227795</v>
+        <v>98.461522823979266</v>
       </c>
       <c r="AD39" t="s">
         <v>417</v>
@@ -12498,16 +12498,16 @@
         <v>680</v>
       </c>
       <c r="AM39" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="AN39" t="s">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="AO39">
-        <v>0.99777413567568085</v>
+        <v>0.99418244113372889</v>
       </c>
       <c r="AP39">
-        <v>40.807512612516987</v>
+        <v>106.6552458816375</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12572,16 +12572,16 @@
         <v>478</v>
       </c>
       <c r="Y40" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="Z40" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="AA40">
-        <v>0.99539558382203508</v>
+        <v>0.99462643269733408</v>
       </c>
       <c r="AB40">
-        <v>84.414296596023817</v>
+        <v>98.51540054887441</v>
       </c>
       <c r="AD40" t="s">
         <v>417</v>
@@ -12608,16 +12608,16 @@
         <v>682</v>
       </c>
       <c r="AM40" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="AN40" t="s">
-        <v>597</v>
+        <v>775</v>
       </c>
       <c r="AO40">
-        <v>0.99568571110966864</v>
+        <v>0.99206751173516827</v>
       </c>
       <c r="AP40">
-        <v>79.095296322741547</v>
+        <v>145.42895152191466</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12682,16 +12682,16 @@
         <v>480</v>
       </c>
       <c r="Y41" t="s">
-        <v>400</v>
+        <v>365</v>
       </c>
       <c r="Z41" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="AA41">
-        <v>0.99282834435956602</v>
+        <v>0.99755789282691543</v>
       </c>
       <c r="AB41">
-        <v>131.48035340795542</v>
+        <v>44.77196483988353</v>
       </c>
       <c r="AD41" t="s">
         <v>417</v>
@@ -12718,16 +12718,16 @@
         <v>684</v>
       </c>
       <c r="AM41" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="AN41" t="s">
-        <v>589</v>
+        <v>793</v>
       </c>
       <c r="AO41">
-        <v>0.99609062270337045</v>
+        <v>0.99566554346996428</v>
       </c>
       <c r="AP41">
-        <v>71.671917104874566</v>
+        <v>79.46503638398778</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12792,16 +12792,16 @@
         <v>482</v>
       </c>
       <c r="Y42" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="Z42" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="AA42">
-        <v>0.99569310304523451</v>
+        <v>0.99246356041150996</v>
       </c>
       <c r="AB42">
-        <v>78.959777504033639</v>
+        <v>138.16805912231732</v>
       </c>
       <c r="AD42" t="s">
         <v>417</v>
@@ -12828,16 +12828,16 @@
         <v>686</v>
       </c>
       <c r="AM42" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AN42" t="s">
-        <v>796</v>
+        <v>580</v>
       </c>
       <c r="AO42">
-        <v>0.99598588086244633</v>
+        <v>0.99667664296701652</v>
       </c>
       <c r="AP42">
-        <v>73.592184188484865</v>
+        <v>60.928212271363194</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12902,16 +12902,16 @@
         <v>484</v>
       </c>
       <c r="Y43" t="s">
-        <v>414</v>
+        <v>344</v>
       </c>
       <c r="Z43" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="AA43">
-        <v>0.99502431999137919</v>
+        <v>0.99571525957109708</v>
       </c>
       <c r="AB43">
-        <v>91.220800158047325</v>
+        <v>78.553574529886689</v>
       </c>
       <c r="AD43" t="s">
         <v>417</v>
@@ -12938,16 +12938,16 @@
         <v>688</v>
       </c>
       <c r="AM43" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="AN43" t="s">
-        <v>578</v>
+        <v>614</v>
       </c>
       <c r="AO43">
-        <v>0.99368259233234391</v>
+        <v>0.99608442334318104</v>
       </c>
       <c r="AP43">
-        <v>115.81914057369519</v>
+        <v>71.785572041680055</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -13012,16 +13012,16 @@
         <v>486</v>
       </c>
       <c r="Y44" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="Z44" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="AA44">
-        <v>0.99584577617815018</v>
+        <v>0.99553579843385909</v>
       </c>
       <c r="AB44">
-        <v>76.16077006724673</v>
+        <v>81.84369537924907</v>
       </c>
       <c r="AD44" t="s">
         <v>417</v>
@@ -13048,16 +13048,16 @@
         <v>690</v>
       </c>
       <c r="AM44" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="AN44" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="AO44">
-        <v>0.9954443722844073</v>
+        <v>0.9967907157363165</v>
       </c>
       <c r="AP44">
-        <v>83.519841452532361</v>
+        <v>58.836878167530941</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13122,16 +13122,16 @@
         <v>488</v>
       </c>
       <c r="Y45" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="Z45" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AA45">
-        <v>0.99699505644961572</v>
+        <v>0.99734372305564056</v>
       </c>
       <c r="AB45">
-        <v>55.090631757044932</v>
+        <v>48.698410646589842</v>
       </c>
       <c r="AD45" t="s">
         <v>417</v>
@@ -13158,16 +13158,16 @@
         <v>692</v>
       </c>
       <c r="AM45" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="AN45" t="s">
-        <v>623</v>
+        <v>798</v>
       </c>
       <c r="AO45">
-        <v>0.99363040616365128</v>
+        <v>0.99443964677468366</v>
       </c>
       <c r="AP45">
-        <v>116.77588699972566</v>
+        <v>101.93980913079895</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13232,16 +13232,16 @@
         <v>490</v>
       </c>
       <c r="Y46" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="Z46" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="AA46">
-        <v>0.99170691261633115</v>
+        <v>0.99662670467221526</v>
       </c>
       <c r="AB46">
-        <v>152.03993536726261</v>
+        <v>61.843747676054292</v>
       </c>
       <c r="AD46" t="s">
         <v>417</v>
@@ -13268,16 +13268,16 @@
         <v>694</v>
       </c>
       <c r="AM46" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AN46" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="AO46">
-        <v>0.99782402570187057</v>
+        <v>0.99761003390352465</v>
       </c>
       <c r="AP46">
-        <v>39.892862132373601</v>
+        <v>43.816045102048356</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13342,16 +13342,16 @@
         <v>492</v>
       </c>
       <c r="Y47" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="Z47" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="AA47">
-        <v>0.9904035062850528</v>
+        <v>0.99740761205901929</v>
       </c>
       <c r="AB47">
-        <v>175.93571810736526</v>
+        <v>47.527112251312907</v>
       </c>
       <c r="AD47" t="s">
         <v>417</v>
@@ -13378,16 +13378,16 @@
         <v>696</v>
       </c>
       <c r="AM47" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AN47" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AO47">
-        <v>0.99756462867082185</v>
+        <v>0.99777413567568085</v>
       </c>
       <c r="AP47">
-        <v>44.648474368267038</v>
+        <v>40.807512612516987</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13452,16 +13452,16 @@
         <v>494</v>
       </c>
       <c r="Y48" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="Z48" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="AA48">
-        <v>0.99125780375299366</v>
+        <v>0.99730769203227776</v>
       </c>
       <c r="AB48">
-        <v>160.27359786178269</v>
+        <v>49.358979408241737</v>
       </c>
       <c r="AD48" t="s">
         <v>417</v>
@@ -13488,16 +13488,16 @@
         <v>698</v>
       </c>
       <c r="AM48" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AN48" t="s">
-        <v>803</v>
+        <v>604</v>
       </c>
       <c r="AO48">
-        <v>0.99474825047892679</v>
+        <v>0.99611612132862803</v>
       </c>
       <c r="AP48">
-        <v>96.282074553009053</v>
+        <v>71.204442308486065</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13562,16 +13562,16 @@
         <v>496</v>
       </c>
       <c r="Y49" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="Z49" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="AA49">
-        <v>0.99619006668481902</v>
+        <v>0.998073964784436</v>
       </c>
       <c r="AB49">
-        <v>69.848777444984194</v>
+        <v>35.310645618673441</v>
       </c>
       <c r="AD49" t="s">
         <v>417</v>
@@ -13598,16 +13598,16 @@
         <v>700</v>
       </c>
       <c r="AM49" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="AN49" t="s">
-        <v>805</v>
+        <v>590</v>
       </c>
       <c r="AO49">
-        <v>0.99684527597966854</v>
+        <v>0.99761105057437038</v>
       </c>
       <c r="AP49">
-        <v>57.836607039410005</v>
+        <v>43.797406136543607</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13672,16 +13672,16 @@
         <v>498</v>
       </c>
       <c r="Y50" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="Z50" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AA50">
-        <v>0.99021813732178554</v>
+        <v>0.99282834435956602</v>
       </c>
       <c r="AB50">
-        <v>179.3341491005981</v>
+        <v>131.48035340795542</v>
       </c>
       <c r="AD50" t="s">
         <v>417</v>
@@ -13708,16 +13708,16 @@
         <v>702</v>
       </c>
       <c r="AM50" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="AN50" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="AO50">
-        <v>0.9943927545810437</v>
+        <v>0.99615289372526561</v>
       </c>
       <c r="AP50">
-        <v>102.79949934753229</v>
+        <v>70.530281703464368</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13782,16 +13782,16 @@
         <v>500</v>
       </c>
       <c r="Y51" t="s">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="Z51" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AA51">
-        <v>0.99686736582623381</v>
+        <v>0.99569310304523451</v>
       </c>
       <c r="AB51">
-        <v>57.431626519047455</v>
+        <v>78.959777504033639</v>
       </c>
       <c r="AD51" t="s">
         <v>417</v>
@@ -13818,16 +13818,16 @@
         <v>704</v>
       </c>
       <c r="AM51" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="AN51" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="AO51">
-        <v>0.99074948308423383</v>
+        <v>0.99474825047892679</v>
       </c>
       <c r="AP51">
-        <v>169.59281012238051</v>
+        <v>96.282074553009053</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13892,16 +13892,16 @@
         <v>502</v>
       </c>
       <c r="Y52" t="s">
-        <v>383</v>
+        <v>414</v>
       </c>
       <c r="Z52" t="s">
-        <v>608</v>
+        <v>581</v>
       </c>
       <c r="AA52">
-        <v>0.99725672762159434</v>
+        <v>0.99502431999137919</v>
       </c>
       <c r="AB52">
-        <v>50.29332693743671</v>
+        <v>91.220800158047325</v>
       </c>
       <c r="AD52" t="s">
         <v>417</v>
@@ -13928,16 +13928,16 @@
         <v>706</v>
       </c>
       <c r="AM52" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="AN52" t="s">
-        <v>606</v>
+        <v>807</v>
       </c>
       <c r="AO52">
-        <v>0.99270401267208797</v>
+        <v>0.99684527597966854</v>
       </c>
       <c r="AP52">
-        <v>133.75976767838793</v>
+        <v>57.836607039410005</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -14002,16 +14002,16 @@
         <v>504</v>
       </c>
       <c r="Y53" t="s">
-        <v>350</v>
+        <v>405</v>
       </c>
       <c r="Z53" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="AA53">
-        <v>0.99478609753984348</v>
+        <v>0.99584577617815018</v>
       </c>
       <c r="AB53">
-        <v>95.588211769535249</v>
+        <v>76.16077006724673</v>
       </c>
       <c r="AD53" t="s">
         <v>417</v>
@@ -14038,16 +14038,16 @@
         <v>708</v>
       </c>
       <c r="AM53" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="AN53" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="AO53">
-        <v>0.99764772442226368</v>
+        <v>0.9943927545810437</v>
       </c>
       <c r="AP53">
-        <v>43.125052258499352</v>
+        <v>102.79949934753229</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -14112,16 +14112,16 @@
         <v>506</v>
       </c>
       <c r="Y54" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="Z54" t="s">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="AA54">
-        <v>0.99568525132868968</v>
+        <v>0.99699505644961572</v>
       </c>
       <c r="AB54">
-        <v>79.10372564068922</v>
+        <v>55.090631757044932</v>
       </c>
       <c r="AD54" t="s">
         <v>417</v>
@@ -14148,16 +14148,16 @@
         <v>710</v>
       </c>
       <c r="AM54" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="AN54" t="s">
-        <v>812</v>
+        <v>618</v>
       </c>
       <c r="AO54">
-        <v>0.99703044337128366</v>
+        <v>0.99368259233234391</v>
       </c>
       <c r="AP54">
-        <v>54.441871526466279</v>
+        <v>115.81914057369519</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -14222,16 +14222,16 @@
         <v>508</v>
       </c>
       <c r="Y55" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="Z55" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="AA55">
-        <v>0.99590266392783655</v>
+        <v>0.99170691261633115</v>
       </c>
       <c r="AB55">
-        <v>75.117827989662302</v>
+        <v>152.03993536726261</v>
       </c>
       <c r="AD55" t="s">
         <v>417</v>
@@ -14258,16 +14258,16 @@
         <v>712</v>
       </c>
       <c r="AM55" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="AN55" t="s">
-        <v>767</v>
+        <v>581</v>
       </c>
       <c r="AO55">
-        <v>0.99584476105827657</v>
+        <v>0.9954443722844073</v>
       </c>
       <c r="AP55">
-        <v>76.179380598263194</v>
+        <v>83.519841452532361</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14332,16 +14332,16 @@
         <v>510</v>
       </c>
       <c r="Y56" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="Z56" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="AA56">
-        <v>0.99449671322390631</v>
+        <v>0.9904035062850528</v>
       </c>
       <c r="AB56">
-        <v>100.89359089505045</v>
+        <v>175.93571810736526</v>
       </c>
       <c r="AD56" t="s">
         <v>417</v>
@@ -14368,16 +14368,16 @@
         <v>714</v>
       </c>
       <c r="AM56" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="AN56" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AO56">
-        <v>0.9961146125371938</v>
+        <v>0.99363040616365128</v>
       </c>
       <c r="AP56">
-        <v>71.232103484781334</v>
+        <v>116.77588699972566</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14442,16 +14442,16 @@
         <v>512</v>
       </c>
       <c r="Y57" t="s">
-        <v>377</v>
+        <v>340</v>
       </c>
       <c r="Z57" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="AA57">
-        <v>0.99701127670202949</v>
+        <v>0.99551989204648861</v>
       </c>
       <c r="AB57">
-        <v>54.793260462791778</v>
+        <v>82.135312481041623</v>
       </c>
       <c r="AD57" t="s">
         <v>417</v>
@@ -14478,16 +14478,16 @@
         <v>716</v>
       </c>
       <c r="AM57" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="AN57" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="AO57">
-        <v>0.99607298561021362</v>
+        <v>0.99782402570187057</v>
       </c>
       <c r="AP57">
-        <v>71.995263812749926</v>
+        <v>39.892862132373601</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14552,16 +14552,16 @@
         <v>514</v>
       </c>
       <c r="Y58" t="s">
-        <v>407</v>
+        <v>359</v>
       </c>
       <c r="Z58" t="s">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="AA58">
-        <v>0.99675394464629852</v>
+        <v>0.9979392050107273</v>
       </c>
       <c r="AB58">
-        <v>59.511014817860868</v>
+        <v>37.781241469999252</v>
       </c>
       <c r="AD58" t="s">
         <v>417</v>
@@ -14588,16 +14588,16 @@
         <v>718</v>
       </c>
       <c r="AM58" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="AN58" t="s">
-        <v>615</v>
+        <v>590</v>
       </c>
       <c r="AO58">
-        <v>0.9929182563937401</v>
+        <v>0.99756462867082185</v>
       </c>
       <c r="AP58">
-        <v>129.83196611476453</v>
+        <v>44.648474368267038</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14662,16 +14662,16 @@
         <v>516</v>
       </c>
       <c r="Y59" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="Z59" t="s">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="AA59">
-        <v>0.9962437778559039</v>
+        <v>0.9982033297630386</v>
       </c>
       <c r="AB59">
-        <v>68.86407264176249</v>
+        <v>32.938954344292306</v>
       </c>
       <c r="AD59" t="s">
         <v>417</v>
@@ -14698,16 +14698,16 @@
         <v>720</v>
       </c>
       <c r="AM59" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="AN59" t="s">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="AO59">
-        <v>0.99628542339510884</v>
+        <v>0.99720397512579328</v>
       </c>
       <c r="AP59">
-        <v>68.100571089671959</v>
+        <v>51.260456027123361</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14772,16 +14772,16 @@
         <v>518</v>
       </c>
       <c r="Y60" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Z60" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="AA60">
-        <v>0.99617006411660358</v>
+        <v>0.99769372286934066</v>
       </c>
       <c r="AB60">
-        <v>70.215491195600634</v>
+        <v>42.281747395421668</v>
       </c>
       <c r="AD60" t="s">
         <v>417</v>
@@ -14808,16 +14808,16 @@
         <v>722</v>
       </c>
       <c r="AM60" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="AN60" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="AO60">
-        <v>0.99660391553167893</v>
+        <v>0.99565348329230585</v>
       </c>
       <c r="AP60">
-        <v>62.261548585886977</v>
+        <v>79.686139641060379</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14882,16 +14882,16 @@
         <v>520</v>
       </c>
       <c r="Y61" t="s">
-        <v>406</v>
+        <v>339</v>
       </c>
       <c r="Z61" t="s">
-        <v>588</v>
+        <v>607</v>
       </c>
       <c r="AA61">
-        <v>0.99670408962762203</v>
+        <v>0.99359748433922845</v>
       </c>
       <c r="AB61">
-        <v>60.425023493595695</v>
+        <v>117.37945378081078</v>
       </c>
       <c r="AD61" t="s">
         <v>417</v>
@@ -14918,16 +14918,16 @@
         <v>724</v>
       </c>
       <c r="AM61" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="AN61" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="AO61">
-        <v>0.9959136876641268</v>
+        <v>0.99568571110966864</v>
       </c>
       <c r="AP61">
-        <v>74.915726157675209</v>
+        <v>79.095296322741547</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14992,16 +14992,16 @@
         <v>522</v>
       </c>
       <c r="Y62" t="s">
-        <v>361</v>
+        <v>409</v>
       </c>
       <c r="Z62" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="AA62">
-        <v>0.9960389195261472</v>
+        <v>0.99592552983543692</v>
       </c>
       <c r="AB62">
-        <v>72.619808687301173</v>
+        <v>74.698619683656872</v>
       </c>
       <c r="AD62" t="s">
         <v>417</v>
@@ -15028,16 +15028,16 @@
         <v>726</v>
       </c>
       <c r="AM62" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="AN62" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="AO62">
-        <v>0.9935275292913992</v>
+        <v>0.99609062270337045</v>
       </c>
       <c r="AP62">
-        <v>118.66196299101547</v>
+        <v>71.671917104874566</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -15102,16 +15102,16 @@
         <v>524</v>
       </c>
       <c r="Y63" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="Z63" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="AA63">
-        <v>0.99707957985864093</v>
+        <v>0.99463677905825021</v>
       </c>
       <c r="AB63">
-        <v>53.541035924916123</v>
+        <v>98.325717265413417</v>
       </c>
       <c r="AD63" t="s">
         <v>417</v>
@@ -15138,16 +15138,16 @@
         <v>728</v>
       </c>
       <c r="AM63" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="AN63" t="s">
-        <v>600</v>
+        <v>819</v>
       </c>
       <c r="AO63">
-        <v>0.99687120387267125</v>
+        <v>0.99598588086244633</v>
       </c>
       <c r="AP63">
-        <v>57.361262334360205</v>
+        <v>73.592184188484865</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -15212,16 +15212,16 @@
         <v>526</v>
       </c>
       <c r="Y64" t="s">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="Z64" t="s">
-        <v>614</v>
+        <v>590</v>
       </c>
       <c r="AA64">
-        <v>0.99359748433922845</v>
+        <v>0.99667564038633161</v>
       </c>
       <c r="AB64">
-        <v>117.37945378081078</v>
+        <v>60.946592917253042</v>
       </c>
       <c r="AD64" t="s">
         <v>417</v>
@@ -15248,16 +15248,16 @@
         <v>730</v>
       </c>
       <c r="AM64" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="AN64" t="s">
-        <v>587</v>
+        <v>613</v>
       </c>
       <c r="AO64">
-        <v>0.99245794727704639</v>
+        <v>0.99660391553167893</v>
       </c>
       <c r="AP64">
-        <v>138.27096658748206</v>
+        <v>62.261548585886977</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -15322,16 +15322,16 @@
         <v>528</v>
       </c>
       <c r="Y65" t="s">
-        <v>409</v>
+        <v>366</v>
       </c>
       <c r="Z65" t="s">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="AA65">
-        <v>0.99592552983543692</v>
+        <v>0.99125780375299366</v>
       </c>
       <c r="AB65">
-        <v>74.698619683656872</v>
+        <v>160.27359786178269</v>
       </c>
       <c r="AD65" t="s">
         <v>417</v>
@@ -15358,16 +15358,16 @@
         <v>732</v>
       </c>
       <c r="AM65" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AN65" t="s">
-        <v>783</v>
+        <v>578</v>
       </c>
       <c r="AO65">
-        <v>0.99381230463557813</v>
+        <v>0.9959136876641268</v>
       </c>
       <c r="AP65">
-        <v>113.44108168106689</v>
+        <v>74.915726157675209</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15432,16 +15432,16 @@
         <v>530</v>
       </c>
       <c r="Y66" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="Z66" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="AA66">
-        <v>0.99463677905825021</v>
+        <v>0.99619006668481902</v>
       </c>
       <c r="AB66">
-        <v>98.325717265413417</v>
+        <v>69.848777444984194</v>
       </c>
       <c r="AD66" t="s">
         <v>417</v>
@@ -15468,16 +15468,16 @@
         <v>734</v>
       </c>
       <c r="AM66" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="AN66" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="AO66">
-        <v>0.99534539864304916</v>
+        <v>0.9935275292913992</v>
       </c>
       <c r="AP66">
-        <v>85.3343582107656</v>
+        <v>118.66196299101547</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15542,16 +15542,16 @@
         <v>532</v>
       </c>
       <c r="Y67" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="Z67" t="s">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="AA67">
-        <v>0.99667564038633161</v>
+        <v>0.99021813732178554</v>
       </c>
       <c r="AB67">
-        <v>60.946592917253042</v>
+        <v>179.3341491005981</v>
       </c>
       <c r="AD67" t="s">
         <v>417</v>
@@ -15578,16 +15578,16 @@
         <v>736</v>
       </c>
       <c r="AM67" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="AN67" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="AO67">
-        <v>0.99310873310996184</v>
+        <v>0.99687120387267125</v>
       </c>
       <c r="AP67">
-        <v>126.33989298403215</v>
+        <v>57.361262334360205</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15652,16 +15652,16 @@
         <v>534</v>
       </c>
       <c r="Y68" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
       <c r="Z68" t="s">
-        <v>616</v>
+        <v>592</v>
       </c>
       <c r="AA68">
-        <v>0.99080344458411729</v>
+        <v>0.99686736582623381</v>
       </c>
       <c r="AB68">
-        <v>168.60351595784994</v>
+        <v>57.431626519047455</v>
       </c>
       <c r="AD68" t="s">
         <v>417</v>
@@ -15688,16 +15688,16 @@
         <v>738</v>
       </c>
       <c r="AM68" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="AN68" t="s">
-        <v>588</v>
+        <v>825</v>
       </c>
       <c r="AO68">
-        <v>0.99715437961127318</v>
+        <v>0.99618121233373258</v>
       </c>
       <c r="AP68">
-        <v>52.169707126657627</v>
+        <v>70.011107214903078</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -15762,16 +15762,16 @@
         <v>536</v>
       </c>
       <c r="Y69" t="s">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="Z69" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="AA69">
-        <v>0.98636012609964985</v>
+        <v>0.99725672762159434</v>
       </c>
       <c r="AB69">
-        <v>250.06435483975247</v>
+        <v>50.29332693743671</v>
       </c>
       <c r="AD69" t="s">
         <v>417</v>
@@ -15798,16 +15798,16 @@
         <v>740</v>
       </c>
       <c r="AM69" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AN69" t="s">
-        <v>591</v>
+        <v>617</v>
       </c>
       <c r="AO69">
-        <v>0.9950502580620818</v>
+        <v>0.99592364356186902</v>
       </c>
       <c r="AP69">
-        <v>90.745268861833736</v>
+        <v>74.733201365734146</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -15872,16 +15872,16 @@
         <v>538</v>
       </c>
       <c r="Y70" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="Z70" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="AA70">
-        <v>0.99598850450039844</v>
+        <v>0.99579357955795456</v>
       </c>
       <c r="AB70">
-        <v>73.544084159361034</v>
+        <v>77.117708104165573</v>
       </c>
       <c r="AD70" t="s">
         <v>417</v>
@@ -15908,16 +15908,16 @@
         <v>742</v>
       </c>
       <c r="AM70" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AN70" t="s">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="AO70">
-        <v>0.99425851119451991</v>
+        <v>0.99641167752379312</v>
       </c>
       <c r="AP70">
-        <v>105.26062810046888</v>
+        <v>65.785912063792665</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -15982,16 +15982,16 @@
         <v>540</v>
       </c>
       <c r="Y71" t="s">
-        <v>412</v>
+        <v>368</v>
       </c>
       <c r="Z71" t="s">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="AA71">
-        <v>0.99310312827752323</v>
+        <v>0.99066346416517681</v>
       </c>
       <c r="AB71">
-        <v>126.44264824540761</v>
+        <v>171.16982363842584</v>
       </c>
       <c r="AD71" t="s">
         <v>417</v>
@@ -16018,16 +16018,16 @@
         <v>744</v>
       </c>
       <c r="AM71" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AN71" t="s">
-        <v>590</v>
+        <v>785</v>
       </c>
       <c r="AO71">
-        <v>0.99712282780353001</v>
+        <v>0.99540934349034305</v>
       </c>
       <c r="AP71">
-        <v>52.74815693528295</v>
+        <v>84.162036010377406</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -16092,16 +16092,16 @@
         <v>542</v>
       </c>
       <c r="Y72" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="Z72" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="AA72">
-        <v>0.99462937148232844</v>
+        <v>0.99560939477262078</v>
       </c>
       <c r="AB72">
-        <v>98.461522823979266</v>
+        <v>80.494429168619106</v>
       </c>
       <c r="AD72" t="s">
         <v>417</v>
@@ -16128,16 +16128,16 @@
         <v>746</v>
       </c>
       <c r="AM72" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AN72" t="s">
-        <v>621</v>
+        <v>581</v>
       </c>
       <c r="AO72">
-        <v>0.99005506097810436</v>
+        <v>0.99657664224037934</v>
       </c>
       <c r="AP72">
-        <v>182.32388206808599</v>
+        <v>62.761558926379031</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16202,16 +16202,16 @@
         <v>544</v>
       </c>
       <c r="Y73" t="s">
-        <v>408</v>
+        <v>342</v>
       </c>
       <c r="Z73" t="s">
-        <v>588</v>
+        <v>615</v>
       </c>
       <c r="AA73">
-        <v>0.99462643269733408</v>
+        <v>0.99544039231362502</v>
       </c>
       <c r="AB73">
-        <v>98.51540054887441</v>
+        <v>83.592807583541571</v>
       </c>
       <c r="AD73" t="s">
         <v>417</v>
@@ -16238,16 +16238,16 @@
         <v>748</v>
       </c>
       <c r="AM73" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="AN73" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="AO73">
-        <v>0.99631269816920021</v>
+        <v>0.99091245964276031</v>
       </c>
       <c r="AP73">
-        <v>67.600533564663479</v>
+        <v>166.60490654939525</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -16312,16 +16312,16 @@
         <v>546</v>
       </c>
       <c r="Y74" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="Z74" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="AA74">
-        <v>0.99755789282691543</v>
+        <v>0.99190124970484694</v>
       </c>
       <c r="AB74">
-        <v>44.77196483988353</v>
+        <v>148.47708874447352</v>
       </c>
       <c r="AD74" t="s">
         <v>417</v>
@@ -16348,16 +16348,16 @@
         <v>750</v>
       </c>
       <c r="AM74" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AN74" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AO74">
-        <v>0.99772400077475298</v>
+        <v>0.99846230399777702</v>
       </c>
       <c r="AP74">
-        <v>41.726652462862774</v>
+        <v>28.191093374087806</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -16422,16 +16422,16 @@
         <v>548</v>
       </c>
       <c r="Y75" t="s">
-        <v>380</v>
+        <v>415</v>
       </c>
       <c r="Z75" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="AA75">
-        <v>0.99246356041150996</v>
+        <v>0.9940089461809174</v>
       </c>
       <c r="AB75">
-        <v>138.16805912231732</v>
+        <v>109.83598668318054</v>
       </c>
       <c r="AD75" t="s">
         <v>417</v>
@@ -16458,16 +16458,16 @@
         <v>752</v>
       </c>
       <c r="AM75" t="s">
+        <v>832</v>
+      </c>
+      <c r="AN75" t="s">
         <v>833</v>
       </c>
-      <c r="AN75" t="s">
-        <v>812</v>
-      </c>
       <c r="AO75">
-        <v>0.99604673274056554</v>
+        <v>0.99439150850611324</v>
       </c>
       <c r="AP75">
-        <v>72.476566422965192</v>
+        <v>102.82234405458999</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -16532,16 +16532,16 @@
         <v>550</v>
       </c>
       <c r="Y76" t="s">
-        <v>338</v>
+        <v>396</v>
       </c>
       <c r="Z76" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AA76">
-        <v>0.99578350963230966</v>
+        <v>0.99600761890991041</v>
       </c>
       <c r="AB76">
-        <v>77.302323407656075</v>
+        <v>73.193653318309615</v>
       </c>
       <c r="AD76" t="s">
         <v>417</v>
@@ -16571,13 +16571,13 @@
         <v>834</v>
       </c>
       <c r="AN76" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="AO76">
-        <v>0.99720397512579328</v>
+        <v>0.99595416313893737</v>
       </c>
       <c r="AP76">
-        <v>51.260456027123361</v>
+        <v>74.173675786148877</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -16642,16 +16642,16 @@
         <v>552</v>
       </c>
       <c r="Y77" t="s">
-        <v>410</v>
+        <v>355</v>
       </c>
       <c r="Z77" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="AA77">
-        <v>0.99720191150310689</v>
+        <v>0.99700029739711071</v>
       </c>
       <c r="AB77">
-        <v>51.298289109706943</v>
+        <v>54.994547719637801</v>
       </c>
       <c r="AD77" t="s">
         <v>417</v>
@@ -16681,13 +16681,13 @@
         <v>835</v>
       </c>
       <c r="AN77" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="AO77">
-        <v>0.99565348329230585</v>
+        <v>0.99687821505939955</v>
       </c>
       <c r="AP77">
-        <v>79.686139641060379</v>
+        <v>57.232723911007447</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -16752,16 +16752,16 @@
         <v>554</v>
       </c>
       <c r="Y78" t="s">
-        <v>404</v>
+        <v>363</v>
       </c>
       <c r="Z78" t="s">
-        <v>612</v>
+        <v>590</v>
       </c>
       <c r="AA78">
-        <v>0.9954551465796494</v>
+        <v>0.99408511741207395</v>
       </c>
       <c r="AB78">
-        <v>83.32231270642734</v>
+        <v>108.43951411197776</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -16826,16 +16826,16 @@
         <v>556</v>
       </c>
       <c r="Y79" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="Z79" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="AA79">
-        <v>0.99552053983611355</v>
+        <v>0.99529948277209723</v>
       </c>
       <c r="AB79">
-        <v>82.123436337918946</v>
+        <v>86.176149178218239</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -16900,16 +16900,16 @@
         <v>558</v>
       </c>
       <c r="Y80" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="Z80" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AA80">
-        <v>0.98935435476104872</v>
+        <v>0.99540885392130762</v>
       </c>
       <c r="AB80">
-        <v>195.1701627141077</v>
+        <v>84.171011442693441</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -16974,16 +16974,16 @@
         <v>560</v>
       </c>
       <c r="Y81" t="s">
-        <v>395</v>
+        <v>354</v>
       </c>
       <c r="Z81" t="s">
-        <v>591</v>
+        <v>619</v>
       </c>
       <c r="AA81">
-        <v>0.99775872574768198</v>
+        <v>0.99360802526828129</v>
       </c>
       <c r="AB81">
-        <v>41.090027959164246</v>
+        <v>117.18620341484296</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -17048,16 +17048,16 @@
         <v>562</v>
       </c>
       <c r="Y82" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
       <c r="Z82" t="s">
-        <v>622</v>
+        <v>588</v>
       </c>
       <c r="AA82">
-        <v>0.99571525957109708</v>
+        <v>0.99515679011930902</v>
       </c>
       <c r="AB82">
-        <v>78.553574529886689</v>
+        <v>88.792181146001369</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -17122,16 +17122,16 @@
         <v>564</v>
       </c>
       <c r="Y83" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="Z83" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="AA83">
-        <v>0.99553579843385909</v>
+        <v>0.99409145347725225</v>
       </c>
       <c r="AB83">
-        <v>81.84369537924907</v>
+        <v>108.32335291704148</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -17196,16 +17196,16 @@
         <v>566</v>
       </c>
       <c r="Y84" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="Z84" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="AA84">
-        <v>0.99734372305564056</v>
+        <v>0.99464051280908794</v>
       </c>
       <c r="AB84">
-        <v>48.698410646589842</v>
+        <v>98.257265166721183</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -17270,16 +17270,16 @@
         <v>568</v>
       </c>
       <c r="Y85" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="Z85" t="s">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="AA85">
-        <v>0.99662670467221526</v>
+        <v>0.99080344458411729</v>
       </c>
       <c r="AB85">
-        <v>61.843747676054292</v>
+        <v>168.60351595784994</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -17344,16 +17344,16 @@
         <v>570</v>
       </c>
       <c r="Y86" t="s">
-        <v>364</v>
+        <v>413</v>
       </c>
       <c r="Z86" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="AA86">
-        <v>0.99740761205901929</v>
+        <v>0.98636012609964985</v>
       </c>
       <c r="AB86">
-        <v>47.527112251312907</v>
+        <v>250.06435483975247</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -17418,16 +17418,16 @@
         <v>572</v>
       </c>
       <c r="Y87" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="Z87" t="s">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="AA87">
-        <v>0.99730769203227776</v>
+        <v>0.99598850450039844</v>
       </c>
       <c r="AB87">
-        <v>49.358979408241737</v>
+        <v>73.544084159361034</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -17492,16 +17492,16 @@
         <v>574</v>
       </c>
       <c r="Y88" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="Z88" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="AA88">
-        <v>0.998073964784436</v>
+        <v>0.99310312827752323</v>
       </c>
       <c r="AB88">
-        <v>35.310645618673441</v>
+        <v>126.44264824540761</v>
       </c>
     </row>
   </sheetData>
@@ -17510,7 +17510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BA2C21-464C-4CE8-974C-618640D38619}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5432F551-B2D3-449A-8983-52E3B2B8CE18}">
   <dimension ref="B9:Z77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17622,7 +17622,7 @@
         <v>911</v>
       </c>
       <c r="K11" t="s">
-        <v>815</v>
+        <v>787</v>
       </c>
       <c r="L11">
         <v>29.7146465744454</v>
@@ -17655,7 +17655,7 @@
         <v>1045</v>
       </c>
       <c r="X11" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="Y11">
         <v>0.33825</v>
@@ -17690,7 +17690,7 @@
         <v>913</v>
       </c>
       <c r="K12" t="s">
-        <v>827</v>
+        <v>779</v>
       </c>
       <c r="L12">
         <v>13.367096811591049</v>
@@ -17723,7 +17723,7 @@
         <v>1047</v>
       </c>
       <c r="X12" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="Y12">
         <v>10.88325</v>
@@ -17758,7 +17758,7 @@
         <v>915</v>
       </c>
       <c r="K13" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="L13">
         <v>24.156328337033791</v>
@@ -17791,7 +17791,7 @@
         <v>1049</v>
       </c>
       <c r="X13" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="Y13">
         <v>26.983499999999999</v>
@@ -17826,7 +17826,7 @@
         <v>917</v>
       </c>
       <c r="K14" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="L14">
         <v>16.006796560234815</v>
@@ -17859,7 +17859,7 @@
         <v>1051</v>
       </c>
       <c r="X14" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="Y14">
         <v>42.507750000000001</v>
@@ -17894,7 +17894,7 @@
         <v>919</v>
       </c>
       <c r="K15" t="s">
-        <v>825</v>
+        <v>777</v>
       </c>
       <c r="L15">
         <v>17.682358378036344</v>
@@ -17927,7 +17927,7 @@
         <v>1053</v>
       </c>
       <c r="X15" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="Y15">
         <v>24.900749999999999</v>
@@ -17962,7 +17962,7 @@
         <v>921</v>
       </c>
       <c r="K16" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="L16">
         <v>29.492382648463739</v>
@@ -17995,7 +17995,7 @@
         <v>1055</v>
       </c>
       <c r="X16" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="Y16">
         <v>18.545249999999999</v>
@@ -18030,7 +18030,7 @@
         <v>923</v>
       </c>
       <c r="K17" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="L17">
         <v>8.6778699255653748</v>
@@ -18063,7 +18063,7 @@
         <v>1057</v>
       </c>
       <c r="X17" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="Y17">
         <v>29.838000000000001</v>
@@ -18098,7 +18098,7 @@
         <v>925</v>
       </c>
       <c r="K18" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="L18">
         <v>12.772248157772113</v>
@@ -18131,7 +18131,7 @@
         <v>1059</v>
       </c>
       <c r="X18" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="Y18">
         <v>58.689</v>
@@ -18166,7 +18166,7 @@
         <v>927</v>
       </c>
       <c r="K19" t="s">
-        <v>834</v>
+        <v>814</v>
       </c>
       <c r="L19">
         <v>15.217638427037592</v>
@@ -18199,7 +18199,7 @@
         <v>1061</v>
       </c>
       <c r="X19" t="s">
-        <v>905</v>
+        <v>885</v>
       </c>
       <c r="Y19">
         <v>48.432000000000002</v>
@@ -18234,7 +18234,7 @@
         <v>929</v>
       </c>
       <c r="K20" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="L20">
         <v>3.1385663053565613</v>
@@ -18267,7 +18267,7 @@
         <v>1063</v>
       </c>
       <c r="X20" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="Y20">
         <v>47.794499999999999</v>
@@ -18302,7 +18302,7 @@
         <v>931</v>
       </c>
       <c r="K21" t="s">
-        <v>810</v>
+        <v>771</v>
       </c>
       <c r="L21">
         <v>4.0628682283884237</v>
@@ -18335,7 +18335,7 @@
         <v>1065</v>
       </c>
       <c r="X21" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="Y21">
         <v>7.1767500000000002</v>
@@ -18370,7 +18370,7 @@
         <v>933</v>
       </c>
       <c r="K22" t="s">
-        <v>761</v>
+        <v>835</v>
       </c>
       <c r="L22">
         <v>19.408837136062758</v>
@@ -18403,7 +18403,7 @@
         <v>1067</v>
       </c>
       <c r="X22" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="Y22">
         <v>8.1052499999999998</v>
@@ -18438,7 +18438,7 @@
         <v>935</v>
       </c>
       <c r="K23" t="s">
-        <v>835</v>
+        <v>815</v>
       </c>
       <c r="L23">
         <v>15.054857587707319</v>
@@ -18471,7 +18471,7 @@
         <v>1069</v>
       </c>
       <c r="X23" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="Y23">
         <v>9.3810000000000002</v>
@@ -18506,7 +18506,7 @@
         <v>937</v>
       </c>
       <c r="K24" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="L24">
         <v>13.019602602156084</v>
@@ -18539,7 +18539,7 @@
         <v>1071</v>
       </c>
       <c r="X24" t="s">
-        <v>908</v>
+        <v>888</v>
       </c>
       <c r="Y24">
         <v>11.47575</v>
@@ -18574,7 +18574,7 @@
         <v>939</v>
       </c>
       <c r="K25" t="s">
-        <v>830</v>
+        <v>760</v>
       </c>
       <c r="L25">
         <v>25.094411791551167</v>
@@ -18607,7 +18607,7 @@
         <v>1073</v>
       </c>
       <c r="X25" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="Y25">
         <v>6.1372499999999999</v>
@@ -18642,7 +18642,7 @@
         <v>941</v>
       </c>
       <c r="K26" t="s">
-        <v>779</v>
+        <v>802</v>
       </c>
       <c r="L26">
         <v>18.31221960055294</v>
@@ -18675,7 +18675,7 @@
         <v>1075</v>
       </c>
       <c r="X26" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="Y26">
         <v>14.57325</v>
@@ -18710,7 +18710,7 @@
         <v>943</v>
       </c>
       <c r="K27" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="L27">
         <v>27.91719839668141</v>
@@ -18743,7 +18743,7 @@
         <v>1077</v>
       </c>
       <c r="X27" t="s">
-        <v>907</v>
+        <v>887</v>
       </c>
       <c r="Y27">
         <v>10.491</v>
@@ -18778,7 +18778,7 @@
         <v>945</v>
       </c>
       <c r="K28" t="s">
-        <v>770</v>
+        <v>831</v>
       </c>
       <c r="L28">
         <v>8.5144758814389814</v>
@@ -18811,7 +18811,7 @@
         <v>1079</v>
       </c>
       <c r="X28" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="Y28">
         <v>17.414249999999999</v>
@@ -18846,7 +18846,7 @@
         <v>947</v>
       </c>
       <c r="K29" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="L29">
         <v>12.144708893333986</v>
@@ -18879,7 +18879,7 @@
         <v>1081</v>
       </c>
       <c r="X29" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="Y29">
         <v>10.968</v>
@@ -18914,7 +18914,7 @@
         <v>949</v>
       </c>
       <c r="K30" t="s">
-        <v>831</v>
+        <v>761</v>
       </c>
       <c r="L30">
         <v>1.6724491767694549</v>
@@ -18947,7 +18947,7 @@
         <v>1083</v>
       </c>
       <c r="X30" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="Y30">
         <v>10.79175</v>
@@ -18982,7 +18982,7 @@
         <v>951</v>
       </c>
       <c r="K31" t="s">
-        <v>832</v>
+        <v>762</v>
       </c>
       <c r="L31">
         <v>13.894741632015101</v>
@@ -19015,7 +19015,7 @@
         <v>1085</v>
       </c>
       <c r="X31" t="s">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="Y31">
         <v>20.114249999999998</v>
@@ -19050,7 +19050,7 @@
         <v>953</v>
       </c>
       <c r="K32" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="L32">
         <v>11.876635800692616</v>
@@ -19083,7 +19083,7 @@
         <v>1087</v>
       </c>
       <c r="X32" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="Y32">
         <v>44.373750000000001</v>
@@ -19118,7 +19118,7 @@
         <v>955</v>
       </c>
       <c r="K33" t="s">
-        <v>833</v>
+        <v>763</v>
       </c>
       <c r="L33">
         <v>27.15579263061009</v>
@@ -19151,7 +19151,7 @@
         <v>1089</v>
       </c>
       <c r="X33" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="Y33">
         <v>18.57525</v>
@@ -19186,7 +19186,7 @@
         <v>957</v>
       </c>
       <c r="K34" t="s">
-        <v>816</v>
+        <v>788</v>
       </c>
       <c r="L34">
         <v>27.043339674957092</v>
@@ -19219,7 +19219,7 @@
         <v>1091</v>
       </c>
       <c r="X34" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="Y34">
         <v>18.241499999999998</v>
@@ -19254,7 +19254,7 @@
         <v>959</v>
       </c>
       <c r="K35" t="s">
-        <v>811</v>
+        <v>772</v>
       </c>
       <c r="L35">
         <v>12.170927347824723</v>
@@ -19289,7 +19289,7 @@
         <v>961</v>
       </c>
       <c r="K36" t="s">
-        <v>817</v>
+        <v>789</v>
       </c>
       <c r="L36">
         <v>26.999240466622091</v>
@@ -19324,7 +19324,7 @@
         <v>963</v>
       </c>
       <c r="K37" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="L37">
         <v>23.305350986470582</v>
@@ -19359,7 +19359,7 @@
         <v>965</v>
       </c>
       <c r="K38" t="s">
-        <v>780</v>
+        <v>803</v>
       </c>
       <c r="L38">
         <v>19.293897715957783</v>
@@ -19394,7 +19394,7 @@
         <v>967</v>
       </c>
       <c r="K39" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="L39">
         <v>34.8352470366899</v>
@@ -19429,7 +19429,7 @@
         <v>969</v>
       </c>
       <c r="K40" t="s">
-        <v>795</v>
+        <v>818</v>
       </c>
       <c r="L40">
         <v>22.439012549480047</v>
@@ -19464,7 +19464,7 @@
         <v>971</v>
       </c>
       <c r="K41" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="L41">
         <v>19.571302094407635</v>
@@ -19499,7 +19499,7 @@
         <v>973</v>
       </c>
       <c r="K42" t="s">
-        <v>769</v>
+        <v>830</v>
       </c>
       <c r="L42">
         <v>16.258507759053195</v>
@@ -19534,7 +19534,7 @@
         <v>975</v>
       </c>
       <c r="K43" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="L43">
         <v>48.074816212675138</v>
@@ -19569,7 +19569,7 @@
         <v>977</v>
       </c>
       <c r="K44" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="L44">
         <v>65.59399718970684</v>
@@ -19604,7 +19604,7 @@
         <v>979</v>
       </c>
       <c r="K45" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="L45">
         <v>65.706815294563484</v>
@@ -19639,7 +19639,7 @@
         <v>981</v>
       </c>
       <c r="K46" t="s">
-        <v>760</v>
+        <v>834</v>
       </c>
       <c r="L46">
         <v>13.859521883612567</v>
@@ -19674,7 +19674,7 @@
         <v>983</v>
       </c>
       <c r="K47" t="s">
-        <v>768</v>
+        <v>829</v>
       </c>
       <c r="L47">
         <v>32.682899602232801</v>
@@ -19709,7 +19709,7 @@
         <v>985</v>
       </c>
       <c r="K48" t="s">
-        <v>765</v>
+        <v>827</v>
       </c>
       <c r="L48">
         <v>39.028686646898073</v>
@@ -19744,7 +19744,7 @@
         <v>987</v>
       </c>
       <c r="K49" t="s">
-        <v>826</v>
+        <v>778</v>
       </c>
       <c r="L49">
         <v>25.808486809088087</v>
@@ -19779,7 +19779,7 @@
         <v>989</v>
       </c>
       <c r="K50" t="s">
-        <v>764</v>
+        <v>826</v>
       </c>
       <c r="L50">
         <v>64.703394190718342</v>
@@ -19814,7 +19814,7 @@
         <v>991</v>
       </c>
       <c r="K51" t="s">
-        <v>794</v>
+        <v>817</v>
       </c>
       <c r="L51">
         <v>46.777110562179843</v>
@@ -19849,7 +19849,7 @@
         <v>993</v>
       </c>
       <c r="K52" t="s">
-        <v>824</v>
+        <v>776</v>
       </c>
       <c r="L52">
         <v>83.307298494129057</v>
@@ -19884,7 +19884,7 @@
         <v>995</v>
       </c>
       <c r="K53" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="L53">
         <v>8.0718642408500934</v>
@@ -19919,7 +19919,7 @@
         <v>997</v>
       </c>
       <c r="K54" t="s">
-        <v>823</v>
+        <v>774</v>
       </c>
       <c r="L54">
         <v>25.555956589747868</v>
@@ -19954,7 +19954,7 @@
         <v>999</v>
       </c>
       <c r="K55" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="L55">
         <v>26.74310381624198</v>
@@ -19989,7 +19989,7 @@
         <v>1001</v>
       </c>
       <c r="K56" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="L56">
         <v>47.811917655816522</v>
@@ -20024,7 +20024,7 @@
         <v>1003</v>
       </c>
       <c r="K57" t="s">
-        <v>782</v>
+        <v>791</v>
       </c>
       <c r="L57">
         <v>65.898010391046881</v>
@@ -20059,7 +20059,7 @@
         <v>1005</v>
       </c>
       <c r="K58" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="L58">
         <v>49.914822287456737</v>
@@ -20094,7 +20094,7 @@
         <v>1007</v>
       </c>
       <c r="K59" t="s">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="L59">
         <v>19.963633091222835</v>
@@ -20129,7 +20129,7 @@
         <v>1009</v>
       </c>
       <c r="K60" t="s">
-        <v>807</v>
+        <v>768</v>
       </c>
       <c r="L60">
         <v>71.04376789192942</v>
@@ -20164,7 +20164,7 @@
         <v>1011</v>
       </c>
       <c r="K61" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="L61">
         <v>43.07229279461999</v>
@@ -20199,7 +20199,7 @@
         <v>1013</v>
       </c>
       <c r="K62" t="s">
-        <v>766</v>
+        <v>828</v>
       </c>
       <c r="L62">
         <v>38.769945374969119</v>
@@ -20234,7 +20234,7 @@
         <v>1015</v>
       </c>
       <c r="K63" t="s">
-        <v>758</v>
+        <v>832</v>
       </c>
       <c r="L63">
         <v>59.009737840109466</v>
@@ -20269,7 +20269,7 @@
         <v>1017</v>
       </c>
       <c r="K64" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="L64">
         <v>28.865927665826828</v>
@@ -20304,7 +20304,7 @@
         <v>1019</v>
       </c>
       <c r="K65" t="s">
-        <v>778</v>
+        <v>801</v>
       </c>
       <c r="L65">
         <v>37.976260419426943</v>
@@ -20339,7 +20339,7 @@
         <v>1021</v>
       </c>
       <c r="K66" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="L66">
         <v>44.88386263672971</v>
@@ -20374,7 +20374,7 @@
         <v>1023</v>
       </c>
       <c r="K67" t="s">
-        <v>793</v>
+        <v>816</v>
       </c>
       <c r="L67">
         <v>23.350121881103082</v>
@@ -20409,7 +20409,7 @@
         <v>1025</v>
       </c>
       <c r="K68" t="s">
-        <v>829</v>
+        <v>759</v>
       </c>
       <c r="L68">
         <v>15.289477961960474</v>
@@ -20444,7 +20444,7 @@
         <v>1027</v>
       </c>
       <c r="K69" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="L69">
         <v>10.395885695189069</v>
@@ -20479,7 +20479,7 @@
         <v>1029</v>
       </c>
       <c r="K70" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="L70">
         <v>23.89105636564183</v>
@@ -20514,7 +20514,7 @@
         <v>1031</v>
       </c>
       <c r="K71" t="s">
-        <v>828</v>
+        <v>758</v>
       </c>
       <c r="L71">
         <v>18.959710131684457</v>
@@ -20549,7 +20549,7 @@
         <v>1033</v>
       </c>
       <c r="K72" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="L72">
         <v>6.6550975614073966</v>
@@ -20584,7 +20584,7 @@
         <v>1035</v>
       </c>
       <c r="K73" t="s">
-        <v>814</v>
+        <v>786</v>
       </c>
       <c r="L73">
         <v>13.961943802326671</v>
@@ -20619,7 +20619,7 @@
         <v>1037</v>
       </c>
       <c r="K74" t="s">
-        <v>809</v>
+        <v>770</v>
       </c>
       <c r="L74">
         <v>51.937776653453852</v>
@@ -20654,7 +20654,7 @@
         <v>1039</v>
       </c>
       <c r="K75" t="s">
-        <v>822</v>
+        <v>773</v>
       </c>
       <c r="L75">
         <v>21.246092446368579</v>
@@ -20689,7 +20689,7 @@
         <v>1041</v>
       </c>
       <c r="K76" t="s">
-        <v>762</v>
+        <v>824</v>
       </c>
       <c r="L76">
         <v>19.42059121972445</v>
@@ -20724,7 +20724,7 @@
         <v>1043</v>
       </c>
       <c r="K77" t="s">
-        <v>813</v>
+        <v>784</v>
       </c>
       <c r="L77">
         <v>30.063621105864488</v>
@@ -20739,7 +20739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80C9E26C-C699-430C-BD85-432D2844F234}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4446820A-3517-4025-BD08-D0FF8ABBD467}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -20903,13 +20903,13 @@
         <v>19</v>
       </c>
       <c r="F13">
-        <v>0.58899999999999997</v>
+        <v>2.1204000000000001</v>
       </c>
       <c r="I13">
-        <v>0.54400000000000004</v>
+        <v>1.9583999999999999</v>
       </c>
       <c r="L13">
-        <v>0.497</v>
+        <v>1.7891999999999999</v>
       </c>
       <c r="M13" t="s">
         <v>1097</v>
@@ -21179,13 +21179,13 @@
         <v>19</v>
       </c>
       <c r="F19">
-        <v>1.9279999999999999</v>
+        <v>6.9408000000000003</v>
       </c>
       <c r="I19">
-        <v>1.9279999999999999</v>
+        <v>6.9408000000000003</v>
       </c>
       <c r="L19">
-        <v>1.9279999999999999</v>
+        <v>6.9408000000000003</v>
       </c>
       <c r="M19" t="s">
         <v>1097</v>
@@ -21455,13 +21455,13 @@
         <v>1102</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="H25">
-        <v>0.9</v>
+        <v>3.24</v>
       </c>
       <c r="L25">
-        <v>0.9</v>
+        <v>3.24</v>
       </c>
       <c r="M25" t="s">
         <v>1097</v>
@@ -21479,7 +21479,7 @@
         <v>21</v>
       </c>
       <c r="T25" t="s">
-        <v>421</v>
+        <v>1125</v>
       </c>
       <c r="U25" t="s">
         <v>1122</v>
@@ -21520,7 +21520,7 @@
         <v>21</v>
       </c>
       <c r="T26" t="s">
-        <v>421</v>
+        <v>1125</v>
       </c>
       <c r="U26" t="s">
         <v>1122</v>
@@ -21723,13 +21723,13 @@
         <v>1106</v>
       </c>
       <c r="F33">
-        <v>1.294</v>
+        <v>4.6584000000000003</v>
       </c>
       <c r="I33">
-        <v>1.1060000000000001</v>
+        <v>3.9815999999999998</v>
       </c>
       <c r="L33">
-        <v>0.98899999999999999</v>
+        <v>3.5604</v>
       </c>
       <c r="M33" t="s">
         <v>1097</v>
@@ -21891,13 +21891,13 @@
         <v>19</v>
       </c>
       <c r="F39">
-        <v>2.3610000000000002</v>
+        <v>8.4995999999999992</v>
       </c>
       <c r="I39">
-        <v>2.3610000000000002</v>
+        <v>8.4995999999999992</v>
       </c>
       <c r="L39">
-        <v>2.3610000000000002</v>
+        <v>8.4995999999999992</v>
       </c>
       <c r="M39" t="s">
         <v>1097</v>
@@ -22059,13 +22059,13 @@
         <v>19</v>
       </c>
       <c r="F45">
-        <v>2.5499999999999998</v>
+        <v>9.18</v>
       </c>
       <c r="I45">
-        <v>2.4420000000000002</v>
+        <v>8.7911999999999999</v>
       </c>
       <c r="L45">
-        <v>2.3170000000000002</v>
+        <v>8.3412000000000006</v>
       </c>
       <c r="M45" t="s">
         <v>1097</v>
@@ -22227,13 +22227,13 @@
         <v>19</v>
       </c>
       <c r="F51">
-        <v>2.6389999999999998</v>
+        <v>9.5004000000000008</v>
       </c>
       <c r="I51">
-        <v>2.6389999999999998</v>
+        <v>9.5004000000000008</v>
       </c>
       <c r="L51">
-        <v>2.6389999999999998</v>
+        <v>9.5004000000000008</v>
       </c>
       <c r="M51" t="s">
         <v>1097</v>
@@ -22540,10 +22540,10 @@
         <v>19</v>
       </c>
       <c r="I62">
-        <v>0.77800000000000002</v>
+        <v>2.8008000000000002</v>
       </c>
       <c r="L62">
-        <v>0.77800000000000002</v>
+        <v>2.8008000000000002</v>
       </c>
       <c r="M62" t="s">
         <v>1097</v>
@@ -22694,19 +22694,19 @@
         <v>19</v>
       </c>
       <c r="H67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="I67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="J67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="K67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="L67">
-        <v>0.72199999999999998</v>
+        <v>2.5992000000000002</v>
       </c>
       <c r="M67" t="s">
         <v>1097</v>
@@ -22845,13 +22845,13 @@
         <v>19</v>
       </c>
       <c r="F72">
-        <v>1.4570000000000001</v>
+        <v>5.2451999999999996</v>
       </c>
       <c r="I72">
-        <v>1.4570000000000001</v>
+        <v>5.2451999999999996</v>
       </c>
       <c r="L72">
-        <v>1.4570000000000001</v>
+        <v>5.2451999999999996</v>
       </c>
       <c r="M72" t="s">
         <v>1097</v>
@@ -23036,13 +23036,13 @@
         <v>1102</v>
       </c>
       <c r="E79">
-        <v>0.6</v>
+        <v>2.16</v>
       </c>
       <c r="H79">
-        <v>0.6</v>
+        <v>2.16</v>
       </c>
       <c r="L79">
-        <v>0.6</v>
+        <v>2.16</v>
       </c>
       <c r="M79" t="s">
         <v>1097</v>
@@ -23250,13 +23250,13 @@
         <v>1102</v>
       </c>
       <c r="E87">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="H87">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="L87">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="M87" t="s">
         <v>1097</v>
@@ -23418,13 +23418,13 @@
         <v>1102</v>
       </c>
       <c r="E93">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="H93">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="L93">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="M93" t="s">
         <v>1097</v>
@@ -23533,9 +23533,6 @@
       <c r="B97" t="s">
         <v>1118</v>
       </c>
-      <c r="C97" t="s">
-        <v>19</v>
-      </c>
       <c r="D97" t="s">
         <v>1102</v>
       </c>
@@ -23562,9 +23559,6 @@
       <c r="B98" t="s">
         <v>1118</v>
       </c>
-      <c r="C98" t="s">
-        <v>19</v>
-      </c>
       <c r="D98" t="s">
         <v>1102</v>
       </c>
@@ -23591,26 +23585,23 @@
       <c r="B99" t="s">
         <v>1118</v>
       </c>
-      <c r="C99" t="s">
-        <v>19</v>
-      </c>
       <c r="D99" t="s">
         <v>1102</v>
       </c>
       <c r="G99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="H99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="I99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="J99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="L99">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="M99" t="s">
         <v>1097</v>
@@ -23620,9 +23611,6 @@
       <c r="B100" t="s">
         <v>1118</v>
       </c>
-      <c r="C100" t="s">
-        <v>19</v>
-      </c>
       <c r="D100" t="s">
         <v>1102</v>
       </c>
@@ -23649,9 +23637,6 @@
       <c r="B101" t="s">
         <v>1118</v>
       </c>
-      <c r="C101" t="s">
-        <v>19</v>
-      </c>
       <c r="D101" t="s">
         <v>1102</v>
       </c>
@@ -23687,9 +23672,6 @@
       <c r="B102" t="s">
         <v>1118</v>
       </c>
-      <c r="C102" t="s">
-        <v>19</v>
-      </c>
       <c r="D102" t="s">
         <v>1102</v>
       </c>
@@ -23725,9 +23707,6 @@
       <c r="B103" t="s">
         <v>1119</v>
       </c>
-      <c r="C103" t="s">
-        <v>19</v>
-      </c>
       <c r="D103" t="s">
         <v>1102</v>
       </c>
@@ -23754,9 +23733,6 @@
       <c r="B104" t="s">
         <v>1119</v>
       </c>
-      <c r="C104" t="s">
-        <v>19</v>
-      </c>
       <c r="D104" t="s">
         <v>1102</v>
       </c>
@@ -23783,26 +23759,23 @@
       <c r="B105" t="s">
         <v>1119</v>
       </c>
-      <c r="C105" t="s">
-        <v>19</v>
-      </c>
       <c r="D105" t="s">
         <v>1102</v>
       </c>
       <c r="G105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="H105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="I105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="J105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="L105">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="M105" t="s">
         <v>1097</v>
@@ -23812,9 +23785,6 @@
       <c r="B106" t="s">
         <v>1119</v>
       </c>
-      <c r="C106" t="s">
-        <v>19</v>
-      </c>
       <c r="D106" t="s">
         <v>1102</v>
       </c>
@@ -23841,9 +23811,6 @@
       <c r="B107" t="s">
         <v>1119</v>
       </c>
-      <c r="C107" t="s">
-        <v>19</v>
-      </c>
       <c r="D107" t="s">
         <v>1102</v>
       </c>
@@ -23879,9 +23846,6 @@
       <c r="B108" t="s">
         <v>1119</v>
       </c>
-      <c r="C108" t="s">
-        <v>19</v>
-      </c>
       <c r="D108" t="s">
         <v>1102</v>
       </c>
@@ -24038,28 +24002,28 @@
         <v>1121</v>
       </c>
       <c r="E112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="F112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="G112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="H112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="I112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="J112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="K112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="L112">
-        <v>1.3</v>
+        <v>4.68</v>
       </c>
       <c r="M112" t="s">
         <v>1097</v>

--- a/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CD96F4-628E-4E27-AED8-2D896423BFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94AD716-0BFF-474B-84CA-2533B647FA3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1383,18 +1383,408 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_062</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 62</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_064</t>
   </si>
   <si>
@@ -1437,282 +1827,6 @@
     <t>connecting solar to buses in cluster 56</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_029</t>
   </si>
   <si>
@@ -1743,219 +1857,141 @@
     <t>connecting solar to buses in cluster 46</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND,e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND,e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND,e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_Rajahmundry_IND,e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND,e_Vadodara_IND,e_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND,e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND,e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND,e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND,e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Medinipur_IND,e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND,e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND,e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Vadodara_IND,e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND,e_Phalodi_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND,e_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND,e_Indore_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND,e_Jaipur_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Moga_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Sikandarabad_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Bhuj_IND,e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND,e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Indore_IND</t>
+  </si>
+  <si>
     <t>e_Wardha_IND,e_Solapur_IND</t>
   </si>
   <si>
     <t>e_Solapur_IND,e_Dharmapuri_IND,e_Kurnool_IND</t>
   </si>
   <si>
-    <t>e_Jaipur_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Dharmapuri_IND</t>
-  </si>
-  <si>
     <t>e_Wardha_IND,e_Sikandarabad_IND,e_Korba_IND,e_Fatehpur_IND</t>
   </si>
   <si>
-    <t>e_Rajahmundry_IND,e_Korba_IND</t>
-  </si>
-  <si>
     <t>e_Korba_IND,e_Fatehpur_IND</t>
   </si>
   <si>
     <t>e_Korba_IND,e_Fatehpur_IND,e_Medinipur_IND</t>
   </si>
   <si>
-    <t>e_Bhuj_IND,e_Vadodara_IND</t>
-  </si>
-  <si>
-    <t>e_Dharmapuri_IND,e_Kurnool_IND</t>
-  </si>
-  <si>
-    <t>e_Kurnool_IND,e_Rajahmundry_IND</t>
-  </si>
-  <si>
-    <t>e_Korba_IND,e_Rajahmundry_IND</t>
-  </si>
-  <si>
-    <t>e_Fatehpur_IND</t>
-  </si>
-  <si>
-    <t>e_Phalodi_IND,e_Jaipur_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Korba_IND</t>
-  </si>
-  <si>
-    <t>e_Tezpur_IND</t>
-  </si>
-  <si>
-    <t>e_Sikandarabad_IND,e_Fatehpur_IND</t>
-  </si>
-  <si>
-    <t>e_Moga_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Indore_IND,e_Sikandarabad_IND,e_Jaipur_IND</t>
-  </si>
-  <si>
-    <t>e_Indore_IND,e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Medinipur_IND,e_Fatehpur_IND</t>
-  </si>
-  <si>
-    <t>e_Moga_IND</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND,e_Vadodara_IND,e_Indore_IND</t>
-  </si>
-  <si>
-    <t>e_Kurnool_IND,e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>e_Solapur_IND</t>
-  </si>
-  <si>
-    <t>e_Vadodara_IND,e_Indore_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Kurnool_IND</t>
-  </si>
-  <si>
-    <t>e_Indore_IND,e_Jaipur_IND</t>
-  </si>
-  <si>
-    <t>e_Vadodara_IND,e_Phalodi_IND,e_Jaipur_IND</t>
-  </si>
-  <si>
-    <t>e_Korba_IND,e_Medinipur_IND</t>
-  </si>
-  <si>
     <t>e_Phalodi_IND</t>
   </si>
   <si>
@@ -1965,40 +2001,76 @@
     <t>e_Fatehpur_IND,e_Tezpur_IND</t>
   </si>
   <si>
-    <t>e_Bhuj_IND,e_Vadodara_IND,e_Phalodi_IND</t>
-  </si>
-  <si>
-    <t>e_Bhuj_IND</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>e_Vadodara_IND,e_Indore_IND</t>
-  </si>
-  <si>
-    <t>e_Phalodi_IND,e_Moga_IND</t>
-  </si>
-  <si>
-    <t>e_Solapur_IND,e_Kurnool_IND</t>
-  </si>
-  <si>
-    <t>e_Solapur_IND,e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>e_Sikandarabad_IND,e_Moga_IND</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND,e_Korba_IND</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND,e_Bhuj_IND,e_Vadodara_IND</t>
-  </si>
-  <si>
-    <t>e_Dharmapuri_IND,e_Solapur_IND</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND,e_Indore_IND</t>
+    <t>distr_wonelc_won_IND_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_061</t>
@@ -2037,6 +2109,264 @@
     <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
+    <t>distr_wonelc_won_IND_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_IND_008</t>
   </si>
   <si>
@@ -2055,174 +2385,6 @@
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_IND_055</t>
   </si>
   <si>
@@ -2241,166 +2403,49 @@
     <t>connecting wind onshore to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>elc_won_IND_056</t>
+  </si>
+  <si>
+    <t>e_Indore_IND,e_Jaipur_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_054</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_014</t>
+  </si>
+  <si>
+    <t>elc_won_IND_067</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_063</t>
+  </si>
+  <si>
+    <t>elc_won_IND_001</t>
+  </si>
+  <si>
+    <t>elc_won_IND_024</t>
+  </si>
+  <si>
+    <t>elc_won_IND_026</t>
+  </si>
+  <si>
+    <t>elc_won_IND_052</t>
+  </si>
+  <si>
+    <t>elc_won_IND_037</t>
+  </si>
+  <si>
+    <t>elc_won_IND_032</t>
+  </si>
+  <si>
+    <t>elc_won_IND_018</t>
   </si>
   <si>
     <t>elc_won_IND_061</t>
@@ -2424,6 +2469,156 @@
     <t>e_Medinipur_IND</t>
   </si>
   <si>
+    <t>elc_won_IND_053</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND,e_Vadodara_IND,e_Bhuj_IND,e_Indore_IND,e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_036</t>
+  </si>
+  <si>
+    <t>elc_won_IND_012</t>
+  </si>
+  <si>
+    <t>elc_won_IND_050</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND,e_Wardha_IND,e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_064</t>
+  </si>
+  <si>
+    <t>elc_won_IND_011</t>
+  </si>
+  <si>
+    <t>elc_won_IND_025</t>
+  </si>
+  <si>
+    <t>elc_won_IND_043</t>
+  </si>
+  <si>
+    <t>elc_won_IND_045</t>
+  </si>
+  <si>
+    <t>elc_won_IND_031</t>
+  </si>
+  <si>
+    <t>elc_won_IND_059</t>
+  </si>
+  <si>
+    <t>elc_won_IND_027</t>
+  </si>
+  <si>
+    <t>elc_won_IND_049</t>
+  </si>
+  <si>
+    <t>elc_won_IND_047</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND,e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_035</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Vadodara_IND,e_Indore_IND,e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_062</t>
+  </si>
+  <si>
+    <t>elc_won_IND_033</t>
+  </si>
+  <si>
+    <t>elc_won_IND_060</t>
+  </si>
+  <si>
+    <t>elc_won_IND_010</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND,e_Korba_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_019</t>
+  </si>
+  <si>
+    <t>elc_won_IND_017</t>
+  </si>
+  <si>
+    <t>elc_won_IND_048</t>
+  </si>
+  <si>
+    <t>elc_won_IND_034</t>
+  </si>
+  <si>
+    <t>elc_won_IND_046</t>
+  </si>
+  <si>
+    <t>elc_won_IND_022</t>
+  </si>
+  <si>
+    <t>elc_won_IND_009</t>
+  </si>
+  <si>
+    <t>elc_won_IND_013</t>
+  </si>
+  <si>
+    <t>elc_won_IND_066</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND,e_Phalodi_IND,e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>elc_won_IND_040</t>
+  </si>
+  <si>
+    <t>elc_won_IND_038</t>
+  </si>
+  <si>
+    <t>elc_won_IND_065</t>
+  </si>
+  <si>
+    <t>elc_won_IND_044</t>
+  </si>
+  <si>
+    <t>elc_won_IND_042</t>
+  </si>
+  <si>
+    <t>elc_won_IND_005</t>
+  </si>
+  <si>
+    <t>elc_won_IND_039</t>
+  </si>
+  <si>
+    <t>elc_won_IND_002</t>
+  </si>
+  <si>
+    <t>elc_won_IND_051</t>
+  </si>
+  <si>
+    <t>elc_won_IND_004</t>
+  </si>
+  <si>
+    <t>elc_won_IND_029</t>
+  </si>
+  <si>
+    <t>elc_won_IND_003</t>
+  </si>
+  <si>
+    <t>elc_won_IND_057</t>
+  </si>
+  <si>
+    <t>elc_won_IND_041</t>
+  </si>
+  <si>
+    <t>elc_won_IND_030</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND,e_Kurnool_IND,e_Rajahmundry_IND</t>
+  </si>
+  <si>
     <t>elc_won_IND_008</t>
   </si>
   <si>
@@ -2433,105 +2628,6 @@
     <t>elc_won_IND_006</t>
   </si>
   <si>
-    <t>elc_won_IND_050</t>
-  </si>
-  <si>
-    <t>e_Bhuj_IND,e_Wardha_IND,e_Vadodara_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_064</t>
-  </si>
-  <si>
-    <t>elc_won_IND_011</t>
-  </si>
-  <si>
-    <t>elc_won_IND_025</t>
-  </si>
-  <si>
-    <t>elc_won_IND_065</t>
-  </si>
-  <si>
-    <t>elc_won_IND_044</t>
-  </si>
-  <si>
-    <t>e_Solapur_IND,e_Dharmapuri_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_042</t>
-  </si>
-  <si>
-    <t>elc_won_IND_005</t>
-  </si>
-  <si>
-    <t>elc_won_IND_039</t>
-  </si>
-  <si>
-    <t>elc_won_IND_002</t>
-  </si>
-  <si>
-    <t>elc_won_IND_051</t>
-  </si>
-  <si>
-    <t>elc_won_IND_004</t>
-  </si>
-  <si>
-    <t>elc_won_IND_029</t>
-  </si>
-  <si>
-    <t>elc_won_IND_003</t>
-  </si>
-  <si>
-    <t>elc_won_IND_067</t>
-  </si>
-  <si>
-    <t>e_Phalodi_IND,e_Jaipur_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_063</t>
-  </si>
-  <si>
-    <t>elc_won_IND_001</t>
-  </si>
-  <si>
-    <t>elc_won_IND_024</t>
-  </si>
-  <si>
-    <t>elc_won_IND_026</t>
-  </si>
-  <si>
-    <t>elc_won_IND_049</t>
-  </si>
-  <si>
-    <t>elc_won_IND_047</t>
-  </si>
-  <si>
-    <t>elc_won_IND_035</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND,e_Vadodara_IND,e_Indore_IND,e_Solapur_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_062</t>
-  </si>
-  <si>
-    <t>elc_won_IND_033</t>
-  </si>
-  <si>
-    <t>elc_won_IND_060</t>
-  </si>
-  <si>
-    <t>elc_won_IND_010</t>
-  </si>
-  <si>
-    <t>e_Fatehpur_IND,e_Korba_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_019</t>
-  </si>
-  <si>
-    <t>elc_won_IND_017</t>
-  </si>
-  <si>
     <t>elc_won_IND_055</t>
   </si>
   <si>
@@ -2541,100 +2637,136 @@
     <t>elc_won_IND_028</t>
   </si>
   <si>
-    <t>elc_won_IND_056</t>
-  </si>
-  <si>
-    <t>e_Indore_IND,e_Jaipur_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_054</t>
-  </si>
-  <si>
-    <t>e_Sikandarabad_IND,e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_014</t>
-  </si>
-  <si>
-    <t>elc_won_IND_043</t>
-  </si>
-  <si>
-    <t>elc_won_IND_045</t>
-  </si>
-  <si>
-    <t>elc_won_IND_031</t>
-  </si>
-  <si>
-    <t>elc_won_IND_059</t>
-  </si>
-  <si>
-    <t>elc_won_IND_027</t>
-  </si>
-  <si>
-    <t>elc_won_IND_009</t>
-  </si>
-  <si>
-    <t>elc_won_IND_013</t>
-  </si>
-  <si>
-    <t>elc_won_IND_057</t>
-  </si>
-  <si>
-    <t>elc_won_IND_041</t>
-  </si>
-  <si>
-    <t>elc_won_IND_030</t>
-  </si>
-  <si>
-    <t>e_Dharmapuri_IND,e_Kurnool_IND,e_Rajahmundry_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_048</t>
-  </si>
-  <si>
-    <t>elc_won_IND_034</t>
-  </si>
-  <si>
-    <t>elc_won_IND_046</t>
-  </si>
-  <si>
-    <t>elc_won_IND_022</t>
-  </si>
-  <si>
-    <t>elc_won_IND_066</t>
-  </si>
-  <si>
-    <t>e_Jaipur_IND,e_Phalodi_IND,e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_040</t>
-  </si>
-  <si>
-    <t>elc_won_IND_038</t>
-  </si>
-  <si>
-    <t>elc_won_IND_052</t>
-  </si>
-  <si>
-    <t>elc_won_IND_037</t>
-  </si>
-  <si>
-    <t>elc_won_IND_032</t>
-  </si>
-  <si>
-    <t>elc_won_IND_018</t>
-  </si>
-  <si>
-    <t>elc_won_IND_053</t>
-  </si>
-  <si>
-    <t>e_Phalodi_IND,e_Vadodara_IND,e_Bhuj_IND,e_Indore_IND,e_Jaipur_IND</t>
-  </si>
-  <si>
-    <t>elc_won_IND_036</t>
-  </si>
-  <si>
-    <t>elc_won_IND_012</t>
+    <t>distr_wofelc_wof_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_004</t>
@@ -2643,223 +2775,91 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_021</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
+    <t>elc_wof_IND_002</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_013</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_023</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_010</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_011</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND,e_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_003</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_016</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>e_Bhuj_IND,e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_014</t>
   </si>
   <si>
     <t>elc_wof_IND_004</t>
   </si>
   <si>
-    <t>elc_wof_IND_009</t>
-  </si>
-  <si>
-    <t>e_Bhuj_IND,e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_014</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_002</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_015</t>
-  </si>
-  <si>
     <t>elc_wof_IND_021</t>
   </si>
   <si>
     <t>e_Rajahmundry_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_010</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_018</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_013</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_023</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_011</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND,e_Bhuj_IND</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_003</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_016</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_024</t>
   </si>
   <si>
     <t>e_won_IND_001</t>
@@ -8280,7 +8280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFA3D80-4287-46A1-914D-71857FDD2C91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731C0CD3-DBC0-4022-B7E0-696A31CBAF6C}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -8518,16 +8518,16 @@
         <v>418</v>
       </c>
       <c r="Y11" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="Z11" t="s">
         <v>578</v>
       </c>
       <c r="AA11">
-        <v>0.99557960200072415</v>
+        <v>0.99670408962762203</v>
       </c>
       <c r="AB11">
-        <v>81.040629986723459</v>
+        <v>60.425023493595695</v>
       </c>
       <c r="AD11" t="s">
         <v>417</v>
@@ -8557,13 +8557,13 @@
         <v>758</v>
       </c>
       <c r="AN11" t="s">
-        <v>595</v>
+        <v>759</v>
       </c>
       <c r="AO11">
-        <v>0.99425851119451991</v>
+        <v>0.99474825047892679</v>
       </c>
       <c r="AP11">
-        <v>105.26062810046888</v>
+        <v>96.282074553009053</v>
       </c>
       <c r="AR11" t="s">
         <v>417</v>
@@ -8593,13 +8593,13 @@
         <v>884</v>
       </c>
       <c r="BB11" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="BC11">
-        <v>0.98734896749216872</v>
+        <v>0.97123008268954114</v>
       </c>
       <c r="BD11">
-        <v>898.7317460537439</v>
+        <v>1095.1134925657575</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8664,16 +8664,16 @@
         <v>422</v>
       </c>
       <c r="Y12" t="s">
-        <v>401</v>
+        <v>361</v>
       </c>
       <c r="Z12" t="s">
         <v>579</v>
       </c>
       <c r="AA12">
-        <v>0.99295357769237991</v>
+        <v>0.9960389195261472</v>
       </c>
       <c r="AB12">
-        <v>129.18440897303603</v>
+        <v>72.619808687301173</v>
       </c>
       <c r="AD12" t="s">
         <v>417</v>
@@ -8700,16 +8700,16 @@
         <v>626</v>
       </c>
       <c r="AM12" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AN12" t="s">
-        <v>580</v>
+        <v>761</v>
       </c>
       <c r="AO12">
-        <v>0.99712282780353001</v>
+        <v>0.99684527597966854</v>
       </c>
       <c r="AP12">
-        <v>52.74815693528295</v>
+        <v>57.836607039410005</v>
       </c>
       <c r="AR12" t="s">
         <v>417</v>
@@ -8739,13 +8739,13 @@
         <v>885</v>
       </c>
       <c r="BB12" t="s">
-        <v>886</v>
+        <v>596</v>
       </c>
       <c r="BC12">
-        <v>0.98137594918937099</v>
+        <v>0.99307601382667698</v>
       </c>
       <c r="BD12">
-        <v>971.50301904282946</v>
+        <v>692.74232246689905</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8810,16 +8810,16 @@
         <v>424</v>
       </c>
       <c r="Y13" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="Z13" t="s">
         <v>580</v>
       </c>
       <c r="AA13">
-        <v>0.99696751363483405</v>
+        <v>0.99707957985864093</v>
       </c>
       <c r="AB13">
-        <v>55.595583361375894</v>
+        <v>53.541035924916123</v>
       </c>
       <c r="AD13" t="s">
         <v>417</v>
@@ -8846,16 +8846,16 @@
         <v>628</v>
       </c>
       <c r="AM13" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="AN13" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="AO13">
-        <v>0.99005506097810436</v>
+        <v>0.9943927545810437</v>
       </c>
       <c r="AP13">
-        <v>182.32388206808599</v>
+        <v>102.79949934753229</v>
       </c>
       <c r="AR13" t="s">
         <v>417</v>
@@ -8882,16 +8882,16 @@
         <v>840</v>
       </c>
       <c r="BA13" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="BB13" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="BC13">
-        <v>0.9889956676941275</v>
+        <v>0.99275904397179515</v>
       </c>
       <c r="BD13">
-        <v>878.66944859321336</v>
+        <v>712.85934259006547</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8956,16 +8956,16 @@
         <v>426</v>
       </c>
       <c r="Y14" t="s">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="Z14" t="s">
         <v>581</v>
       </c>
       <c r="AA14">
-        <v>0.98964014500078279</v>
+        <v>0.99551989204648861</v>
       </c>
       <c r="AB14">
-        <v>189.93067498564957</v>
+        <v>82.135312481041623</v>
       </c>
       <c r="AD14" t="s">
         <v>417</v>
@@ -8992,16 +8992,16 @@
         <v>630</v>
       </c>
       <c r="AM14" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="AN14" t="s">
-        <v>584</v>
+        <v>764</v>
       </c>
       <c r="AO14">
-        <v>0.99631269816920021</v>
+        <v>0.99584476105827657</v>
       </c>
       <c r="AP14">
-        <v>67.600533564663479</v>
+        <v>76.179380598263194</v>
       </c>
       <c r="AR14" t="s">
         <v>417</v>
@@ -9028,16 +9028,16 @@
         <v>842</v>
       </c>
       <c r="BA14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="BB14" t="s">
-        <v>581</v>
+        <v>779</v>
       </c>
       <c r="BC14">
-        <v>0.99193721244794397</v>
+        <v>0.98389167860462323</v>
       </c>
       <c r="BD14">
-        <v>765.01824997048959</v>
+        <v>940.85304900034021</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9102,16 +9102,16 @@
         <v>428</v>
       </c>
       <c r="Y15" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="Z15" t="s">
         <v>582</v>
       </c>
       <c r="AA15">
-        <v>0.9966137462997855</v>
+        <v>0.9979392050107273</v>
       </c>
       <c r="AB15">
-        <v>62.081317837266766</v>
+        <v>37.781241469999252</v>
       </c>
       <c r="AD15" t="s">
         <v>417</v>
@@ -9138,16 +9138,16 @@
         <v>632</v>
       </c>
       <c r="AM15" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="AN15" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="AO15">
-        <v>0.99772400077475298</v>
+        <v>0.9961146125371938</v>
       </c>
       <c r="AP15">
-        <v>41.726652462862774</v>
+        <v>71.232103484781334</v>
       </c>
       <c r="AR15" t="s">
         <v>417</v>
@@ -9174,16 +9174,16 @@
         <v>844</v>
       </c>
       <c r="BA15" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="BB15" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="BC15">
-        <v>0.97123008268954114</v>
+        <v>0.96206044130113966</v>
       </c>
       <c r="BD15">
-        <v>1095.1134925657575</v>
+        <v>1206.8302901477819</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9248,16 +9248,16 @@
         <v>430</v>
       </c>
       <c r="Y16" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="Z16" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AA16">
-        <v>0.99011796851295664</v>
+        <v>0.9982033297630386</v>
       </c>
       <c r="AB16">
-        <v>181.17057726246117</v>
+        <v>32.938954344292306</v>
       </c>
       <c r="AD16" t="s">
         <v>417</v>
@@ -9284,16 +9284,16 @@
         <v>634</v>
       </c>
       <c r="AM16" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="AN16" t="s">
-        <v>764</v>
+        <v>579</v>
       </c>
       <c r="AO16">
-        <v>0.99604673274056554</v>
+        <v>0.99607298561021362</v>
       </c>
       <c r="AP16">
-        <v>72.476566422965192</v>
+        <v>71.995263812749926</v>
       </c>
       <c r="AR16" t="s">
         <v>417</v>
@@ -9320,16 +9320,16 @@
         <v>846</v>
       </c>
       <c r="BA16" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="BB16" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="BC16">
-        <v>0.99603877136023145</v>
+        <v>0.98742179529179352</v>
       </c>
       <c r="BD16">
-        <v>504.70597767064743</v>
+        <v>897.84446069498176</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9394,16 +9394,16 @@
         <v>432</v>
       </c>
       <c r="Y17" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="Z17" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AA17">
-        <v>0.99635118654529808</v>
+        <v>0.99769372286934066</v>
       </c>
       <c r="AB17">
-        <v>66.894913336202478</v>
+        <v>42.281747395421668</v>
       </c>
       <c r="AD17" t="s">
         <v>417</v>
@@ -9430,16 +9430,16 @@
         <v>636</v>
       </c>
       <c r="AM17" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="AN17" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="AO17">
-        <v>0.99784941409648109</v>
+        <v>0.9929182563937401</v>
       </c>
       <c r="AP17">
-        <v>39.427408231180806</v>
+        <v>129.83196611476453</v>
       </c>
       <c r="AR17" t="s">
         <v>417</v>
@@ -9466,16 +9466,16 @@
         <v>848</v>
       </c>
       <c r="BA17" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="BB17" t="s">
-        <v>892</v>
+        <v>578</v>
       </c>
       <c r="BC17">
-        <v>0.99308209783432144</v>
+        <v>0.99526782804010661</v>
       </c>
       <c r="BD17">
-        <v>692.35619078172965</v>
+        <v>553.63518038790414</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9540,16 +9540,16 @@
         <v>434</v>
       </c>
       <c r="Y18" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="Z18" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AA18">
-        <v>0.99440507690252466</v>
+        <v>0.99540885392130762</v>
       </c>
       <c r="AB18">
-        <v>102.57359012038077</v>
+        <v>84.171011442693441</v>
       </c>
       <c r="AD18" t="s">
         <v>417</v>
@@ -9576,16 +9576,16 @@
         <v>638</v>
       </c>
       <c r="AM18" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AN18" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AO18">
-        <v>0.99831921281104818</v>
+        <v>0.99628542339510884</v>
       </c>
       <c r="AP18">
-        <v>30.814431797450247</v>
+        <v>68.100571089671959</v>
       </c>
       <c r="AR18" t="s">
         <v>417</v>
@@ -9612,16 +9612,16 @@
         <v>850</v>
       </c>
       <c r="BA18" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="BB18" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="BC18">
-        <v>0.98154438143849254</v>
+        <v>0.98605138538291048</v>
       </c>
       <c r="BD18">
-        <v>969.45095280769931</v>
+        <v>914.54062141820793</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9686,16 +9686,16 @@
         <v>436</v>
       </c>
       <c r="Y19" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="Z19" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AA19">
-        <v>0.99578350963230966</v>
+        <v>0.99360802526828129</v>
       </c>
       <c r="AB19">
-        <v>77.302323407656075</v>
+        <v>117.18620341484296</v>
       </c>
       <c r="AD19" t="s">
         <v>417</v>
@@ -9722,16 +9722,16 @@
         <v>640</v>
       </c>
       <c r="AM19" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="AN19" t="s">
-        <v>594</v>
+        <v>764</v>
       </c>
       <c r="AO19">
-        <v>0.99845356202909108</v>
+        <v>0.99540934349034305</v>
       </c>
       <c r="AP19">
-        <v>28.351362799997673</v>
+        <v>84.162036010377406</v>
       </c>
       <c r="AR19" t="s">
         <v>417</v>
@@ -9758,16 +9758,16 @@
         <v>852</v>
       </c>
       <c r="BA19" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="BB19" t="s">
-        <v>613</v>
+        <v>578</v>
       </c>
       <c r="BC19">
-        <v>0.98787195157138663</v>
+        <v>0.99603877136023145</v>
       </c>
       <c r="BD19">
-        <v>892.36005668860651</v>
+        <v>504.70597767064743</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9832,16 +9832,16 @@
         <v>438</v>
       </c>
       <c r="Y20" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="Z20" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AA20">
-        <v>0.99720191150310689</v>
+        <v>0.99515679011930902</v>
       </c>
       <c r="AB20">
-        <v>51.298289109706943</v>
+        <v>88.792181146001369</v>
       </c>
       <c r="AD20" t="s">
         <v>417</v>
@@ -9868,16 +9868,16 @@
         <v>642</v>
       </c>
       <c r="AM20" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AN20" t="s">
-        <v>769</v>
+        <v>578</v>
       </c>
       <c r="AO20">
-        <v>0.99074948308423383</v>
+        <v>0.99657664224037934</v>
       </c>
       <c r="AP20">
-        <v>169.59281012238051</v>
+        <v>62.761558926379031</v>
       </c>
       <c r="AR20" t="s">
         <v>417</v>
@@ -9904,16 +9904,16 @@
         <v>854</v>
       </c>
       <c r="BA20" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="BB20" t="s">
-        <v>614</v>
+        <v>590</v>
       </c>
       <c r="BC20">
-        <v>0.98853599644984702</v>
+        <v>0.98154438143849254</v>
       </c>
       <c r="BD20">
-        <v>884.26977658603062</v>
+        <v>969.45095280769931</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9978,16 +9978,16 @@
         <v>440</v>
       </c>
       <c r="Y21" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="Z21" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AA21">
-        <v>0.9954551465796494</v>
+        <v>0.99409145347725225</v>
       </c>
       <c r="AB21">
-        <v>83.32231270642734</v>
+        <v>108.32335291704148</v>
       </c>
       <c r="AD21" t="s">
         <v>417</v>
@@ -10014,16 +10014,16 @@
         <v>644</v>
       </c>
       <c r="AM21" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN21" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="AO21">
-        <v>0.99270401267208797</v>
+        <v>0.99091245964276031</v>
       </c>
       <c r="AP21">
-        <v>133.75976767838793</v>
+        <v>166.60490654939525</v>
       </c>
       <c r="AR21" t="s">
         <v>417</v>
@@ -10050,16 +10050,16 @@
         <v>856</v>
       </c>
       <c r="BA21" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="BB21" t="s">
-        <v>587</v>
+        <v>895</v>
       </c>
       <c r="BC21">
-        <v>0.99307601382667698</v>
+        <v>0.98158890816872557</v>
       </c>
       <c r="BD21">
-        <v>692.74232246689905</v>
+        <v>968.90846881102618</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10124,16 +10124,16 @@
         <v>442</v>
       </c>
       <c r="Y22" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="Z22" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AA22">
-        <v>0.99552053983611355</v>
+        <v>0.99464051280908794</v>
       </c>
       <c r="AB22">
-        <v>82.123436337918946</v>
+        <v>98.257265166721183</v>
       </c>
       <c r="AD22" t="s">
         <v>417</v>
@@ -10160,16 +10160,16 @@
         <v>646</v>
       </c>
       <c r="AM22" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AN22" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="AO22">
-        <v>0.99764772442226368</v>
+        <v>0.99846230399777702</v>
       </c>
       <c r="AP22">
-        <v>43.125052258499352</v>
+        <v>28.191093374087806</v>
       </c>
       <c r="AR22" t="s">
         <v>417</v>
@@ -10196,16 +10196,16 @@
         <v>858</v>
       </c>
       <c r="BA22" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="BB22" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="BC22">
-        <v>0.99275904397179515</v>
+        <v>0.98402494782096717</v>
       </c>
       <c r="BD22">
-        <v>712.85934259006547</v>
+        <v>939.22938571455006</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10270,16 +10270,16 @@
         <v>444</v>
       </c>
       <c r="Y23" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="Z23" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AA23">
-        <v>0.98935435476104872</v>
+        <v>0.99579357955795456</v>
       </c>
       <c r="AB23">
-        <v>195.1701627141077</v>
+        <v>77.117708104165573</v>
       </c>
       <c r="AD23" t="s">
         <v>417</v>
@@ -10306,16 +10306,16 @@
         <v>648</v>
       </c>
       <c r="AM23" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AN23" t="s">
-        <v>764</v>
+        <v>610</v>
       </c>
       <c r="AO23">
-        <v>0.99703044337128366</v>
+        <v>0.99425851119451991</v>
       </c>
       <c r="AP23">
-        <v>54.441871526466279</v>
+        <v>105.26062810046888</v>
       </c>
       <c r="AR23" t="s">
         <v>417</v>
@@ -10342,16 +10342,16 @@
         <v>860</v>
       </c>
       <c r="BA23" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="BB23" t="s">
-        <v>764</v>
+        <v>578</v>
       </c>
       <c r="BC23">
-        <v>0.98389167860462323</v>
+        <v>0.99223982078870177</v>
       </c>
       <c r="BD23">
-        <v>940.85304900034021</v>
+        <v>745.81270727705794</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10416,16 +10416,16 @@
         <v>446</v>
       </c>
       <c r="Y24" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="Z24" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AA24">
-        <v>0.99775872574768198</v>
+        <v>0.99066346416517681</v>
       </c>
       <c r="AB24">
-        <v>41.090027959164246</v>
+        <v>171.16982363842584</v>
       </c>
       <c r="AD24" t="s">
         <v>417</v>
@@ -10452,16 +10452,16 @@
         <v>650</v>
       </c>
       <c r="AM24" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AN24" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="AO24">
-        <v>0.99245794727704639</v>
+        <v>0.99712282780353001</v>
       </c>
       <c r="AP24">
-        <v>138.27096658748206</v>
+        <v>52.74815693528295</v>
       </c>
       <c r="AR24" t="s">
         <v>417</v>
@@ -10488,16 +10488,16 @@
         <v>862</v>
       </c>
       <c r="BA24" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="BB24" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="BC24">
-        <v>0.96206044130113966</v>
+        <v>0.98838558997012138</v>
       </c>
       <c r="BD24">
-        <v>1206.8302901477819</v>
+        <v>886.10222886402141</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10562,16 +10562,16 @@
         <v>448</v>
       </c>
       <c r="Y25" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="Z25" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AA25">
-        <v>0.99569491323214321</v>
+        <v>0.99560939477262078</v>
       </c>
       <c r="AB25">
-        <v>78.926590744041093</v>
+        <v>80.494429168619106</v>
       </c>
       <c r="AD25" t="s">
         <v>417</v>
@@ -10598,16 +10598,16 @@
         <v>652</v>
       </c>
       <c r="AM25" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AN25" t="s">
-        <v>775</v>
+        <v>599</v>
       </c>
       <c r="AO25">
-        <v>0.99381230463557813</v>
+        <v>0.99005506097810436</v>
       </c>
       <c r="AP25">
-        <v>113.44108168106689</v>
+        <v>182.32388206808599</v>
       </c>
       <c r="AR25" t="s">
         <v>417</v>
@@ -10634,16 +10634,16 @@
         <v>864</v>
       </c>
       <c r="BA25" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="BB25" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="BC25">
-        <v>0.98742179529179352</v>
+        <v>0.98730637899749651</v>
       </c>
       <c r="BD25">
-        <v>897.84446069498176</v>
+        <v>899.25061588050085</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10708,16 +10708,16 @@
         <v>450</v>
       </c>
       <c r="Y26" t="s">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="Z26" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AA26">
-        <v>0.99484118006716937</v>
+        <v>0.99544039231362502</v>
       </c>
       <c r="AB26">
-        <v>94.578365435227795</v>
+        <v>83.592807583541571</v>
       </c>
       <c r="AD26" t="s">
         <v>417</v>
@@ -10747,13 +10747,13 @@
         <v>776</v>
       </c>
       <c r="AN26" t="s">
-        <v>579</v>
+        <v>619</v>
       </c>
       <c r="AO26">
-        <v>0.99534539864304916</v>
+        <v>0.99631269816920021</v>
       </c>
       <c r="AP26">
-        <v>85.3343582107656</v>
+        <v>67.600533564663479</v>
       </c>
       <c r="AR26" t="s">
         <v>417</v>
@@ -10780,16 +10780,16 @@
         <v>866</v>
       </c>
       <c r="BA26" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="BB26" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="BC26">
-        <v>0.99526782804010661</v>
+        <v>0.98809190602642238</v>
       </c>
       <c r="BD26">
-        <v>553.63518038790414</v>
+        <v>889.68027824475359</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10854,16 +10854,16 @@
         <v>452</v>
       </c>
       <c r="Y27" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="Z27" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AA27">
-        <v>0.99539558382203508</v>
+        <v>0.99190124970484694</v>
       </c>
       <c r="AB27">
-        <v>84.414296596023817</v>
+        <v>148.47708874447352</v>
       </c>
       <c r="AD27" t="s">
         <v>417</v>
@@ -10896,10 +10896,10 @@
         <v>595</v>
       </c>
       <c r="AO27">
-        <v>0.99310873310996184</v>
+        <v>0.99772400077475298</v>
       </c>
       <c r="AP27">
-        <v>126.33989298403215</v>
+        <v>41.726652462862774</v>
       </c>
       <c r="AR27" t="s">
         <v>417</v>
@@ -10926,16 +10926,16 @@
         <v>868</v>
       </c>
       <c r="BA27" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="BB27" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="BC27">
-        <v>0.98605138538291048</v>
+        <v>0.994208528887633</v>
       </c>
       <c r="BD27">
-        <v>914.54062141820793</v>
+        <v>620.86536659822605</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -11000,16 +11000,16 @@
         <v>454</v>
       </c>
       <c r="Y28" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="Z28" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="AA28">
-        <v>0.99670408962762203</v>
+        <v>0.9940089461809174</v>
       </c>
       <c r="AB28">
-        <v>60.425023493595695</v>
+        <v>109.83598668318054</v>
       </c>
       <c r="AD28" t="s">
         <v>417</v>
@@ -11039,13 +11039,13 @@
         <v>778</v>
       </c>
       <c r="AN28" t="s">
-        <v>581</v>
+        <v>779</v>
       </c>
       <c r="AO28">
-        <v>0.99715437961127318</v>
+        <v>0.99604673274056554</v>
       </c>
       <c r="AP28">
-        <v>52.169707126657627</v>
+        <v>72.476566422965192</v>
       </c>
       <c r="AR28" t="s">
         <v>417</v>
@@ -11072,16 +11072,16 @@
         <v>870</v>
       </c>
       <c r="BA28" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="BB28" t="s">
-        <v>904</v>
+        <v>589</v>
       </c>
       <c r="BC28">
-        <v>0.98158890816872557</v>
+        <v>0.98787195157138663</v>
       </c>
       <c r="BD28">
-        <v>968.90846881102618</v>
+        <v>892.36005668860651</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11146,16 +11146,16 @@
         <v>456</v>
       </c>
       <c r="Y29" t="s">
-        <v>361</v>
+        <v>396</v>
       </c>
       <c r="Z29" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AA29">
-        <v>0.9960389195261472</v>
+        <v>0.99600761890991041</v>
       </c>
       <c r="AB29">
-        <v>72.619808687301173</v>
+        <v>73.193653318309615</v>
       </c>
       <c r="AD29" t="s">
         <v>417</v>
@@ -11182,16 +11182,16 @@
         <v>660</v>
       </c>
       <c r="AM29" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AN29" t="s">
-        <v>590</v>
+        <v>781</v>
       </c>
       <c r="AO29">
-        <v>0.9950502580620818</v>
+        <v>0.99439150850611324</v>
       </c>
       <c r="AP29">
-        <v>90.745268861833736</v>
+        <v>102.82234405458999</v>
       </c>
       <c r="AR29" t="s">
         <v>417</v>
@@ -11218,16 +11218,16 @@
         <v>872</v>
       </c>
       <c r="BA29" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="BB29" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="BC29">
-        <v>0.98402494782096717</v>
+        <v>0.98853599644984702</v>
       </c>
       <c r="BD29">
-        <v>939.22938571455006</v>
+        <v>884.26977658603062</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11292,16 +11292,16 @@
         <v>458</v>
       </c>
       <c r="Y30" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="Z30" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA30">
-        <v>0.99707957985864093</v>
+        <v>0.99700029739711071</v>
       </c>
       <c r="AB30">
-        <v>53.541035924916123</v>
+        <v>54.994547719637801</v>
       </c>
       <c r="AD30" t="s">
         <v>417</v>
@@ -11328,16 +11328,16 @@
         <v>662</v>
       </c>
       <c r="AM30" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AN30" t="s">
-        <v>615</v>
+        <v>578</v>
       </c>
       <c r="AO30">
-        <v>0.99533901157332205</v>
+        <v>0.99595416313893737</v>
       </c>
       <c r="AP30">
-        <v>85.451454489096079</v>
+        <v>74.173675786148877</v>
       </c>
       <c r="AR30" t="s">
         <v>417</v>
@@ -11364,16 +11364,16 @@
         <v>874</v>
       </c>
       <c r="BA30" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="BB30" t="s">
-        <v>581</v>
+        <v>905</v>
       </c>
       <c r="BC30">
-        <v>0.99223982078870177</v>
+        <v>0.98137594918937099</v>
       </c>
       <c r="BD30">
-        <v>745.81270727705794</v>
+        <v>971.50301904282946</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11438,16 +11438,16 @@
         <v>460</v>
       </c>
       <c r="Y31" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="Z31" t="s">
         <v>595</v>
       </c>
       <c r="AA31">
-        <v>0.99478609753984348</v>
+        <v>0.99408511741207395</v>
       </c>
       <c r="AB31">
-        <v>95.588211769535249</v>
+        <v>108.43951411197776</v>
       </c>
       <c r="AD31" t="s">
         <v>417</v>
@@ -11474,16 +11474,16 @@
         <v>664</v>
       </c>
       <c r="AM31" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="AN31" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="AO31">
-        <v>0.99754339130519476</v>
+        <v>0.99687821505939955</v>
       </c>
       <c r="AP31">
-        <v>45.037826071429087</v>
+        <v>57.232723911007447</v>
       </c>
       <c r="AR31" t="s">
         <v>417</v>
@@ -11510,16 +11510,16 @@
         <v>876</v>
       </c>
       <c r="BA31" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="BB31" t="s">
-        <v>613</v>
+        <v>578</v>
       </c>
       <c r="BC31">
-        <v>0.98838558997012138</v>
+        <v>0.9889956676941275</v>
       </c>
       <c r="BD31">
-        <v>886.10222886402141</v>
+        <v>878.66944859321336</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11584,16 +11584,16 @@
         <v>462</v>
       </c>
       <c r="Y32" t="s">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="Z32" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AA32">
-        <v>0.99568525132868968</v>
+        <v>0.99529948277209723</v>
       </c>
       <c r="AB32">
-        <v>79.10372564068922</v>
+        <v>86.176149178218239</v>
       </c>
       <c r="AD32" t="s">
         <v>417</v>
@@ -11620,16 +11620,16 @@
         <v>666</v>
       </c>
       <c r="AM32" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="AN32" t="s">
-        <v>588</v>
+        <v>785</v>
       </c>
       <c r="AO32">
-        <v>0.99542398891280204</v>
+        <v>0.99074948308423383</v>
       </c>
       <c r="AP32">
-        <v>83.893536598629126</v>
+        <v>169.59281012238051</v>
       </c>
       <c r="AR32" t="s">
         <v>417</v>
@@ -11656,16 +11656,16 @@
         <v>878</v>
       </c>
       <c r="BA32" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="BB32" t="s">
-        <v>614</v>
+        <v>578</v>
       </c>
       <c r="BC32">
-        <v>0.98730637899749651</v>
+        <v>0.99193721244794397</v>
       </c>
       <c r="BD32">
-        <v>899.25061588050085</v>
+        <v>765.01824997048959</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11730,16 +11730,16 @@
         <v>464</v>
       </c>
       <c r="Y33" t="s">
-        <v>345</v>
+        <v>407</v>
       </c>
       <c r="Z33" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AA33">
-        <v>0.99590266392783655</v>
+        <v>0.99675394464629852</v>
       </c>
       <c r="AB33">
-        <v>75.117827989662302</v>
+        <v>59.511014817860868</v>
       </c>
       <c r="AD33" t="s">
         <v>417</v>
@@ -11766,16 +11766,16 @@
         <v>668</v>
       </c>
       <c r="AM33" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="AN33" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
       <c r="AO33">
-        <v>0.99617615910816915</v>
+        <v>0.99270401267208797</v>
       </c>
       <c r="AP33">
-        <v>70.103749683564772</v>
+        <v>133.75976767838793</v>
       </c>
       <c r="AR33" t="s">
         <v>417</v>
@@ -11802,16 +11802,16 @@
         <v>880</v>
       </c>
       <c r="BA33" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="BB33" t="s">
-        <v>603</v>
+        <v>583</v>
       </c>
       <c r="BC33">
-        <v>0.98809190602642238</v>
+        <v>0.98734896749216872</v>
       </c>
       <c r="BD33">
-        <v>889.68027824475359</v>
+        <v>898.7317460537439</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11876,16 +11876,16 @@
         <v>466</v>
       </c>
       <c r="Y34" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="Z34" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AA34">
-        <v>0.99449671322390631</v>
+        <v>0.9962437778559039</v>
       </c>
       <c r="AB34">
-        <v>100.89359089505045</v>
+        <v>68.86407264176249</v>
       </c>
       <c r="AD34" t="s">
         <v>417</v>
@@ -11912,16 +11912,16 @@
         <v>670</v>
       </c>
       <c r="AM34" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="AN34" t="s">
-        <v>785</v>
+        <v>595</v>
       </c>
       <c r="AO34">
-        <v>0.99584476105827657</v>
+        <v>0.99764772442226368</v>
       </c>
       <c r="AP34">
-        <v>76.179380598263194</v>
+        <v>43.125052258499352</v>
       </c>
       <c r="AR34" t="s">
         <v>417</v>
@@ -11948,16 +11948,16 @@
         <v>882</v>
       </c>
       <c r="BA34" t="s">
+        <v>909</v>
+      </c>
+      <c r="BB34" t="s">
         <v>910</v>
       </c>
-      <c r="BB34" t="s">
-        <v>592</v>
-      </c>
       <c r="BC34">
-        <v>0.994208528887633</v>
+        <v>0.99308209783432144</v>
       </c>
       <c r="BD34">
-        <v>620.86536659822605</v>
+        <v>692.35619078172965</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -12022,16 +12022,16 @@
         <v>468</v>
       </c>
       <c r="Y35" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="Z35" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="AA35">
-        <v>0.99701127670202949</v>
+        <v>0.99617006411660358</v>
       </c>
       <c r="AB35">
-        <v>54.793260462791778</v>
+        <v>70.215491195600634</v>
       </c>
       <c r="AD35" t="s">
         <v>417</v>
@@ -12058,16 +12058,16 @@
         <v>672</v>
       </c>
       <c r="AM35" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AN35" t="s">
-        <v>598</v>
+        <v>779</v>
       </c>
       <c r="AO35">
-        <v>0.9961146125371938</v>
+        <v>0.99703044337128366</v>
       </c>
       <c r="AP35">
-        <v>71.232103484781334</v>
+        <v>54.441871526466279</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -12132,16 +12132,16 @@
         <v>470</v>
       </c>
       <c r="Y36" t="s">
-        <v>407</v>
+        <v>362</v>
       </c>
       <c r="Z36" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="AA36">
-        <v>0.99675394464629852</v>
+        <v>0.99699505644961572</v>
       </c>
       <c r="AB36">
-        <v>59.511014817860868</v>
+        <v>55.090631757044932</v>
       </c>
       <c r="AD36" t="s">
         <v>417</v>
@@ -12168,16 +12168,16 @@
         <v>674</v>
       </c>
       <c r="AM36" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AN36" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="AO36">
-        <v>0.99607298561021362</v>
+        <v>0.99368259233234391</v>
       </c>
       <c r="AP36">
-        <v>71.995263812749926</v>
+        <v>115.81914057369519</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12242,16 +12242,16 @@
         <v>472</v>
       </c>
       <c r="Y37" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Z37" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="AA37">
-        <v>0.9962437778559039</v>
+        <v>0.99170691261633115</v>
       </c>
       <c r="AB37">
-        <v>68.86407264176249</v>
+        <v>152.03993536726261</v>
       </c>
       <c r="AD37" t="s">
         <v>417</v>
@@ -12278,16 +12278,16 @@
         <v>676</v>
       </c>
       <c r="AM37" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AN37" t="s">
-        <v>608</v>
+        <v>578</v>
       </c>
       <c r="AO37">
-        <v>0.9929182563937401</v>
+        <v>0.9954443722844073</v>
       </c>
       <c r="AP37">
-        <v>129.83196611476453</v>
+        <v>83.519841452532361</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12352,16 +12352,16 @@
         <v>474</v>
       </c>
       <c r="Y38" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Z38" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="AA38">
-        <v>0.99617006411660358</v>
+        <v>0.9904035062850528</v>
       </c>
       <c r="AB38">
-        <v>70.215491195600634</v>
+        <v>175.93571810736526</v>
       </c>
       <c r="AD38" t="s">
         <v>417</v>
@@ -12388,16 +12388,16 @@
         <v>678</v>
       </c>
       <c r="AM38" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="AN38" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AO38">
-        <v>0.99628542339510884</v>
+        <v>0.99363040616365128</v>
       </c>
       <c r="AP38">
-        <v>68.100571089671959</v>
+        <v>116.77588699972566</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12462,16 +12462,16 @@
         <v>476</v>
       </c>
       <c r="Y39" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="Z39" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AA39">
-        <v>0.99462937148232844</v>
+        <v>0.99578350963230966</v>
       </c>
       <c r="AB39">
-        <v>98.461522823979266</v>
+        <v>77.302323407656075</v>
       </c>
       <c r="AD39" t="s">
         <v>417</v>
@@ -12498,16 +12498,16 @@
         <v>680</v>
       </c>
       <c r="AM39" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="AN39" t="s">
-        <v>614</v>
+        <v>579</v>
       </c>
       <c r="AO39">
-        <v>0.99418244113372889</v>
+        <v>0.99782402570187057</v>
       </c>
       <c r="AP39">
-        <v>106.6552458816375</v>
+        <v>39.892862132373601</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12572,16 +12572,16 @@
         <v>478</v>
       </c>
       <c r="Y40" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Z40" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="AA40">
-        <v>0.99462643269733408</v>
+        <v>0.99720191150310689</v>
       </c>
       <c r="AB40">
-        <v>98.51540054887441</v>
+        <v>51.298289109706943</v>
       </c>
       <c r="AD40" t="s">
         <v>417</v>
@@ -12608,16 +12608,16 @@
         <v>682</v>
       </c>
       <c r="AM40" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="AN40" t="s">
-        <v>775</v>
+        <v>595</v>
       </c>
       <c r="AO40">
-        <v>0.99206751173516827</v>
+        <v>0.99756462867082185</v>
       </c>
       <c r="AP40">
-        <v>145.42895152191466</v>
+        <v>44.648474368267038</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12682,16 +12682,16 @@
         <v>480</v>
       </c>
       <c r="Y41" t="s">
-        <v>365</v>
+        <v>404</v>
       </c>
       <c r="Z41" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AA41">
-        <v>0.99755789282691543</v>
+        <v>0.9954551465796494</v>
       </c>
       <c r="AB41">
-        <v>44.77196483988353</v>
+        <v>83.32231270642734</v>
       </c>
       <c r="AD41" t="s">
         <v>417</v>
@@ -12718,16 +12718,16 @@
         <v>684</v>
       </c>
       <c r="AM41" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="AN41" t="s">
-        <v>793</v>
+        <v>590</v>
       </c>
       <c r="AO41">
-        <v>0.99566554346996428</v>
+        <v>0.99418244113372889</v>
       </c>
       <c r="AP41">
-        <v>79.46503638398778</v>
+        <v>106.6552458816375</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12792,16 +12792,16 @@
         <v>482</v>
       </c>
       <c r="Y42" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="Z42" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="AA42">
-        <v>0.99246356041150996</v>
+        <v>0.99552053983611355</v>
       </c>
       <c r="AB42">
-        <v>138.16805912231732</v>
+        <v>82.123436337918946</v>
       </c>
       <c r="AD42" t="s">
         <v>417</v>
@@ -12828,16 +12828,16 @@
         <v>686</v>
       </c>
       <c r="AM42" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AN42" t="s">
-        <v>580</v>
+        <v>796</v>
       </c>
       <c r="AO42">
-        <v>0.99667664296701652</v>
+        <v>0.99206751173516827</v>
       </c>
       <c r="AP42">
-        <v>60.928212271363194</v>
+        <v>145.42895152191466</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12902,16 +12902,16 @@
         <v>484</v>
       </c>
       <c r="Y43" t="s">
-        <v>344</v>
+        <v>388</v>
       </c>
       <c r="Z43" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AA43">
-        <v>0.99571525957109708</v>
+        <v>0.98935435476104872</v>
       </c>
       <c r="AB43">
-        <v>78.553574529886689</v>
+        <v>195.1701627141077</v>
       </c>
       <c r="AD43" t="s">
         <v>417</v>
@@ -12938,16 +12938,16 @@
         <v>688</v>
       </c>
       <c r="AM43" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AN43" t="s">
-        <v>614</v>
+        <v>798</v>
       </c>
       <c r="AO43">
-        <v>0.99608442334318104</v>
+        <v>0.99566554346996428</v>
       </c>
       <c r="AP43">
-        <v>71.785572041680055</v>
+        <v>79.46503638398778</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -13012,16 +13012,16 @@
         <v>486</v>
       </c>
       <c r="Y44" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Z44" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="AA44">
-        <v>0.99553579843385909</v>
+        <v>0.99775872574768198</v>
       </c>
       <c r="AB44">
-        <v>81.84369537924907</v>
+        <v>41.090027959164246</v>
       </c>
       <c r="AD44" t="s">
         <v>417</v>
@@ -13048,16 +13048,16 @@
         <v>690</v>
       </c>
       <c r="AM44" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="AN44" t="s">
         <v>594</v>
       </c>
       <c r="AO44">
-        <v>0.9967907157363165</v>
+        <v>0.99667664296701652</v>
       </c>
       <c r="AP44">
-        <v>58.836878167530941</v>
+        <v>60.928212271363194</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13122,16 +13122,16 @@
         <v>488</v>
       </c>
       <c r="Y45" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="Z45" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="AA45">
-        <v>0.99734372305564056</v>
+        <v>0.99571525957109708</v>
       </c>
       <c r="AB45">
-        <v>48.698410646589842</v>
+        <v>78.553574529886689</v>
       </c>
       <c r="AD45" t="s">
         <v>417</v>
@@ -13158,16 +13158,16 @@
         <v>692</v>
       </c>
       <c r="AM45" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="AN45" t="s">
-        <v>798</v>
+        <v>590</v>
       </c>
       <c r="AO45">
-        <v>0.99443964677468366</v>
+        <v>0.99608442334318104</v>
       </c>
       <c r="AP45">
-        <v>101.93980913079895</v>
+        <v>71.785572041680055</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13232,16 +13232,16 @@
         <v>490</v>
       </c>
       <c r="Y46" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="Z46" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="AA46">
-        <v>0.99662670467221526</v>
+        <v>0.99553579843385909</v>
       </c>
       <c r="AB46">
-        <v>61.843747676054292</v>
+        <v>81.84369537924907</v>
       </c>
       <c r="AD46" t="s">
         <v>417</v>
@@ -13268,16 +13268,16 @@
         <v>694</v>
       </c>
       <c r="AM46" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="AN46" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="AO46">
-        <v>0.99761003390352465</v>
+        <v>0.9967907157363165</v>
       </c>
       <c r="AP46">
-        <v>43.816045102048356</v>
+        <v>58.836878167530941</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13342,16 +13342,16 @@
         <v>492</v>
       </c>
       <c r="Y47" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="Z47" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="AA47">
-        <v>0.99740761205901929</v>
+        <v>0.99734372305564056</v>
       </c>
       <c r="AB47">
-        <v>47.527112251312907</v>
+        <v>48.698410646589842</v>
       </c>
       <c r="AD47" t="s">
         <v>417</v>
@@ -13378,16 +13378,16 @@
         <v>696</v>
       </c>
       <c r="AM47" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AN47" t="s">
-        <v>590</v>
+        <v>803</v>
       </c>
       <c r="AO47">
-        <v>0.99777413567568085</v>
+        <v>0.99443964677468366</v>
       </c>
       <c r="AP47">
-        <v>40.807512612516987</v>
+        <v>101.93980913079895</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13452,16 +13452,16 @@
         <v>494</v>
       </c>
       <c r="Y48" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="Z48" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="AA48">
-        <v>0.99730769203227776</v>
+        <v>0.99662670467221526</v>
       </c>
       <c r="AB48">
-        <v>49.358979408241737</v>
+        <v>61.843747676054292</v>
       </c>
       <c r="AD48" t="s">
         <v>417</v>
@@ -13488,16 +13488,16 @@
         <v>698</v>
       </c>
       <c r="AM48" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AN48" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="AO48">
-        <v>0.99611612132862803</v>
+        <v>0.99761003390352465</v>
       </c>
       <c r="AP48">
-        <v>71.204442308486065</v>
+        <v>43.816045102048356</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13562,16 +13562,16 @@
         <v>496</v>
       </c>
       <c r="Y49" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="Z49" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="AA49">
-        <v>0.998073964784436</v>
+        <v>0.99740761205901929</v>
       </c>
       <c r="AB49">
-        <v>35.310645618673441</v>
+        <v>47.527112251312907</v>
       </c>
       <c r="AD49" t="s">
         <v>417</v>
@@ -13598,16 +13598,16 @@
         <v>700</v>
       </c>
       <c r="AM49" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="AN49" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="AO49">
-        <v>0.99761105057437038</v>
+        <v>0.99777413567568085</v>
       </c>
       <c r="AP49">
-        <v>43.797406136543607</v>
+        <v>40.807512612516987</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13672,16 +13672,16 @@
         <v>498</v>
       </c>
       <c r="Y50" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="Z50" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="AA50">
-        <v>0.99282834435956602</v>
+        <v>0.99730769203227776</v>
       </c>
       <c r="AB50">
-        <v>131.48035340795542</v>
+        <v>49.358979408241737</v>
       </c>
       <c r="AD50" t="s">
         <v>417</v>
@@ -13708,16 +13708,16 @@
         <v>702</v>
       </c>
       <c r="AM50" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="AN50" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AO50">
-        <v>0.99615289372526561</v>
+        <v>0.99660391553167893</v>
       </c>
       <c r="AP50">
-        <v>70.530281703464368</v>
+        <v>62.261548585886977</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13782,16 +13782,16 @@
         <v>500</v>
       </c>
       <c r="Y51" t="s">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="Z51" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="AA51">
-        <v>0.99569310304523451</v>
+        <v>0.998073964784436</v>
       </c>
       <c r="AB51">
-        <v>78.959777504033639</v>
+        <v>35.310645618673441</v>
       </c>
       <c r="AD51" t="s">
         <v>417</v>
@@ -13818,16 +13818,16 @@
         <v>704</v>
       </c>
       <c r="AM51" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="AN51" t="s">
-        <v>805</v>
+        <v>616</v>
       </c>
       <c r="AO51">
-        <v>0.99474825047892679</v>
+        <v>0.9959136876641268</v>
       </c>
       <c r="AP51">
-        <v>96.282074553009053</v>
+        <v>74.915726157675209</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13892,16 +13892,16 @@
         <v>502</v>
       </c>
       <c r="Y52" t="s">
-        <v>414</v>
+        <v>339</v>
       </c>
       <c r="Z52" t="s">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="AA52">
-        <v>0.99502431999137919</v>
+        <v>0.99359748433922845</v>
       </c>
       <c r="AB52">
-        <v>91.220800158047325</v>
+        <v>117.37945378081078</v>
       </c>
       <c r="AD52" t="s">
         <v>417</v>
@@ -13928,16 +13928,16 @@
         <v>706</v>
       </c>
       <c r="AM52" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="AN52" t="s">
-        <v>807</v>
+        <v>578</v>
       </c>
       <c r="AO52">
-        <v>0.99684527597966854</v>
+        <v>0.9935275292913992</v>
       </c>
       <c r="AP52">
-        <v>57.836607039410005</v>
+        <v>118.66196299101547</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -14002,16 +14002,16 @@
         <v>504</v>
       </c>
       <c r="Y53" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="Z53" t="s">
-        <v>605</v>
+        <v>578</v>
       </c>
       <c r="AA53">
-        <v>0.99584577617815018</v>
+        <v>0.99592552983543692</v>
       </c>
       <c r="AB53">
-        <v>76.16077006724673</v>
+        <v>74.698619683656872</v>
       </c>
       <c r="AD53" t="s">
         <v>417</v>
@@ -14038,16 +14038,16 @@
         <v>708</v>
       </c>
       <c r="AM53" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AN53" t="s">
-        <v>620</v>
+        <v>580</v>
       </c>
       <c r="AO53">
-        <v>0.9943927545810437</v>
+        <v>0.99687120387267125</v>
       </c>
       <c r="AP53">
-        <v>102.79949934753229</v>
+        <v>57.361262334360205</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -14112,16 +14112,16 @@
         <v>506</v>
       </c>
       <c r="Y54" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="Z54" t="s">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="AA54">
-        <v>0.99699505644961572</v>
+        <v>0.99463677905825021</v>
       </c>
       <c r="AB54">
-        <v>55.090631757044932</v>
+        <v>98.325717265413417</v>
       </c>
       <c r="AD54" t="s">
         <v>417</v>
@@ -14148,16 +14148,16 @@
         <v>710</v>
       </c>
       <c r="AM54" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AN54" t="s">
-        <v>618</v>
+        <v>579</v>
       </c>
       <c r="AO54">
-        <v>0.99368259233234391</v>
+        <v>0.99720397512579328</v>
       </c>
       <c r="AP54">
-        <v>115.81914057369519</v>
+        <v>51.260456027123361</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -14222,16 +14222,16 @@
         <v>508</v>
       </c>
       <c r="Y55" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="Z55" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AA55">
-        <v>0.99170691261633115</v>
+        <v>0.99667564038633161</v>
       </c>
       <c r="AB55">
-        <v>152.03993536726261</v>
+        <v>60.946592917253042</v>
       </c>
       <c r="AD55" t="s">
         <v>417</v>
@@ -14258,16 +14258,16 @@
         <v>712</v>
       </c>
       <c r="AM55" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AN55" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="AO55">
-        <v>0.9954443722844073</v>
+        <v>0.99565348329230585</v>
       </c>
       <c r="AP55">
-        <v>83.519841452532361</v>
+        <v>79.686139641060379</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14332,16 +14332,16 @@
         <v>510</v>
       </c>
       <c r="Y56" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="Z56" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="AA56">
-        <v>0.9904035062850528</v>
+        <v>0.99462937148232844</v>
       </c>
       <c r="AB56">
-        <v>175.93571810736526</v>
+        <v>98.461522823979266</v>
       </c>
       <c r="AD56" t="s">
         <v>417</v>
@@ -14368,16 +14368,16 @@
         <v>714</v>
       </c>
       <c r="AM56" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AN56" t="s">
-        <v>602</v>
+        <v>813</v>
       </c>
       <c r="AO56">
-        <v>0.99363040616365128</v>
+        <v>0.99618121233373258</v>
       </c>
       <c r="AP56">
-        <v>116.77588699972566</v>
+        <v>70.011107214903078</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14442,16 +14442,16 @@
         <v>512</v>
       </c>
       <c r="Y57" t="s">
-        <v>340</v>
+        <v>408</v>
       </c>
       <c r="Z57" t="s">
-        <v>606</v>
+        <v>578</v>
       </c>
       <c r="AA57">
-        <v>0.99551989204648861</v>
+        <v>0.99462643269733408</v>
       </c>
       <c r="AB57">
-        <v>82.135312481041623</v>
+        <v>98.51540054887441</v>
       </c>
       <c r="AD57" t="s">
         <v>417</v>
@@ -14478,16 +14478,16 @@
         <v>716</v>
       </c>
       <c r="AM57" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="AN57" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AO57">
-        <v>0.99782402570187057</v>
+        <v>0.99592364356186902</v>
       </c>
       <c r="AP57">
-        <v>39.892862132373601</v>
+        <v>74.733201365734146</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14552,16 +14552,16 @@
         <v>514</v>
       </c>
       <c r="Y58" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="Z58" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="AA58">
-        <v>0.9979392050107273</v>
+        <v>0.99755789282691543</v>
       </c>
       <c r="AB58">
-        <v>37.781241469999252</v>
+        <v>44.77196483988353</v>
       </c>
       <c r="AD58" t="s">
         <v>417</v>
@@ -14588,16 +14588,16 @@
         <v>718</v>
       </c>
       <c r="AM58" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="AN58" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AO58">
-        <v>0.99756462867082185</v>
+        <v>0.99641167752379312</v>
       </c>
       <c r="AP58">
-        <v>44.648474368267038</v>
+        <v>65.785912063792665</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14662,16 +14662,16 @@
         <v>516</v>
       </c>
       <c r="Y59" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="Z59" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="AA59">
-        <v>0.9982033297630386</v>
+        <v>0.99246356041150996</v>
       </c>
       <c r="AB59">
-        <v>32.938954344292306</v>
+        <v>138.16805912231732</v>
       </c>
       <c r="AD59" t="s">
         <v>417</v>
@@ -14698,16 +14698,16 @@
         <v>720</v>
       </c>
       <c r="AM59" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="AN59" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AO59">
-        <v>0.99720397512579328</v>
+        <v>0.99245794727704639</v>
       </c>
       <c r="AP59">
-        <v>51.260456027123361</v>
+        <v>138.27096658748206</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14772,16 +14772,16 @@
         <v>518</v>
       </c>
       <c r="Y60" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="Z60" t="s">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="AA60">
-        <v>0.99769372286934066</v>
+        <v>0.99282834435956602</v>
       </c>
       <c r="AB60">
-        <v>42.281747395421668</v>
+        <v>131.48035340795542</v>
       </c>
       <c r="AD60" t="s">
         <v>417</v>
@@ -14808,16 +14808,16 @@
         <v>722</v>
       </c>
       <c r="AM60" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="AN60" t="s">
-        <v>592</v>
+        <v>796</v>
       </c>
       <c r="AO60">
-        <v>0.99565348329230585</v>
+        <v>0.99381230463557813</v>
       </c>
       <c r="AP60">
-        <v>79.686139641060379</v>
+        <v>113.44108168106689</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14882,16 +14882,16 @@
         <v>520</v>
       </c>
       <c r="Y61" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="Z61" t="s">
         <v>607</v>
       </c>
       <c r="AA61">
-        <v>0.99359748433922845</v>
+        <v>0.99569310304523451</v>
       </c>
       <c r="AB61">
-        <v>117.37945378081078</v>
+        <v>78.959777504033639</v>
       </c>
       <c r="AD61" t="s">
         <v>417</v>
@@ -14918,16 +14918,16 @@
         <v>724</v>
       </c>
       <c r="AM61" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AN61" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="AO61">
-        <v>0.99568571110966864</v>
+        <v>0.99534539864304916</v>
       </c>
       <c r="AP61">
-        <v>79.095296322741547</v>
+        <v>85.3343582107656</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14992,16 +14992,16 @@
         <v>522</v>
       </c>
       <c r="Y62" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="Z62" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="AA62">
-        <v>0.99592552983543692</v>
+        <v>0.99502431999137919</v>
       </c>
       <c r="AB62">
-        <v>74.698619683656872</v>
+        <v>91.220800158047325</v>
       </c>
       <c r="AD62" t="s">
         <v>417</v>
@@ -15028,16 +15028,16 @@
         <v>726</v>
       </c>
       <c r="AM62" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="AN62" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="AO62">
-        <v>0.99609062270337045</v>
+        <v>0.99310873310996184</v>
       </c>
       <c r="AP62">
-        <v>71.671917104874566</v>
+        <v>126.33989298403215</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -15102,16 +15102,16 @@
         <v>524</v>
       </c>
       <c r="Y63" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="Z63" t="s">
         <v>608</v>
       </c>
       <c r="AA63">
-        <v>0.99463677905825021</v>
+        <v>0.99584577617815018</v>
       </c>
       <c r="AB63">
-        <v>98.325717265413417</v>
+        <v>76.16077006724673</v>
       </c>
       <c r="AD63" t="s">
         <v>417</v>
@@ -15138,16 +15138,16 @@
         <v>728</v>
       </c>
       <c r="AM63" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="AN63" t="s">
-        <v>819</v>
+        <v>578</v>
       </c>
       <c r="AO63">
-        <v>0.99598588086244633</v>
+        <v>0.99715437961127318</v>
       </c>
       <c r="AP63">
-        <v>73.592184188484865</v>
+        <v>52.169707126657627</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -15212,16 +15212,16 @@
         <v>526</v>
       </c>
       <c r="Y64" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="Z64" t="s">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="AA64">
-        <v>0.99667564038633161</v>
+        <v>0.99569491323214321</v>
       </c>
       <c r="AB64">
-        <v>60.946592917253042</v>
+        <v>78.926590744041093</v>
       </c>
       <c r="AD64" t="s">
         <v>417</v>
@@ -15248,16 +15248,16 @@
         <v>730</v>
       </c>
       <c r="AM64" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AN64" t="s">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="AO64">
-        <v>0.99660391553167893</v>
+        <v>0.9950502580620818</v>
       </c>
       <c r="AP64">
-        <v>62.261548585886977</v>
+        <v>90.745268861833736</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -15322,16 +15322,16 @@
         <v>528</v>
       </c>
       <c r="Y65" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="Z65" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="AA65">
-        <v>0.99125780375299366</v>
+        <v>0.99484118006716937</v>
       </c>
       <c r="AB65">
-        <v>160.27359786178269</v>
+        <v>94.578365435227795</v>
       </c>
       <c r="AD65" t="s">
         <v>417</v>
@@ -15358,16 +15358,16 @@
         <v>732</v>
       </c>
       <c r="AM65" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AN65" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="AO65">
-        <v>0.9959136876641268</v>
+        <v>0.99533901157332205</v>
       </c>
       <c r="AP65">
-        <v>74.915726157675209</v>
+        <v>85.451454489096079</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15432,16 +15432,16 @@
         <v>530</v>
       </c>
       <c r="Y66" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="Z66" t="s">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="AA66">
-        <v>0.99619006668481902</v>
+        <v>0.99539558382203508</v>
       </c>
       <c r="AB66">
-        <v>69.848777444984194</v>
+        <v>84.414296596023817</v>
       </c>
       <c r="AD66" t="s">
         <v>417</v>
@@ -15468,16 +15468,16 @@
         <v>734</v>
       </c>
       <c r="AM66" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AN66" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO66">
-        <v>0.9935275292913992</v>
+        <v>0.99754339130519476</v>
       </c>
       <c r="AP66">
-        <v>118.66196299101547</v>
+        <v>45.037826071429087</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15542,16 +15542,16 @@
         <v>532</v>
       </c>
       <c r="Y67" t="s">
-        <v>386</v>
+        <v>350</v>
       </c>
       <c r="Z67" t="s">
         <v>610</v>
       </c>
       <c r="AA67">
-        <v>0.99021813732178554</v>
+        <v>0.99478609753984348</v>
       </c>
       <c r="AB67">
-        <v>179.3341491005981</v>
+        <v>95.588211769535249</v>
       </c>
       <c r="AD67" t="s">
         <v>417</v>
@@ -15578,16 +15578,16 @@
         <v>736</v>
       </c>
       <c r="AM67" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AN67" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="AO67">
-        <v>0.99687120387267125</v>
+        <v>0.99542398891280204</v>
       </c>
       <c r="AP67">
-        <v>57.361262334360205</v>
+        <v>83.893536598629126</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15652,16 +15652,16 @@
         <v>534</v>
       </c>
       <c r="Y68" t="s">
-        <v>392</v>
+        <v>348</v>
       </c>
       <c r="Z68" t="s">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="AA68">
-        <v>0.99686736582623381</v>
+        <v>0.99568525132868968</v>
       </c>
       <c r="AB68">
-        <v>57.431626519047455</v>
+        <v>79.10372564068922</v>
       </c>
       <c r="AD68" t="s">
         <v>417</v>
@@ -15688,16 +15688,16 @@
         <v>738</v>
       </c>
       <c r="AM68" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AN68" t="s">
-        <v>825</v>
+        <v>595</v>
       </c>
       <c r="AO68">
-        <v>0.99618121233373258</v>
+        <v>0.99617615910816915</v>
       </c>
       <c r="AP68">
-        <v>70.011107214903078</v>
+        <v>70.103749683564772</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -15762,16 +15762,16 @@
         <v>536</v>
       </c>
       <c r="Y69" t="s">
-        <v>383</v>
+        <v>345</v>
       </c>
       <c r="Z69" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA69">
-        <v>0.99725672762159434</v>
+        <v>0.99590266392783655</v>
       </c>
       <c r="AB69">
-        <v>50.29332693743671</v>
+        <v>75.117827989662302</v>
       </c>
       <c r="AD69" t="s">
         <v>417</v>
@@ -15801,13 +15801,13 @@
         <v>826</v>
       </c>
       <c r="AN69" t="s">
-        <v>617</v>
+        <v>581</v>
       </c>
       <c r="AO69">
-        <v>0.99592364356186902</v>
+        <v>0.99568571110966864</v>
       </c>
       <c r="AP69">
-        <v>74.733201365734146</v>
+        <v>79.095296322741547</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -15872,16 +15872,16 @@
         <v>538</v>
       </c>
       <c r="Y70" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="Z70" t="s">
-        <v>612</v>
+        <v>582</v>
       </c>
       <c r="AA70">
-        <v>0.99579357955795456</v>
+        <v>0.99449671322390631</v>
       </c>
       <c r="AB70">
-        <v>77.117708104165573</v>
+        <v>100.89359089505045</v>
       </c>
       <c r="AD70" t="s">
         <v>417</v>
@@ -15911,13 +15911,13 @@
         <v>827</v>
       </c>
       <c r="AN70" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="AO70">
-        <v>0.99641167752379312</v>
+        <v>0.99609062270337045</v>
       </c>
       <c r="AP70">
-        <v>65.785912063792665</v>
+        <v>71.671917104874566</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -15982,16 +15982,16 @@
         <v>540</v>
       </c>
       <c r="Y71" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="Z71" t="s">
-        <v>613</v>
+        <v>580</v>
       </c>
       <c r="AA71">
-        <v>0.99066346416517681</v>
+        <v>0.99701127670202949</v>
       </c>
       <c r="AB71">
-        <v>171.16982363842584</v>
+        <v>54.793260462791778</v>
       </c>
       <c r="AD71" t="s">
         <v>417</v>
@@ -16021,13 +16021,13 @@
         <v>828</v>
       </c>
       <c r="AN71" t="s">
-        <v>785</v>
+        <v>829</v>
       </c>
       <c r="AO71">
-        <v>0.99540934349034305</v>
+        <v>0.99598588086244633</v>
       </c>
       <c r="AP71">
-        <v>84.162036010377406</v>
+        <v>73.592184188484865</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -16092,16 +16092,16 @@
         <v>542</v>
       </c>
       <c r="Y72" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="Z72" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AA72">
-        <v>0.99560939477262078</v>
+        <v>0.99080344458411729</v>
       </c>
       <c r="AB72">
-        <v>80.494429168619106</v>
+        <v>168.60351595784994</v>
       </c>
       <c r="AD72" t="s">
         <v>417</v>
@@ -16128,16 +16128,16 @@
         <v>746</v>
       </c>
       <c r="AM72" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AN72" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO72">
-        <v>0.99657664224037934</v>
+        <v>0.99784941409648109</v>
       </c>
       <c r="AP72">
-        <v>62.761558926379031</v>
+        <v>39.427408231180806</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16202,16 +16202,16 @@
         <v>544</v>
       </c>
       <c r="Y73" t="s">
-        <v>342</v>
+        <v>413</v>
       </c>
       <c r="Z73" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AA73">
-        <v>0.99544039231362502</v>
+        <v>0.98636012609964985</v>
       </c>
       <c r="AB73">
-        <v>83.592807583541571</v>
+        <v>250.06435483975247</v>
       </c>
       <c r="AD73" t="s">
         <v>417</v>
@@ -16238,16 +16238,16 @@
         <v>748</v>
       </c>
       <c r="AM73" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AN73" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="AO73">
-        <v>0.99091245964276031</v>
+        <v>0.99831921281104818</v>
       </c>
       <c r="AP73">
-        <v>166.60490654939525</v>
+        <v>30.814431797450247</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -16312,16 +16312,16 @@
         <v>546</v>
       </c>
       <c r="Y74" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="Z74" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AA74">
-        <v>0.99190124970484694</v>
+        <v>0.99598850450039844</v>
       </c>
       <c r="AB74">
-        <v>148.47708874447352</v>
+        <v>73.544084159361034</v>
       </c>
       <c r="AD74" t="s">
         <v>417</v>
@@ -16348,16 +16348,16 @@
         <v>750</v>
       </c>
       <c r="AM74" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AN74" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="AO74">
-        <v>0.99846230399777702</v>
+        <v>0.99845356202909108</v>
       </c>
       <c r="AP74">
-        <v>28.191093374087806</v>
+        <v>28.351362799997673</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -16422,16 +16422,16 @@
         <v>548</v>
       </c>
       <c r="Y75" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="Z75" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="AA75">
-        <v>0.9940089461809174</v>
+        <v>0.99310312827752323</v>
       </c>
       <c r="AB75">
-        <v>109.83598668318054</v>
+        <v>126.44264824540761</v>
       </c>
       <c r="AD75" t="s">
         <v>417</v>
@@ -16458,16 +16458,16 @@
         <v>752</v>
       </c>
       <c r="AM75" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AN75" t="s">
-        <v>833</v>
+        <v>607</v>
       </c>
       <c r="AO75">
-        <v>0.99439150850611324</v>
+        <v>0.99611612132862803</v>
       </c>
       <c r="AP75">
-        <v>102.82234405458999</v>
+        <v>71.204442308486065</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -16532,16 +16532,16 @@
         <v>550</v>
       </c>
       <c r="Y76" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Z76" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AA76">
-        <v>0.99600761890991041</v>
+        <v>0.99557960200072415</v>
       </c>
       <c r="AB76">
-        <v>73.193653318309615</v>
+        <v>81.040629986723459</v>
       </c>
       <c r="AD76" t="s">
         <v>417</v>
@@ -16571,13 +16571,13 @@
         <v>834</v>
       </c>
       <c r="AN76" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="AO76">
-        <v>0.99595416313893737</v>
+        <v>0.99761105057437038</v>
       </c>
       <c r="AP76">
-        <v>74.173675786148877</v>
+        <v>43.797406136543607</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -16642,16 +16642,16 @@
         <v>552</v>
       </c>
       <c r="Y77" t="s">
-        <v>355</v>
+        <v>401</v>
       </c>
       <c r="Z77" t="s">
-        <v>580</v>
+        <v>617</v>
       </c>
       <c r="AA77">
-        <v>0.99700029739711071</v>
+        <v>0.99295357769237991</v>
       </c>
       <c r="AB77">
-        <v>54.994547719637801</v>
+        <v>129.18440897303603</v>
       </c>
       <c r="AD77" t="s">
         <v>417</v>
@@ -16681,13 +16681,13 @@
         <v>835</v>
       </c>
       <c r="AN77" t="s">
-        <v>620</v>
+        <v>595</v>
       </c>
       <c r="AO77">
-        <v>0.99687821505939955</v>
+        <v>0.99615289372526561</v>
       </c>
       <c r="AP77">
-        <v>57.232723911007447</v>
+        <v>70.530281703464368</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -16752,16 +16752,16 @@
         <v>554</v>
       </c>
       <c r="Y78" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="Z78" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AA78">
-        <v>0.99408511741207395</v>
+        <v>0.99696751363483405</v>
       </c>
       <c r="AB78">
-        <v>108.43951411197776</v>
+        <v>55.595583361375894</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -16826,16 +16826,16 @@
         <v>556</v>
       </c>
       <c r="Y79" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="Z79" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="AA79">
-        <v>0.99529948277209723</v>
+        <v>0.98964014500078279</v>
       </c>
       <c r="AB79">
-        <v>86.176149178218239</v>
+        <v>189.93067498564957</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -16900,16 +16900,16 @@
         <v>558</v>
       </c>
       <c r="Y80" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="Z80" t="s">
         <v>618</v>
       </c>
       <c r="AA80">
-        <v>0.99540885392130762</v>
+        <v>0.9966137462997855</v>
       </c>
       <c r="AB80">
-        <v>84.171011442693441</v>
+        <v>62.081317837266766</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -16974,16 +16974,16 @@
         <v>560</v>
       </c>
       <c r="Y81" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="Z81" t="s">
-        <v>619</v>
+        <v>587</v>
       </c>
       <c r="AA81">
-        <v>0.99360802526828129</v>
+        <v>0.99011796851295664</v>
       </c>
       <c r="AB81">
-        <v>117.18620341484296</v>
+        <v>181.17057726246117</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -17048,16 +17048,16 @@
         <v>562</v>
       </c>
       <c r="Y82" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="Z82" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="AA82">
-        <v>0.99515679011930902</v>
+        <v>0.99635118654529808</v>
       </c>
       <c r="AB82">
-        <v>88.792181146001369</v>
+        <v>66.894913336202478</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -17122,16 +17122,16 @@
         <v>564</v>
       </c>
       <c r="Y83" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Z83" t="s">
         <v>620</v>
       </c>
       <c r="AA83">
-        <v>0.99409145347725225</v>
+        <v>0.99440507690252466</v>
       </c>
       <c r="AB83">
-        <v>108.32335291704148</v>
+        <v>102.57359012038077</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -17196,16 +17196,16 @@
         <v>566</v>
       </c>
       <c r="Y84" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="Z84" t="s">
-        <v>583</v>
+        <v>621</v>
       </c>
       <c r="AA84">
-        <v>0.99464051280908794</v>
+        <v>0.99125780375299366</v>
       </c>
       <c r="AB84">
-        <v>98.257265166721183</v>
+        <v>160.27359786178269</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -17270,16 +17270,16 @@
         <v>568</v>
       </c>
       <c r="Y85" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="Z85" t="s">
         <v>621</v>
       </c>
       <c r="AA85">
-        <v>0.99080344458411729</v>
+        <v>0.99619006668481902</v>
       </c>
       <c r="AB85">
-        <v>168.60351595784994</v>
+        <v>69.848777444984194</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -17344,16 +17344,16 @@
         <v>570</v>
       </c>
       <c r="Y86" t="s">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="Z86" t="s">
         <v>622</v>
       </c>
       <c r="AA86">
-        <v>0.98636012609964985</v>
+        <v>0.99021813732178554</v>
       </c>
       <c r="AB86">
-        <v>250.06435483975247</v>
+        <v>179.3341491005981</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -17418,16 +17418,16 @@
         <v>572</v>
       </c>
       <c r="Y87" t="s">
-        <v>346</v>
+        <v>392</v>
       </c>
       <c r="Z87" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="AA87">
-        <v>0.99598850450039844</v>
+        <v>0.99686736582623381</v>
       </c>
       <c r="AB87">
-        <v>73.544084159361034</v>
+        <v>57.431626519047455</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -17492,16 +17492,16 @@
         <v>574</v>
       </c>
       <c r="Y88" t="s">
-        <v>412</v>
+        <v>383</v>
       </c>
       <c r="Z88" t="s">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="AA88">
-        <v>0.99310312827752323</v>
+        <v>0.99725672762159434</v>
       </c>
       <c r="AB88">
-        <v>126.44264824540761</v>
+        <v>50.29332693743671</v>
       </c>
     </row>
   </sheetData>
@@ -17510,7 +17510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5432F551-B2D3-449A-8983-52E3B2B8CE18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73581D1-67F2-4F2C-8A44-9298A1D2042E}">
   <dimension ref="B9:Z77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -17622,7 +17622,7 @@
         <v>911</v>
       </c>
       <c r="K11" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="L11">
         <v>29.7146465744454</v>
@@ -17655,7 +17655,7 @@
         <v>1045</v>
       </c>
       <c r="X11" t="s">
-        <v>899</v>
+        <v>888</v>
       </c>
       <c r="Y11">
         <v>0.33825</v>
@@ -17690,7 +17690,7 @@
         <v>913</v>
       </c>
       <c r="K12" t="s">
-        <v>779</v>
+        <v>821</v>
       </c>
       <c r="L12">
         <v>13.367096811591049</v>
@@ -17723,7 +17723,7 @@
         <v>1047</v>
       </c>
       <c r="X12" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="Y12">
         <v>10.88325</v>
@@ -17758,7 +17758,7 @@
         <v>915</v>
       </c>
       <c r="K13" t="s">
-        <v>783</v>
+        <v>825</v>
       </c>
       <c r="L13">
         <v>24.156328337033791</v>
@@ -17791,7 +17791,7 @@
         <v>1049</v>
       </c>
       <c r="X13" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="Y13">
         <v>26.983499999999999</v>
@@ -17826,7 +17826,7 @@
         <v>917</v>
       </c>
       <c r="K14" t="s">
-        <v>781</v>
+        <v>823</v>
       </c>
       <c r="L14">
         <v>16.006796560234815</v>
@@ -17859,7 +17859,7 @@
         <v>1051</v>
       </c>
       <c r="X14" t="s">
-        <v>884</v>
+        <v>908</v>
       </c>
       <c r="Y14">
         <v>42.507750000000001</v>
@@ -17894,7 +17894,7 @@
         <v>919</v>
       </c>
       <c r="K15" t="s">
-        <v>777</v>
+        <v>819</v>
       </c>
       <c r="L15">
         <v>17.682358378036344</v>
@@ -17927,7 +17927,7 @@
         <v>1053</v>
       </c>
       <c r="X15" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="Y15">
         <v>24.900749999999999</v>
@@ -17962,7 +17962,7 @@
         <v>921</v>
       </c>
       <c r="K16" t="s">
-        <v>767</v>
+        <v>832</v>
       </c>
       <c r="L16">
         <v>29.492382648463739</v>
@@ -17995,7 +17995,7 @@
         <v>1055</v>
       </c>
       <c r="X16" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="Y16">
         <v>18.545249999999999</v>
@@ -18030,7 +18030,7 @@
         <v>923</v>
       </c>
       <c r="K17" t="s">
-        <v>766</v>
+        <v>831</v>
       </c>
       <c r="L17">
         <v>8.6778699255653748</v>
@@ -18063,7 +18063,7 @@
         <v>1057</v>
       </c>
       <c r="X17" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="Y17">
         <v>29.838000000000001</v>
@@ -18098,7 +18098,7 @@
         <v>925</v>
       </c>
       <c r="K18" t="s">
-        <v>765</v>
+        <v>830</v>
       </c>
       <c r="L18">
         <v>12.772248157772113</v>
@@ -18131,7 +18131,7 @@
         <v>1059</v>
       </c>
       <c r="X18" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="Y18">
         <v>58.689</v>
@@ -18166,7 +18166,7 @@
         <v>927</v>
       </c>
       <c r="K19" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="L19">
         <v>15.217638427037592</v>
@@ -18199,7 +18199,7 @@
         <v>1061</v>
       </c>
       <c r="X19" t="s">
-        <v>885</v>
+        <v>904</v>
       </c>
       <c r="Y19">
         <v>48.432000000000002</v>
@@ -18234,7 +18234,7 @@
         <v>929</v>
       </c>
       <c r="K20" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="L20">
         <v>3.1385663053565613</v>
@@ -18302,7 +18302,7 @@
         <v>931</v>
       </c>
       <c r="K21" t="s">
-        <v>771</v>
+        <v>787</v>
       </c>
       <c r="L21">
         <v>4.0628682283884237</v>
@@ -18335,7 +18335,7 @@
         <v>1065</v>
       </c>
       <c r="X21" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="Y21">
         <v>7.1767500000000002</v>
@@ -18370,7 +18370,7 @@
         <v>933</v>
       </c>
       <c r="K22" t="s">
-        <v>835</v>
+        <v>783</v>
       </c>
       <c r="L22">
         <v>19.408837136062758</v>
@@ -18403,7 +18403,7 @@
         <v>1067</v>
       </c>
       <c r="X22" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="Y22">
         <v>8.1052499999999998</v>
@@ -18438,7 +18438,7 @@
         <v>935</v>
       </c>
       <c r="K23" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="L23">
         <v>15.054857587707319</v>
@@ -18471,7 +18471,7 @@
         <v>1069</v>
       </c>
       <c r="X23" t="s">
-        <v>901</v>
+        <v>890</v>
       </c>
       <c r="Y23">
         <v>9.3810000000000002</v>
@@ -18506,7 +18506,7 @@
         <v>937</v>
       </c>
       <c r="K24" t="s">
-        <v>808</v>
+        <v>762</v>
       </c>
       <c r="L24">
         <v>13.019602602156084</v>
@@ -18539,7 +18539,7 @@
         <v>1071</v>
       </c>
       <c r="X24" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="Y24">
         <v>11.47575</v>
@@ -18574,7 +18574,7 @@
         <v>939</v>
       </c>
       <c r="K25" t="s">
-        <v>760</v>
+        <v>775</v>
       </c>
       <c r="L25">
         <v>25.094411791551167</v>
@@ -18607,7 +18607,7 @@
         <v>1073</v>
       </c>
       <c r="X25" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="Y25">
         <v>6.1372499999999999</v>
@@ -18642,7 +18642,7 @@
         <v>941</v>
       </c>
       <c r="K26" t="s">
-        <v>802</v>
+        <v>834</v>
       </c>
       <c r="L26">
         <v>18.31221960055294</v>
@@ -18675,7 +18675,7 @@
         <v>1075</v>
       </c>
       <c r="X26" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="Y26">
         <v>14.57325</v>
@@ -18710,7 +18710,7 @@
         <v>943</v>
       </c>
       <c r="K27" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="L27">
         <v>27.91719839668141</v>
@@ -18743,7 +18743,7 @@
         <v>1077</v>
       </c>
       <c r="X27" t="s">
-        <v>887</v>
+        <v>906</v>
       </c>
       <c r="Y27">
         <v>10.491</v>
@@ -18778,7 +18778,7 @@
         <v>945</v>
       </c>
       <c r="K28" t="s">
-        <v>831</v>
+        <v>772</v>
       </c>
       <c r="L28">
         <v>8.5144758814389814</v>
@@ -18811,7 +18811,7 @@
         <v>1079</v>
       </c>
       <c r="X28" t="s">
-        <v>900</v>
+        <v>889</v>
       </c>
       <c r="Y28">
         <v>17.414249999999999</v>
@@ -18846,7 +18846,7 @@
         <v>947</v>
       </c>
       <c r="K29" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="L29">
         <v>12.144708893333986</v>
@@ -18879,7 +18879,7 @@
         <v>1081</v>
       </c>
       <c r="X29" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
       <c r="Y29">
         <v>10.968</v>
@@ -18914,7 +18914,7 @@
         <v>949</v>
       </c>
       <c r="K30" t="s">
-        <v>761</v>
+        <v>776</v>
       </c>
       <c r="L30">
         <v>1.6724491767694549</v>
@@ -18947,7 +18947,7 @@
         <v>1083</v>
       </c>
       <c r="X30" t="s">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="Y30">
         <v>10.79175</v>
@@ -18982,7 +18982,7 @@
         <v>951</v>
       </c>
       <c r="K31" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="L31">
         <v>13.894741632015101</v>
@@ -19015,7 +19015,7 @@
         <v>1085</v>
       </c>
       <c r="X31" t="s">
-        <v>891</v>
+        <v>909</v>
       </c>
       <c r="Y31">
         <v>20.114249999999998</v>
@@ -19050,7 +19050,7 @@
         <v>953</v>
       </c>
       <c r="K32" t="s">
-        <v>823</v>
+        <v>809</v>
       </c>
       <c r="L32">
         <v>11.876635800692616</v>
@@ -19083,7 +19083,7 @@
         <v>1087</v>
       </c>
       <c r="X32" t="s">
-        <v>898</v>
+        <v>887</v>
       </c>
       <c r="Y32">
         <v>44.373750000000001</v>
@@ -19118,7 +19118,7 @@
         <v>955</v>
       </c>
       <c r="K33" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="L33">
         <v>27.15579263061009</v>
@@ -19151,7 +19151,7 @@
         <v>1089</v>
       </c>
       <c r="X33" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="Y33">
         <v>18.57525</v>
@@ -19186,7 +19186,7 @@
         <v>957</v>
       </c>
       <c r="K34" t="s">
-        <v>788</v>
+        <v>767</v>
       </c>
       <c r="L34">
         <v>27.043339674957092</v>
@@ -19219,7 +19219,7 @@
         <v>1091</v>
       </c>
       <c r="X34" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="Y34">
         <v>18.241499999999998</v>
@@ -19254,7 +19254,7 @@
         <v>959</v>
       </c>
       <c r="K35" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
       <c r="L35">
         <v>12.170927347824723</v>
@@ -19289,7 +19289,7 @@
         <v>961</v>
       </c>
       <c r="K36" t="s">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="L36">
         <v>26.999240466622091</v>
@@ -19324,7 +19324,7 @@
         <v>963</v>
       </c>
       <c r="K37" t="s">
-        <v>813</v>
+        <v>793</v>
       </c>
       <c r="L37">
         <v>23.305350986470582</v>
@@ -19359,7 +19359,7 @@
         <v>965</v>
       </c>
       <c r="K38" t="s">
-        <v>803</v>
+        <v>835</v>
       </c>
       <c r="L38">
         <v>19.293897715957783</v>
@@ -19394,7 +19394,7 @@
         <v>967</v>
       </c>
       <c r="K39" t="s">
-        <v>782</v>
+        <v>824</v>
       </c>
       <c r="L39">
         <v>34.8352470366899</v>
@@ -19429,7 +19429,7 @@
         <v>969</v>
       </c>
       <c r="K40" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="L40">
         <v>22.439012549480047</v>
@@ -19464,7 +19464,7 @@
         <v>971</v>
       </c>
       <c r="K41" t="s">
-        <v>811</v>
+        <v>791</v>
       </c>
       <c r="L41">
         <v>19.571302094407635</v>
@@ -19499,7 +19499,7 @@
         <v>973</v>
       </c>
       <c r="K42" t="s">
-        <v>830</v>
+        <v>771</v>
       </c>
       <c r="L42">
         <v>16.258507759053195</v>
@@ -19534,7 +19534,7 @@
         <v>975</v>
       </c>
       <c r="K43" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="L43">
         <v>48.074816212675138</v>
@@ -19569,7 +19569,7 @@
         <v>977</v>
       </c>
       <c r="K44" t="s">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="L44">
         <v>65.59399718970684</v>
@@ -19604,7 +19604,7 @@
         <v>979</v>
       </c>
       <c r="K45" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="L45">
         <v>65.706815294563484</v>
@@ -19639,7 +19639,7 @@
         <v>981</v>
       </c>
       <c r="K46" t="s">
-        <v>834</v>
+        <v>782</v>
       </c>
       <c r="L46">
         <v>13.859521883612567</v>
@@ -19674,7 +19674,7 @@
         <v>983</v>
       </c>
       <c r="K47" t="s">
-        <v>829</v>
+        <v>770</v>
       </c>
       <c r="L47">
         <v>32.682899602232801</v>
@@ -19709,7 +19709,7 @@
         <v>985</v>
       </c>
       <c r="K48" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="L48">
         <v>39.028686646898073</v>
@@ -19744,7 +19744,7 @@
         <v>987</v>
       </c>
       <c r="K49" t="s">
-        <v>778</v>
+        <v>820</v>
       </c>
       <c r="L49">
         <v>25.808486809088087</v>
@@ -19779,7 +19779,7 @@
         <v>989</v>
       </c>
       <c r="K50" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="L50">
         <v>64.703394190718342</v>
@@ -19814,7 +19814,7 @@
         <v>991</v>
       </c>
       <c r="K51" t="s">
-        <v>817</v>
+        <v>827</v>
       </c>
       <c r="L51">
         <v>46.777110562179843</v>
@@ -19849,7 +19849,7 @@
         <v>993</v>
       </c>
       <c r="K52" t="s">
-        <v>776</v>
+        <v>818</v>
       </c>
       <c r="L52">
         <v>83.307298494129057</v>
@@ -19884,7 +19884,7 @@
         <v>995</v>
       </c>
       <c r="K53" t="s">
-        <v>809</v>
+        <v>789</v>
       </c>
       <c r="L53">
         <v>8.0718642408500934</v>
@@ -19919,7 +19919,7 @@
         <v>997</v>
       </c>
       <c r="K54" t="s">
-        <v>774</v>
+        <v>817</v>
       </c>
       <c r="L54">
         <v>25.555956589747868</v>
@@ -19954,7 +19954,7 @@
         <v>999</v>
       </c>
       <c r="K55" t="s">
-        <v>810</v>
+        <v>790</v>
       </c>
       <c r="L55">
         <v>26.74310381624198</v>
@@ -19989,7 +19989,7 @@
         <v>1001</v>
       </c>
       <c r="K56" t="s">
-        <v>822</v>
+        <v>808</v>
       </c>
       <c r="L56">
         <v>47.811917655816522</v>
@@ -20024,7 +20024,7 @@
         <v>1003</v>
       </c>
       <c r="K57" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="L57">
         <v>65.898010391046881</v>
@@ -20059,7 +20059,7 @@
         <v>1005</v>
       </c>
       <c r="K58" t="s">
-        <v>820</v>
+        <v>806</v>
       </c>
       <c r="L58">
         <v>49.914822287456737</v>
@@ -20094,7 +20094,7 @@
         <v>1007</v>
       </c>
       <c r="K59" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="L59">
         <v>19.963633091222835</v>
@@ -20129,7 +20129,7 @@
         <v>1009</v>
       </c>
       <c r="K60" t="s">
-        <v>768</v>
+        <v>784</v>
       </c>
       <c r="L60">
         <v>71.04376789192942</v>
@@ -20164,7 +20164,7 @@
         <v>1011</v>
       </c>
       <c r="K61" t="s">
-        <v>780</v>
+        <v>822</v>
       </c>
       <c r="L61">
         <v>43.07229279461999</v>
@@ -20199,7 +20199,7 @@
         <v>1013</v>
       </c>
       <c r="K62" t="s">
-        <v>828</v>
+        <v>769</v>
       </c>
       <c r="L62">
         <v>38.769945374969119</v>
@@ -20234,7 +20234,7 @@
         <v>1015</v>
       </c>
       <c r="K63" t="s">
-        <v>832</v>
+        <v>780</v>
       </c>
       <c r="L63">
         <v>59.009737840109466</v>
@@ -20269,7 +20269,7 @@
         <v>1017</v>
       </c>
       <c r="K64" t="s">
-        <v>806</v>
+        <v>760</v>
       </c>
       <c r="L64">
         <v>28.865927665826828</v>
@@ -20304,7 +20304,7 @@
         <v>1019</v>
       </c>
       <c r="K65" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="L65">
         <v>37.976260419426943</v>
@@ -20339,7 +20339,7 @@
         <v>1021</v>
       </c>
       <c r="K66" t="s">
-        <v>804</v>
+        <v>758</v>
       </c>
       <c r="L66">
         <v>44.88386263672971</v>
@@ -20374,7 +20374,7 @@
         <v>1023</v>
       </c>
       <c r="K67" t="s">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="L67">
         <v>23.350121881103082</v>
@@ -20409,7 +20409,7 @@
         <v>1025</v>
       </c>
       <c r="K68" t="s">
-        <v>759</v>
+        <v>774</v>
       </c>
       <c r="L68">
         <v>15.289477961960474</v>
@@ -20444,7 +20444,7 @@
         <v>1027</v>
       </c>
       <c r="K69" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
       <c r="L69">
         <v>10.395885695189069</v>
@@ -20479,7 +20479,7 @@
         <v>1029</v>
       </c>
       <c r="K70" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="L70">
         <v>23.89105636564183</v>
@@ -20514,7 +20514,7 @@
         <v>1031</v>
       </c>
       <c r="K71" t="s">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="L71">
         <v>18.959710131684457</v>
@@ -20549,7 +20549,7 @@
         <v>1033</v>
       </c>
       <c r="K72" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="L72">
         <v>6.6550975614073966</v>
@@ -20584,7 +20584,7 @@
         <v>1035</v>
       </c>
       <c r="K73" t="s">
-        <v>786</v>
+        <v>765</v>
       </c>
       <c r="L73">
         <v>13.961943802326671</v>
@@ -20619,7 +20619,7 @@
         <v>1037</v>
       </c>
       <c r="K74" t="s">
-        <v>770</v>
+        <v>786</v>
       </c>
       <c r="L74">
         <v>51.937776653453852</v>
@@ -20654,7 +20654,7 @@
         <v>1039</v>
       </c>
       <c r="K75" t="s">
-        <v>773</v>
+        <v>816</v>
       </c>
       <c r="L75">
         <v>21.246092446368579</v>
@@ -20689,7 +20689,7 @@
         <v>1041</v>
       </c>
       <c r="K76" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="L76">
         <v>19.42059121972445</v>
@@ -20724,7 +20724,7 @@
         <v>1043</v>
       </c>
       <c r="K77" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="L77">
         <v>30.063621105864488</v>
@@ -20739,7 +20739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4446820A-3517-4025-BD08-D0FF8ABBD467}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0A3A151-D42F-49EE-B165-FE2BC28AE5EC}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
